--- a/outputs/skin-chart-20260914/먹점프_스킨_뒤끝차트_v1.xlsx
+++ b/outputs/skin-chart-20260914/먹점프_스킨_뒤끝차트_v1.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skins" sheetId="1" r:id="R312382aa90104b52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skins" sheetId="1" r:id="Rcbf59ba86a144020"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -297,6 +297,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="0"/>
+  </x:numFmts>
   <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
@@ -331,7 +334,7 @@
       <x:name val="Apple SD Gothic Neo"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -358,6 +361,21 @@
         <x:fgColor rgb="FF282623"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F2EE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF6DF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0C8"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -365,7 +383,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="21">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -421,6 +439,44 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="1" fontId="3" fillId="4" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -529,8 +585,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MukJumpSkinConfig" displayName="MukJumpSkinConfig" ref="A1:Y63" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:Y63"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MukJumpSkinConfig" displayName="MukJumpSkinConfig" ref="A1:Y64" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:Y64"/>
   <x:tableColumns count="25">
     <x:tableColumn id="1" name="schemaVersion"/>
     <x:tableColumn id="2" name="skinId"/>
@@ -2865,44 +2921,15 @@
           <x:t xml:space="preserve">墨3体が同時に生存</x:t>
         </x:is>
       </x:c>
-      <x:c r="Q21" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TurtleShell</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R21" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">시작 방어막</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="S21" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Starting Shield</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T21" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">開幕の盾</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="U21" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">매 판 시작 시 본체에게 방어막 1개를 부여한다.
-충돌·추락을 한 번 막으며 분신에게는 적용되지 않는다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V21" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Start each run with a shield on Ink.
-Blocks one hit or fall; clones excluded.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="W21" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">毎回、本体に盾を1つ付けてスタート。
-衝突・落下を1回防ぎます。分身は対象外です。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="Q21" s="4" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="R21" s="34" t="str"/>
+      <x:c r="S21" s="34" t="str"/>
+      <x:c r="T21" s="34" t="str"/>
+      <x:c r="U21" s="34" t="str"/>
+      <x:c r="V21" s="34" t="str"/>
+      <x:c r="W21" s="34" t="str"/>
       <x:c r="X21" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -7060,8 +7087,88 @@
       </x:c>
       <x:c r="Y63" s="4" t="str"/>
     </x:row>
+    <x:row r="64" ht="76" customHeight="1">
+      <x:c r="A64" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B64" s="31" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C64" s="24" t="str">
+        <x:v>HyunmuHelm</x:v>
+      </x:c>
+      <x:c r="D64" s="27" t="str">
+        <x:v>현무의 투구</x:v>
+      </x:c>
+      <x:c r="E64" s="27" t="str">
+        <x:v>Hyunmu Helm</x:v>
+      </x:c>
+      <x:c r="F64" s="27" t="str">
+        <x:v>玄武の兜</x:v>
+      </x:c>
+      <x:c r="G64" s="26" t="str">
+        <x:v>북쪽을 지키던 등갑을 잠시 빌렸다.</x:v>
+      </x:c>
+      <x:c r="H64" s="26" t="str">
+        <x:v>A shell borrowed from the guardian of the north.</x:v>
+      </x:c>
+      <x:c r="I64" s="26" t="str">
+        <x:v>北を守る甲羅を、しばらく借りてきた。</x:v>
+      </x:c>
+      <x:c r="J64" s="24" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="K64" s="24" t="str">
+        <x:v>Clones</x:v>
+      </x:c>
+      <x:c r="L64" s="32" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M64" s="28" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="N64" s="24" t="str">
+        <x:v>먹 3마리 동시 생존</x:v>
+      </x:c>
+      <x:c r="O64" s="24" t="str">
+        <x:v>Keep 3 Inks alive together</x:v>
+      </x:c>
+      <x:c r="P64" s="24" t="str">
+        <x:v>墨3体が同時に生存</x:v>
+      </x:c>
+      <x:c r="Q64" s="24" t="str">
+        <x:v>HyunmuHelm</x:v>
+      </x:c>
+      <x:c r="R64" s="26" t="str">
+        <x:v>수호</x:v>
+      </x:c>
+      <x:c r="S64" s="26" t="str">
+        <x:v>Protection</x:v>
+      </x:c>
+      <x:c r="T64" s="26" t="str">
+        <x:v>守護</x:v>
+      </x:c>
+      <x:c r="U64" s="26" t="str">
+        <x:v>매 판 시작 시 본체에게 방어막 1개를 부여한다.
+충돌·추락을 한 번 막으며 분신에게는 적용되지 않는다.</x:v>
+      </x:c>
+      <x:c r="V64" s="26" t="str">
+        <x:v>Start each run with a shield on Ink.
+Blocks one hit or fall; clones excluded.</x:v>
+      </x:c>
+      <x:c r="W64" s="26" t="str">
+        <x:v>毎回、本体に盾を1つ付けてスタート。
+衝突・落下を1回防ぎます。分身は対象外です。</x:v>
+      </x:c>
+      <x:c r="X64" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y64" s="24" t="str">
+        <x:v>skin_hyunmu_helm_v1</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:dataValidations count="41">
+  <x:dataValidations count="42">
     <x:dataValidation type="whole" operator="between" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="L3">
       <x:formula1>1</x:formula1>
       <x:formula2>100000000</x:formula2>
@@ -7226,11 +7333,15 @@
       <x:formula1>1</x:formula1>
       <x:formula2>100000000</x:formula2>
     </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="L64">
+      <x:formula1>1</x:formula1>
+      <x:formula2>100000000</x:formula2>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0167e6691d7c441b"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb017a32cfa534c97"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4ba424915554788"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe52e1f7eeed440c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/skin-chart-20260914/먹점프_스킨_뒤끝차트_v1.xlsx
+++ b/outputs/skin-chart-20260914/먹점프_스킨_뒤끝차트_v1.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skins" sheetId="1" r:id="Rcbf59ba86a144020"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skins" sheetId="1" r:id="R312382aa90104b52"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -297,9 +297,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="200" formatCode="0"/>
-  </x:numFmts>
   <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
@@ -334,7 +331,7 @@
       <x:name val="Apple SD Gothic Neo"/>
     </x:font>
   </x:fonts>
-  <x:fills count="9">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -361,21 +358,6 @@
         <x:fgColor rgb="FF282623"/>
       </x:patternFill>
     </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF3F2EE"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF6DF"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF0C8"/>
-      </x:patternFill>
-    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -383,7 +365,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="21">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -439,44 +421,6 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="1" fontId="3" fillId="4" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -585,8 +529,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MukJumpSkinConfig" displayName="MukJumpSkinConfig" ref="A1:Y64" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:Y64"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MukJumpSkinConfig" displayName="MukJumpSkinConfig" ref="A1:Y63" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:Y63"/>
   <x:tableColumns count="25">
     <x:tableColumn id="1" name="schemaVersion"/>
     <x:tableColumn id="2" name="skinId"/>
@@ -2921,15 +2865,44 @@
           <x:t xml:space="preserve">墨3体が同時に生存</x:t>
         </x:is>
       </x:c>
-      <x:c r="Q21" s="4" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="R21" s="34" t="str"/>
-      <x:c r="S21" s="34" t="str"/>
-      <x:c r="T21" s="34" t="str"/>
-      <x:c r="U21" s="34" t="str"/>
-      <x:c r="V21" s="34" t="str"/>
-      <x:c r="W21" s="34" t="str"/>
+      <x:c r="Q21" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TurtleShell</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R21" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">시작 방어막</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="S21" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Starting Shield</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T21" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">開幕の盾</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="U21" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">매 판 시작 시 본체에게 방어막 1개를 부여한다.
+충돌·추락을 한 번 막으며 분신에게는 적용되지 않는다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="V21" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Start each run with a shield on Ink.
+Blocks one hit or fall; clones excluded.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W21" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">毎回、本体に盾を1つ付けてスタート。
+衝突・落下を1回防ぎます。分身は対象外です。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="X21" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -7087,88 +7060,8 @@
       </x:c>
       <x:c r="Y63" s="4" t="str"/>
     </x:row>
-    <x:row r="64" ht="76" customHeight="1">
-      <x:c r="A64" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B64" s="31" t="n">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C64" s="24" t="str">
-        <x:v>HyunmuHelm</x:v>
-      </x:c>
-      <x:c r="D64" s="27" t="str">
-        <x:v>현무의 투구</x:v>
-      </x:c>
-      <x:c r="E64" s="27" t="str">
-        <x:v>Hyunmu Helm</x:v>
-      </x:c>
-      <x:c r="F64" s="27" t="str">
-        <x:v>玄武の兜</x:v>
-      </x:c>
-      <x:c r="G64" s="26" t="str">
-        <x:v>북쪽을 지키던 등갑을 잠시 빌렸다.</x:v>
-      </x:c>
-      <x:c r="H64" s="26" t="str">
-        <x:v>A shell borrowed from the guardian of the north.</x:v>
-      </x:c>
-      <x:c r="I64" s="26" t="str">
-        <x:v>北を守る甲羅を、しばらく借りてきた。</x:v>
-      </x:c>
-      <x:c r="J64" s="24" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="K64" s="24" t="str">
-        <x:v>Clones</x:v>
-      </x:c>
-      <x:c r="L64" s="32" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="M64" s="28" t="str">
-        <x:v>YES</x:v>
-      </x:c>
-      <x:c r="N64" s="24" t="str">
-        <x:v>먹 3마리 동시 생존</x:v>
-      </x:c>
-      <x:c r="O64" s="24" t="str">
-        <x:v>Keep 3 Inks alive together</x:v>
-      </x:c>
-      <x:c r="P64" s="24" t="str">
-        <x:v>墨3体が同時に生存</x:v>
-      </x:c>
-      <x:c r="Q64" s="24" t="str">
-        <x:v>HyunmuHelm</x:v>
-      </x:c>
-      <x:c r="R64" s="26" t="str">
-        <x:v>수호</x:v>
-      </x:c>
-      <x:c r="S64" s="26" t="str">
-        <x:v>Protection</x:v>
-      </x:c>
-      <x:c r="T64" s="26" t="str">
-        <x:v>守護</x:v>
-      </x:c>
-      <x:c r="U64" s="26" t="str">
-        <x:v>매 판 시작 시 본체에게 방어막 1개를 부여한다.
-충돌·추락을 한 번 막으며 분신에게는 적용되지 않는다.</x:v>
-      </x:c>
-      <x:c r="V64" s="26" t="str">
-        <x:v>Start each run with a shield on Ink.
-Blocks one hit or fall; clones excluded.</x:v>
-      </x:c>
-      <x:c r="W64" s="26" t="str">
-        <x:v>毎回、本体に盾を1つ付けてスタート。
-衝突・落下を1回防ぎます。分身は対象外です。</x:v>
-      </x:c>
-      <x:c r="X64" s="33" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y64" s="24" t="str">
-        <x:v>skin_hyunmu_helm_v1</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
-  <x:dataValidations count="42">
+  <x:dataValidations count="41">
     <x:dataValidation type="whole" operator="between" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="L3">
       <x:formula1>1</x:formula1>
       <x:formula2>100000000</x:formula2>
@@ -7333,15 +7226,11 @@
       <x:formula1>1</x:formula1>
       <x:formula2>100000000</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="L64">
-      <x:formula1>1</x:formula1>
-      <x:formula2>100000000</x:formula2>
-    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb017a32cfa534c97"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0167e6691d7c441b"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe52e1f7eeed440c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4ba424915554788"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/skin-chart-20260914/먹점프_스킨_뒤끝차트_v1.xlsx
+++ b/outputs/skin-chart-20260914/먹점프_스킨_뒤끝차트_v1.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skins" sheetId="1" r:id="R312382aa90104b52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skins" sheetId="1" r:id="R00b71a91936341fc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1017,20 +1017,14 @@
           <x:t xml:space="preserve">Gat</x:t>
         </x:is>
       </x:c>
-      <x:c r="D3" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">바람 갓</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E3" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Wind Gat</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F3" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">風の笠</x:t>
-        </x:is>
+      <x:c r="D3" s="13" t="str">
+        <x:v>바람 갓</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="str">
+        <x:v>Wind Gat</x:v>
+      </x:c>
+      <x:c r="F3" s="13" t="str">
+        <x:v>風の笠</x:v>
       </x:c>
       <x:c r="G3" s="7" t="str">
         <x:v>바람처럼 스쳐가는....</x:v>
@@ -1079,20 +1073,14 @@
           <x:t xml:space="preserve">Gat</x:t>
         </x:is>
       </x:c>
-      <x:c r="R3" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">이단 도약</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="S3" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Double Jump</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T3" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">二段跳び</x:t>
-        </x:is>
+      <x:c r="R3" s="7" t="str">
+        <x:v>이단 도약</x:v>
+      </x:c>
+      <x:c r="S3" s="7" t="str">
+        <x:v>Double Jump</x:v>
+      </x:c>
+      <x:c r="T3" s="7" t="str">
+        <x:v>二段跳び</x:v>
       </x:c>
       <x:c r="U3" s="7" t="inlineStr">
         <x:is>
@@ -1133,35 +1121,23 @@
           <x:t xml:space="preserve">SpiderMask</x:t>
         </x:is>
       </x:c>
-      <x:c r="D4" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">거미탈</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Spider Mask</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F4" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">蜘蛛の面</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G4" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">이웃의 빨래줄까지 지키는 작은 영웅.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H4" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A little neighborhood hero. Even the clotheslines are safe.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I4" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ご近所の物干しロープまで守る、小さなヒーロー。</x:t>
-        </x:is>
+      <x:c r="D4" s="13" t="str">
+        <x:v>거미탈</x:v>
+      </x:c>
+      <x:c r="E4" s="13" t="str">
+        <x:v>Spider Mask</x:v>
+      </x:c>
+      <x:c r="F4" s="13" t="str">
+        <x:v>蜘蛛の面</x:v>
+      </x:c>
+      <x:c r="G4" s="7" t="str">
+        <x:v>거미에게 물린 적은 없다</x:v>
+      </x:c>
+      <x:c r="H4" s="7" t="str">
+        <x:v>Never been bitten by a spider</x:v>
+      </x:c>
+      <x:c r="I4" s="7" t="str">
+        <x:v>蜘蛛に噛まれたことはない</x:v>
       </x:c>
       <x:c r="J4" s="4" t="inlineStr">
         <x:is>
@@ -1201,20 +1177,14 @@
           <x:t xml:space="preserve">SpiderMask</x:t>
         </x:is>
       </x:c>
-      <x:c r="R4" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">거미줄 오르기</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="S4" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Web Ascent</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T4" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">糸のぼり</x:t>
-        </x:is>
+      <x:c r="R4" s="7" t="str">
+        <x:v>먹슈트</x:v>
+      </x:c>
+      <x:c r="S4" s="7" t="str">
+        <x:v>Ink Suit</x:v>
+      </x:c>
+      <x:c r="T4" s="7" t="str">
+        <x:v>墨スーツ</x:v>
       </x:c>
       <x:c r="U4" s="7" t="inlineStr">
         <x:is>
@@ -2680,35 +2650,23 @@
           <x:t xml:space="preserve">YakshaMask</x:t>
         </x:is>
       </x:c>
-      <x:c r="D20" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">각시탈</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E20" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bridal Mask</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F20" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">花嫁の面</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G20" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">탈은 웃고 있지만 주먹은 웃지 않는다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H20" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">The mask smiles. The fists do not.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I20" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">仮面は笑うが、拳は笑わない。</x:t>
-        </x:is>
+      <x:c r="D20" s="13" t="str">
+        <x:v>각시탈</x:v>
+      </x:c>
+      <x:c r="E20" s="13" t="str">
+        <x:v>Bridal Mask</x:v>
+      </x:c>
+      <x:c r="F20" s="13" t="str">
+        <x:v>花嫁の面</x:v>
+      </x:c>
+      <x:c r="G20" s="7" t="str">
+        <x:v>정체는 비밀인거같다.</x:v>
+      </x:c>
+      <x:c r="H20" s="7" t="str">
+        <x:v>Seems to keep its identity a secret.</x:v>
+      </x:c>
+      <x:c r="I20" s="7" t="str">
+        <x:v>正体は秘密らしい。</x:v>
       </x:c>
       <x:c r="J20" s="4" t="inlineStr">
         <x:is>
@@ -2748,20 +2706,14 @@
           <x:t xml:space="preserve">YakshaMask</x:t>
         </x:is>
       </x:c>
-      <x:c r="R20" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">퇴마의 일격</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="S20" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Banishing Strike</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T20" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">退魔の一撃</x:t>
-        </x:is>
+      <x:c r="R20" s="7" t="str">
+        <x:v>탈춤</x:v>
+      </x:c>
+      <x:c r="S20" s="7" t="str">
+        <x:v>Mask Dance</x:v>
+      </x:c>
+      <x:c r="T20" s="7" t="str">
+        <x:v>仮面舞</x:v>
       </x:c>
       <x:c r="U20" s="7" t="inlineStr">
         <x:is>
@@ -2802,35 +2754,23 @@
           <x:t xml:space="preserve">TurtleShell</x:t>
         </x:is>
       </x:c>
-      <x:c r="D21" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">거북 투구</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E21" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Turtle Helm</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F21" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">亀のかぶと</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G21" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">느린 장인이 끝내 완성한 투구.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H21" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A very slow craftsman finally finished it.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I21" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">のんびり屋の職人が、ついに仕上げた。</x:t>
-        </x:is>
+      <x:c r="D21" s="13" t="str">
+        <x:v>현무</x:v>
+      </x:c>
+      <x:c r="E21" s="13" t="str">
+        <x:v>Hyunmu</x:v>
+      </x:c>
+      <x:c r="F21" s="13" t="str">
+        <x:v>玄武</x:v>
+      </x:c>
+      <x:c r="G21" s="7" t="str">
+        <x:v>느린 장인이 끝내 완성한 투구.</x:v>
+      </x:c>
+      <x:c r="H21" s="7" t="str">
+        <x:v>A very slow craftsman finally finished it.</x:v>
+      </x:c>
+      <x:c r="I21" s="7" t="str">
+        <x:v>のんびり屋の職人が、ついに仕上げた。</x:v>
       </x:c>
       <x:c r="J21" s="4" t="inlineStr">
         <x:is>
@@ -2870,20 +2810,14 @@
           <x:t xml:space="preserve">TurtleShell</x:t>
         </x:is>
       </x:c>
-      <x:c r="R21" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">시작 방어막</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="S21" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Starting Shield</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T21" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">開幕の盾</x:t>
-        </x:is>
+      <x:c r="R21" s="7" t="str">
+        <x:v>금강</x:v>
+      </x:c>
+      <x:c r="S21" s="7" t="str">
+        <x:v>Vajra</x:v>
+      </x:c>
+      <x:c r="T21" s="7" t="str">
+        <x:v>金剛</x:v>
       </x:c>
       <x:c r="U21" s="7" t="inlineStr">
         <x:is>
@@ -3114,35 +3048,23 @@
           <x:t xml:space="preserve">SpiritHalo</x:t>
         </x:is>
       </x:c>
-      <x:c r="D24" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">금빛 후광</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E24" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Golden Halo</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F24" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">金色の後光</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G24" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">뒤가 환해졌지만 득도한 것은 아니다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H24" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A radiant ring. Enlightenment sold separately.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I24" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">背中は輝いたが、悟ったわけではない。</x:t>
-        </x:is>
+      <x:c r="D24" s="13" t="str">
+        <x:v>윤회의 고리</x:v>
+      </x:c>
+      <x:c r="E24" s="13" t="str">
+        <x:v>Ring of Rebirth</x:v>
+      </x:c>
+      <x:c r="F24" s="13" t="str">
+        <x:v>輪廻の環</x:v>
+      </x:c>
+      <x:c r="G24" s="7" t="str">
+        <x:v>끝은 또다른 시작</x:v>
+      </x:c>
+      <x:c r="H24" s="7" t="str">
+        <x:v>Every end is another beginning</x:v>
+      </x:c>
+      <x:c r="I24" s="7" t="str">
+        <x:v>終わりは新たな始まり</x:v>
       </x:c>
       <x:c r="J24" s="4" t="inlineStr">
         <x:is>
@@ -3182,20 +3104,14 @@
           <x:t xml:space="preserve">SpiritHalo</x:t>
         </x:is>
       </x:c>
-      <x:c r="R24" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">먹의 환원</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="S24" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ink Return</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T24" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">墨の還元</x:t>
-        </x:is>
+      <x:c r="R24" s="7" t="str">
+        <x:v>윤회</x:v>
+      </x:c>
+      <x:c r="S24" s="7" t="str">
+        <x:v>Rebirth</x:v>
+      </x:c>
+      <x:c r="T24" s="7" t="str">
+        <x:v>輪廻</x:v>
       </x:c>
       <x:c r="U24" s="7" t="inlineStr">
         <x:is>
@@ -3426,35 +3342,23 @@
           <x:t xml:space="preserve">PhoenixCrown</x:t>
         </x:is>
       </x:c>
-      <x:c r="D27" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">봉황 관</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E27" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Phoenix Crown</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F27" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">鳳凰の冠</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G27" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">타지 않은 깃은 딱 다섯 개였다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H27" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Exactly five feathers escaped the fire.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I27" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">燃え残った羽は、ちょうど五枚だった。</x:t>
-        </x:is>
+      <x:c r="D27" s="13" t="str">
+        <x:v>봉황 관</x:v>
+      </x:c>
+      <x:c r="E27" s="13" t="str">
+        <x:v>Phoenix Crown</x:v>
+      </x:c>
+      <x:c r="F27" s="13" t="str">
+        <x:v>鳳凰の冠</x:v>
+      </x:c>
+      <x:c r="G27" s="7" t="str">
+        <x:v>타지 않은 깃은 딱 다섯 개였다.</x:v>
+      </x:c>
+      <x:c r="H27" s="7" t="str">
+        <x:v>Exactly five feathers escaped the fire.</x:v>
+      </x:c>
+      <x:c r="I27" s="7" t="str">
+        <x:v>燃え残った羽は、ちょうど五枚だった。</x:v>
       </x:c>
       <x:c r="J27" s="4" t="inlineStr">
         <x:is>
@@ -3494,20 +3398,14 @@
           <x:t xml:space="preserve">PhoenixCrown</x:t>
         </x:is>
       </x:c>
-      <x:c r="R27" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">봉황의 숨결</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="S27" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Phoenix Breath</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T27" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">鳳凰の息吹</x:t>
-        </x:is>
+      <x:c r="R27" s="7" t="str">
+        <x:v>봉황의 숨결</x:v>
+      </x:c>
+      <x:c r="S27" s="7" t="str">
+        <x:v>Phoenix Breath</x:v>
+      </x:c>
+      <x:c r="T27" s="7" t="str">
+        <x:v>鳳凰の息吹</x:v>
       </x:c>
       <x:c r="U27" s="7" t="inlineStr">
         <x:is>
@@ -4688,35 +4586,23 @@
           <x:t xml:space="preserve">CloudBoots</x:t>
         </x:is>
       </x:c>
-      <x:c r="D40" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">구름 장화</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E40" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cloud Boots</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F40" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">雲の靴</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G40" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">비 오는 날엔 양말까지 구름이 된다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H40" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">On rainy days, even the socks turn to cloud.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I40" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">雨の日には、靴下まで雲になる。</x:t>
-        </x:is>
+      <x:c r="D40" s="13" t="str">
+        <x:v>구름 장화</x:v>
+      </x:c>
+      <x:c r="E40" s="13" t="str">
+        <x:v>Cloud Boots</x:v>
+      </x:c>
+      <x:c r="F40" s="13" t="str">
+        <x:v>雲の靴</x:v>
+      </x:c>
+      <x:c r="G40" s="7" t="str">
+        <x:v>비 오는 날엔 양말까지 구름이 된다.</x:v>
+      </x:c>
+      <x:c r="H40" s="7" t="str">
+        <x:v>On rainy days, even the socks turn to cloud.</x:v>
+      </x:c>
+      <x:c r="I40" s="7" t="str">
+        <x:v>雨の日には、靴下まで雲になる。</x:v>
       </x:c>
       <x:c r="J40" s="4" t="inlineStr">
         <x:is>
@@ -4756,20 +4642,14 @@
           <x:t xml:space="preserve">CloudBoots</x:t>
         </x:is>
       </x:c>
-      <x:c r="R40" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">구름 도약</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="S40" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cloud Leap</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T40" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">雲の跳躍</x:t>
-        </x:is>
+      <x:c r="R40" s="7" t="str">
+        <x:v>구름 도약</x:v>
+      </x:c>
+      <x:c r="S40" s="7" t="str">
+        <x:v>Cloud Leap</x:v>
+      </x:c>
+      <x:c r="T40" s="7" t="str">
+        <x:v>雲の跳躍</x:v>
       </x:c>
       <x:c r="U40" s="7" t="inlineStr">
         <x:is>
@@ -5095,35 +4975,23 @@
           <x:t xml:space="preserve">BondKnot</x:t>
         </x:is>
       </x:c>
-      <x:c r="D44" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">인연 매듭</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E44" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bond Knot</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F44" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">縁結び</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G44" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">인연을 묶었더니 발이 먼저 떠올랐다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H44" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">One little bond. Two feet off the ground.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I44" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">縁を結んだら、足が先に浮かんだ。</x:t>
-        </x:is>
+      <x:c r="D44" s="13" t="str">
+        <x:v>무스비</x:v>
+      </x:c>
+      <x:c r="E44" s="13" t="str">
+        <x:v>Musubi</x:v>
+      </x:c>
+      <x:c r="F44" s="13" t="str">
+        <x:v>むすび</x:v>
+      </x:c>
+      <x:c r="G44" s="7" t="str">
+        <x:v>서로 다른 시간을 하나로 묶은 매듭</x:v>
+      </x:c>
+      <x:c r="H44" s="7" t="str">
+        <x:v>A knot that binds different times together</x:v>
+      </x:c>
+      <x:c r="I44" s="7" t="str">
+        <x:v>異なる時間をひとつに結んだ結び目</x:v>
       </x:c>
       <x:c r="J44" s="4" t="inlineStr">
         <x:is>
@@ -5163,20 +5031,14 @@
           <x:t xml:space="preserve">BondKnot</x:t>
         </x:is>
       </x:c>
-      <x:c r="R44" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">첫걸음 도약</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="S44" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">First Leap</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T44" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">はじまりの跳躍</x:t>
-        </x:is>
+      <x:c r="R44" s="7" t="str">
+        <x:v>인연의 이끌림</x:v>
+      </x:c>
+      <x:c r="S44" s="7" t="str">
+        <x:v>Bond's Pull</x:v>
+      </x:c>
+      <x:c r="T44" s="7" t="str">
+        <x:v>縁の導き</x:v>
       </x:c>
       <x:c r="U44" s="7" t="inlineStr">
         <x:is>
@@ -5217,35 +5079,23 @@
           <x:t xml:space="preserve">WindFan</x:t>
         </x:is>
       </x:c>
-      <x:c r="D45" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">바람부채</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E45" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Wind Fan</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F45" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">風の扇</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G45" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">불을 끄려다 주인부터 날려 버렸다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H45" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Meant to cool the fire. Blew its owner away.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I45" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">火を消すつもりが、持ち主を飛ばした。</x:t>
-        </x:is>
+      <x:c r="D45" s="13" t="str">
+        <x:v>바람부채</x:v>
+      </x:c>
+      <x:c r="E45" s="13" t="str">
+        <x:v>Wind Fan</x:v>
+      </x:c>
+      <x:c r="F45" s="13" t="str">
+        <x:v>風の扇</x:v>
+      </x:c>
+      <x:c r="G45" s="7" t="str">
+        <x:v>부채를 펼치면, 바람의 흐름이 바뀔거같다.</x:v>
+      </x:c>
+      <x:c r="H45" s="7" t="str">
+        <x:v>Open the fan, and the wind might change its course.</x:v>
+      </x:c>
+      <x:c r="I45" s="7" t="str">
+        <x:v>扇を開けば、風の流れが変わりそうだ。</x:v>
       </x:c>
       <x:c r="J45" s="4" t="inlineStr">
         <x:is>
@@ -5285,20 +5135,14 @@
           <x:t xml:space="preserve">WindFan</x:t>
         </x:is>
       </x:c>
-      <x:c r="R45" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">바람 도약</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="S45" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Wind Leap</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T45" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">風の跳躍</x:t>
-        </x:is>
+      <x:c r="R45" s="7" t="str">
+        <x:v>바람 도약</x:v>
+      </x:c>
+      <x:c r="S45" s="7" t="str">
+        <x:v>Wind Leap</x:v>
+      </x:c>
+      <x:c r="T45" s="7" t="str">
+        <x:v>風の跳躍</x:v>
       </x:c>
       <x:c r="U45" s="7" t="inlineStr">
         <x:is>
@@ -6622,20 +6466,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N59" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">거북 투구로 아이템 없이 250m 이상 한 판 완료</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O59" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">With Turtle Helm, finish at 250m or higher without items</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P59" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">亀のかぶとでアイテムなしの250m以上プレイを完了</x:t>
-        </x:is>
+      <x:c r="N59" s="4" t="str">
+        <x:v>현무로 아이템 없이 250m 이상 한 판 완료</x:v>
+      </x:c>
+      <x:c r="O59" s="4" t="str">
+        <x:v>With Hyunmu, finish at 250m or higher without items</x:v>
+      </x:c>
+      <x:c r="P59" s="4" t="str">
+        <x:v>玄武でアイテムなしの250m以上プレイを完了</x:v>
       </x:c>
       <x:c r="Q59" s="4" t="inlineStr">
         <x:is>
@@ -6954,35 +6792,23 @@
           <x:t xml:space="preserve">AngelWings</x:t>
         </x:is>
       </x:c>
-      <x:c r="D63" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">천사링</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E63" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Angel Ring</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F63" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">天使の輪</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G63" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">하늘과 지옥 사이에서도 퇴근 시간은 지킨다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H63" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Even between heaven and hell, it clocks out on time.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I63" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">天と地獄の間でも、定時には帰る。</x:t>
-        </x:is>
+      <x:c r="D63" s="13" t="str">
+        <x:v>여명의 고리</x:v>
+      </x:c>
+      <x:c r="E63" s="13" t="str">
+        <x:v>Ring of Dawn</x:v>
+      </x:c>
+      <x:c r="F63" s="13" t="str">
+        <x:v>夜明けの環</x:v>
+      </x:c>
+      <x:c r="G63" s="7" t="str">
+        <x:v>돌아갈 곳을 잃은 빛이 먹 위에 머문다</x:v>
+      </x:c>
+      <x:c r="H63" s="7" t="str">
+        <x:v>A light with nowhere to return rests above Ink</x:v>
+      </x:c>
+      <x:c r="I63" s="7" t="str">
+        <x:v>帰る場所を失った光が、墨の上にとどまる</x:v>
       </x:c>
       <x:c r="J63" s="4" t="inlineStr">
         <x:is>
@@ -7022,20 +6848,14 @@
           <x:t xml:space="preserve">AngelWings</x:t>
         </x:is>
       </x:c>
-      <x:c r="R63" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">다시 피는 빛</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="S63" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Light Reborn</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="T63" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">よみがえる光</x:t>
-        </x:is>
+      <x:c r="R63" s="7" t="str">
+        <x:v>다시 피는 빛</x:v>
+      </x:c>
+      <x:c r="S63" s="7" t="str">
+        <x:v>Light Reborn</x:v>
+      </x:c>
+      <x:c r="T63" s="7" t="str">
+        <x:v>よみがえる光</x:v>
       </x:c>
       <x:c r="U63" s="7" t="inlineStr">
         <x:is>
@@ -7228,9 +7048,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0167e6691d7c441b"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R879ddd8bdfe048ea"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4ba424915554788"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2598efbb30c64d61"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/skin-chart-20260914/먹점프_스킨_뒤끝차트_v1.xlsx
+++ b/outputs/skin-chart-20260914/먹점프_스킨_뒤끝차트_v1.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skins" sheetId="1" r:id="R00b71a91936341fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skins" sheetId="1" r:id="R83c0a3212005417b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1430,20 +1430,14 @@
           <x:t xml:space="preserve">空っぽの墨おばけ</x:t>
         </x:is>
       </x:c>
-      <x:c r="G7" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">다 쓴 종이도 가끔 꿈을 꾼다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H7" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Even used paper dreams sometimes.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I7" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">使い終えた紙も、ときどき夢を見る。</x:t>
-        </x:is>
+      <x:c r="G7" s="7" t="str">
+        <x:v>그린 길은 밟지 않아</x:v>
+      </x:c>
+      <x:c r="H7" s="7" t="str">
+        <x:v>Drawn paths? Not stepping there</x:v>
+      </x:c>
+      <x:c r="I7" s="7" t="str">
+        <x:v>描いた道は踏まないよ</x:v>
       </x:c>
       <x:c r="J7" s="4" t="inlineStr">
         <x:is>
@@ -3841,20 +3835,14 @@
           <x:t xml:space="preserve">夜の番人</x:t>
         </x:is>
       </x:c>
-      <x:c r="G32" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">달에 신호가 뜨면, 이름 없는 지붕의 주인이 깨어난다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H32" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">When the signal reaches the moon, a nameless rooftop guardian wakes.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I32" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">月に合図が浮かぶと、名もなき屋根の守り手が目を覚ます。</x:t>
-        </x:is>
+      <x:c r="G32" s="7" t="str">
+        <x:v>로비의 세 번째 밤</x:v>
+      </x:c>
+      <x:c r="H32" s="7" t="str">
+        <x:v>The lobby's third night</x:v>
+      </x:c>
+      <x:c r="I32" s="7" t="str">
+        <x:v>ロビーの三度目の夜</x:v>
       </x:c>
       <x:c r="J32" s="4" t="inlineStr">
         <x:is>
@@ -3936,20 +3924,14 @@
           <x:t xml:space="preserve">月の旅人</x:t>
         </x:is>
       </x:c>
-      <x:c r="G33" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">달에 떡이 있는지 확인하러 간다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H33" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Off to check if the moon has rice cakes.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I33" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">月にお餅があるか、確かめに行く。</x:t>
-        </x:is>
+      <x:c r="G33" s="7" t="str">
+        <x:v>낮밤낮밤낮밤</x:v>
+      </x:c>
+      <x:c r="H33" s="7" t="str">
+        <x:v>Day, night, day, night, day, night</x:v>
+      </x:c>
+      <x:c r="I33" s="7" t="str">
+        <x:v>昼夜昼夜昼夜</x:v>
       </x:c>
       <x:c r="J33" s="4" t="inlineStr">
         <x:is>
@@ -4031,20 +4013,14 @@
           <x:t xml:space="preserve">ぜんまい猫</x:t>
         </x:is>
       </x:c>
-      <x:c r="G34" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">태엽을 감으면 오히려 잠이 든다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H34" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Winding it up only puts it to sleep.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I34" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ぜんまいを巻くと、かえって眠くなる。</x:t>
-        </x:is>
+      <x:c r="G34" s="7" t="str">
+        <x:v>밤고양이는 60초째 빈손</x:v>
+      </x:c>
+      <x:c r="H34" s="7" t="str">
+        <x:v>Night cat, empty paws for 60s</x:v>
+      </x:c>
+      <x:c r="I34" s="7" t="str">
+        <x:v>夜の猫、60秒ずっと手ぶら</x:v>
       </x:c>
       <x:c r="J34" s="4" t="inlineStr">
         <x:is>
@@ -4126,20 +4102,14 @@
           <x:t xml:space="preserve">七つ目の目</x:t>
         </x:is>
       </x:c>
-      <x:c r="G35" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">일곱 번째 눈은 굴린 먹만 보인다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H35" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Only the roller can see the seventh face.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I35" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">七つ目の目は、振った墨にしか見えない。</x:t>
-        </x:is>
+      <x:c r="G35" s="7" t="str">
+        <x:v>딱 777이 좋아</x:v>
+      </x:c>
+      <x:c r="H35" s="7" t="str">
+        <x:v>Exactly 777, please</x:v>
+      </x:c>
+      <x:c r="I35" s="7" t="str">
+        <x:v>ぴったり777が好き</x:v>
       </x:c>
       <x:c r="J35" s="4" t="inlineStr">
         <x:is>
@@ -5293,20 +5263,14 @@
           <x:t xml:space="preserve">夜ねずみの丸い耳</x:t>
         </x:is>
       </x:c>
-      <x:c r="G47" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">달 뜨면 벼루 창고가 한 칸 빈다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H47" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Moon up. One shelf of ink goes missing.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I47" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">月が出ると、硯の棚がひとつ空く。</x:t>
-        </x:is>
+      <x:c r="G47" s="7" t="str">
+        <x:v>밤참 세 개, 50만큼</x:v>
+      </x:c>
+      <x:c r="H47" s="7" t="str">
+        <x:v>Three night snacks, up to 50</x:v>
+      </x:c>
+      <x:c r="I47" s="7" t="str">
+        <x:v>夜食は三つ、50まで</x:v>
       </x:c>
       <x:c r="J47" s="4" t="inlineStr">
         <x:is>
@@ -5388,20 +5352,14 @@
           <x:t xml:space="preserve">野牛の角</x:t>
         </x:is>
       </x:c>
-      <x:c r="G48" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">서두르지 않았는데 제일 먼저 왔다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H48" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Never hurried. Arrived first anyway.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I48" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">急がなかったのに、いちばん乗り。</x:t>
-        </x:is>
+      <x:c r="G48" s="7" t="str">
+        <x:v>스무 번 꾹꾹, 일 분 버티기</x:v>
+      </x:c>
+      <x:c r="H48" s="7" t="str">
+        <x:v>Twenty firm steps, one minute</x:v>
+      </x:c>
+      <x:c r="I48" s="7" t="str">
+        <x:v>二十回ふみふみ、一分がまん</x:v>
       </x:c>
       <x:c r="J48" s="4" t="inlineStr">
         <x:is>
@@ -5483,20 +5441,14 @@
           <x:t xml:space="preserve">山守虎の縞ずきん</x:t>
         </x:is>
       </x:c>
-      <x:c r="G49" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">아직 포효보다 하품이 더 크다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H49" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Its yawn is still louder than its roar.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I49" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">雄叫びより、あくびの方が大きい。</x:t>
-        </x:is>
+      <x:c r="G49" s="7" t="str">
+        <x:v>밤사냥은 빈손으로</x:v>
+      </x:c>
+      <x:c r="H49" s="7" t="str">
+        <x:v>Night hunting, empty-handed</x:v>
+      </x:c>
+      <x:c r="I49" s="7" t="str">
+        <x:v>夜の狩りは手ぶらで</x:v>
       </x:c>
       <x:c r="J49" s="4" t="inlineStr">
         <x:is>
@@ -5578,20 +5530,14 @@
           <x:t xml:space="preserve">月うさぎの折れ耳</x:t>
         </x:is>
       </x:c>
-      <x:c r="G50" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">떡은 두고 귀만 빌려 왔다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H50" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Left the rice cakes. Borrowed the ears.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I50" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">お餅は置いて、耳だけ借りてきた。</x:t>
-        </x:is>
+      <x:c r="G50" s="7" t="str">
+        <x:v>달을 쓰고 밤길 200</x:v>
+      </x:c>
+      <x:c r="H50" s="7" t="str">
+        <x:v>Wear the moon, climb 200 at night</x:v>
+      </x:c>
+      <x:c r="I50" s="7" t="str">
+        <x:v>月をかぶって、夜道を200</x:v>
       </x:c>
       <x:c r="J50" s="4" t="inlineStr">
         <x:is>
@@ -5673,20 +5619,14 @@
           <x:t xml:space="preserve">ちび竜の芽ぶく角</x:t>
         </x:is>
       </x:c>
-      <x:c r="G51" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">승천 연습은 낮잠 다음에.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H51" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ascension practice comes after a nap.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I51" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">昇天の練習は、お昼寝のあと。</x:t>
-        </x:is>
+      <x:c r="G51" s="7" t="str">
+        <x:v>꼬리 달고 300까지</x:v>
+      </x:c>
+      <x:c r="H51" s="7" t="str">
+        <x:v>Tail on, up to 300</x:v>
+      </x:c>
+      <x:c r="I51" s="7" t="str">
+        <x:v>しっぽをつけて300まで</x:v>
       </x:c>
       <x:c r="J51" s="4" t="inlineStr">
         <x:is>
@@ -5768,20 +5708,14 @@
           <x:t xml:space="preserve">小へびのゆる結び</x:t>
         </x:is>
       </x:c>
-      <x:c r="G52" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">리본인 줄 알고 묶을 뻔했다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H52" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Almost tied it. Thought it was a ribbon.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I52" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">リボンと思って、結ぶところだった。</x:t>
-        </x:is>
+      <x:c r="G52" s="7" t="str">
+        <x:v>거미는 열두 번 콩콩</x:v>
+      </x:c>
+      <x:c r="H52" s="7" t="str">
+        <x:v>The spider hops twelve times</x:v>
+      </x:c>
+      <x:c r="I52" s="7" t="str">
+        <x:v>蜘蛛は十二回ぴょんぴょん</x:v>
       </x:c>
       <x:c r="J52" s="4" t="inlineStr">
         <x:is>
@@ -5863,20 +5797,14 @@
           <x:t xml:space="preserve">風馬のなびくたてがみ</x:t>
         </x:is>
       </x:c>
-      <x:c r="G53" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">발굽 대신 바람 소리만 남겼다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H53" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Left a breeze instead of hoofprints.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I53" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ひづめの跡の代わりに、風の音。</x:t>
-        </x:is>
+      <x:c r="G53" s="7" t="str">
+        <x:v>300까지 일 분이면 돼</x:v>
+      </x:c>
+      <x:c r="H53" s="7" t="str">
+        <x:v>One minute to finish at 300</x:v>
+      </x:c>
+      <x:c r="I53" s="7" t="str">
+        <x:v>300まで、一分あればいい</x:v>
       </x:c>
       <x:c r="J53" s="4" t="inlineStr">
         <x:is>
@@ -5958,20 +5886,14 @@
           <x:t xml:space="preserve">山羊の巻き角</x:t>
         </x:is>
       </x:c>
-      <x:c r="G54" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">산길은 곧게 걷고, 뿔만 둥글게 말았다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H54" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Walked the mountain trail straight. Only the horns took a turn.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I54" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">山道はまっすぐ歩いた。巻いたのは角だけ。</x:t>
-        </x:is>
+      <x:c r="G54" s="7" t="str">
+        <x:v>서른 번 딛고 200까지</x:v>
+      </x:c>
+      <x:c r="H54" s="7" t="str">
+        <x:v>Thirty steps, up to 200</x:v>
+      </x:c>
+      <x:c r="I54" s="7" t="str">
+        <x:v>三十回ふんで200まで</x:v>
       </x:c>
       <x:c r="J54" s="4" t="inlineStr">
         <x:is>
@@ -6053,20 +5975,14 @@
           <x:t xml:space="preserve">猿のしっぽ</x:t>
         </x:is>
       </x:c>
-      <x:c r="G55" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">손이 모자라면 꼬리부터 내민다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H55" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Short a hand? The tail volunteers first.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I55" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">手が足りなければ、しっぽが先に伸びる。</x:t>
-        </x:is>
+      <x:c r="G55" s="7" t="str">
+        <x:v>셋이서 간식 다섯 개</x:v>
+      </x:c>
+      <x:c r="H55" s="7" t="str">
+        <x:v>Three friends, five snacks</x:v>
+      </x:c>
+      <x:c r="I55" s="7" t="str">
+        <x:v>三人でおやつ五つ</x:v>
       </x:c>
       <x:c r="J55" s="4" t="inlineStr">
         <x:is>
@@ -6148,20 +6064,14 @@
           <x:t xml:space="preserve">朝どりの赤いとさか</x:t>
         </x:is>
       </x:c>
-      <x:c r="G56" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">해보다 조금 늦게 일어난다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H56" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Wakes just a little after the sun.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I56" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">お日さまより、少し寝坊する。</x:t>
-        </x:is>
+      <x:c r="G56" s="7" t="str">
+        <x:v>해 뜨면 먹방울 셋</x:v>
+      </x:c>
+      <x:c r="H56" s="7" t="str">
+        <x:v>Sun's up, three Ink Drops</x:v>
+      </x:c>
+      <x:c r="I56" s="7" t="str">
+        <x:v>日が出たら墨滴三つ</x:v>
       </x:c>
       <x:c r="J56" s="4" t="inlineStr">
         <x:is>
@@ -6243,20 +6153,14 @@
           <x:t xml:space="preserve">見守り犬のたれ耳</x:t>
         </x:is>
       </x:c>
-      <x:c r="G57" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">문 대신 친구의 그림자를 지킨다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H57" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Guards a friend's shadow, not a gate.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I57" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">門ではなく、友だちの影を守る。</x:t>
-        </x:is>
+      <x:c r="G57" s="7" t="str">
+        <x:v>둘이서 일 분 반</x:v>
+      </x:c>
+      <x:c r="H57" s="7" t="str">
+        <x:v>Two friends, a minute and a half</x:v>
+      </x:c>
+      <x:c r="I57" s="7" t="str">
+        <x:v>二人で一分半</x:v>
       </x:c>
       <x:c r="J57" s="4" t="inlineStr">
         <x:is>
@@ -6338,20 +6242,14 @@
           <x:t xml:space="preserve">福ぶたの鼻</x:t>
         </x:is>
       </x:c>
-      <x:c r="G58" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">복을 불렀더니 간식도 왔다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H58" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Called for luck. Snacks came too.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I58" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">福を呼んだら、おやつも来た。</x:t>
-        </x:is>
+      <x:c r="G58" s="7" t="str">
+        <x:v>열둘 먹고 꿀꿀</x:v>
+      </x:c>
+      <x:c r="H58" s="7" t="str">
+        <x:v>Twelve treats, oink oink</x:v>
+      </x:c>
+      <x:c r="I58" s="7" t="str">
+        <x:v>十二個食べて、ぶうぶう</x:v>
       </x:c>
       <x:c r="J58" s="4" t="inlineStr">
         <x:is>
@@ -6433,20 +6331,14 @@
           <x:t xml:space="preserve">ヘテの小さな角</x:t>
         </x:is>
       </x:c>
-      <x:c r="G59" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">나쁜 꿈만 콕 찌르는 작은 뿔.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H59" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A tiny horn for poking bad dreams away.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I59" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悪い夢だけ、ちくりと追い払う角。</x:t>
-        </x:is>
+      <x:c r="G59" s="7" t="str">
+        <x:v>현무는 250까지 빈손</x:v>
+      </x:c>
+      <x:c r="H59" s="7" t="str">
+        <x:v>Hyunmu goes to 250 empty-handed</x:v>
+      </x:c>
+      <x:c r="I59" s="7" t="str">
+        <x:v>玄武は250まで手ぶら</x:v>
       </x:c>
       <x:c r="J59" s="4" t="inlineStr">
         <x:is>
@@ -6522,20 +6414,14 @@
           <x:t xml:space="preserve">三足烏の太陽</x:t>
         </x:is>
       </x:c>
-      <x:c r="G60" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">세 발로도 아침엔 자꾸 헛디딘다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H60" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Three feet. Still stumbles in the morning.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I60" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">三本足でも、朝はつまずく。</x:t>
-        </x:is>
+      <x:c r="G60" s="7" t="str">
+        <x:v>밤에는 셋셋셋</x:v>
+      </x:c>
+      <x:c r="H60" s="7" t="str">
+        <x:v>Three-three-three by night</x:v>
+      </x:c>
+      <x:c r="I60" s="7" t="str">
+        <x:v>夜は三・三・三</x:v>
       </x:c>
       <x:c r="J60" s="4" t="inlineStr">
         <x:is>
@@ -6617,20 +6503,14 @@
           <x:t xml:space="preserve">九尾のしっぽ</x:t>
         </x:is>
       </x:c>
-      <x:c r="G61" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">꼬리는 아홉인데, 속마음은 하나도 안 보인다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H61" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Nine tails. Not a single clue what it is thinking.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I61" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">尾は九つ。心の内はひとつも見えない。</x:t>
-        </x:is>
+      <x:c r="G61" s="7" t="str">
+        <x:v>여우 셋이서 300까지</x:v>
+      </x:c>
+      <x:c r="H61" s="7" t="str">
+        <x:v>Three foxes, up to 300</x:v>
+      </x:c>
+      <x:c r="I61" s="7" t="str">
+        <x:v>三匹の狐で300まで</x:v>
       </x:c>
       <x:c r="J61" s="4" t="inlineStr">
         <x:is>
@@ -6712,20 +6592,14 @@
           <x:t xml:space="preserve">8番ボール</x:t>
         </x:is>
       </x:c>
-      <x:c r="G62" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">큐대는 못 잡아도, 각은 제법 잘 본다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H62" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Can't hold a cue. Can still work the angles.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I62" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">キューは持てないが、角度を読むのは得意。</x:t>
-        </x:is>
+      <x:c r="G62" s="7" t="str">
+        <x:v>한 번 던져, 벽에 세 번</x:v>
+      </x:c>
+      <x:c r="H62" s="7" t="str">
+        <x:v>One toss, three wall bounces</x:v>
+      </x:c>
+      <x:c r="I62" s="7" t="str">
+        <x:v>一度投げて、壁に三回</x:v>
       </x:c>
       <x:c r="J62" s="4" t="inlineStr">
         <x:is>
@@ -7048,9 +6922,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R879ddd8bdfe048ea"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc07b293c9de94684"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2598efbb30c64d61"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2caebedf0fd34a76"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/skin-chart-20260914/먹점프_스킨_뒤끝차트_v1.xlsx
+++ b/outputs/skin-chart-20260914/먹점프_스킨_뒤끝차트_v1.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skins" sheetId="1" r:id="R83c0a3212005417b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skins" sheetId="1" r:id="R9718f936902d4aa0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1225,35 +1225,23 @@
           <x:t xml:space="preserve">FirstRibbon</x:t>
         </x:is>
       </x:c>
-      <x:c r="D5" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">첫 먹매듭</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">First Knot</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">はじめの墨結び</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">풀 줄 몰라서 아직 첫 매듭이다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Still the first knot. Nobody can untie it.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ほどけないので、まだ最初の結び目。</x:t>
-        </x:is>
+      <x:c r="D5" s="13" t="str">
+        <x:v>먹매듭</x:v>
+      </x:c>
+      <x:c r="E5" s="13" t="str">
+        <x:v>Ink Knot</x:v>
+      </x:c>
+      <x:c r="F5" s="13" t="str">
+        <x:v>墨結び</x:v>
+      </x:c>
+      <x:c r="G5" s="7" t="str">
+        <x:v>처음 묶은 모양 그대로.</x:v>
+      </x:c>
+      <x:c r="H5" s="7" t="str">
+        <x:v>Still tied as it was the first day.</x:v>
+      </x:c>
+      <x:c r="I5" s="7" t="str">
+        <x:v>初めて結んだ、そのままの形。</x:v>
       </x:c>
       <x:c r="J5" s="4" t="inlineStr">
         <x:is>
@@ -1320,35 +1308,23 @@
           <x:t xml:space="preserve">Scholar</x:t>
         </x:is>
       </x:c>
-      <x:c r="D6" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">선비 관</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E6" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Scholar Cap</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F6" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">書生の冠</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G6" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">붓보다 낮잠에 더 익숙한 선비의 관.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H6" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Its scholar preferred naps to calligraphy.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I6" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">書より昼寝が得意な書生の冠。</x:t>
-        </x:is>
+      <x:c r="D6" s="13" t="str">
+        <x:v>선비 관</x:v>
+      </x:c>
+      <x:c r="E6" s="13" t="str">
+        <x:v>Scholar Cap</x:v>
+      </x:c>
+      <x:c r="F6" s="13" t="str">
+        <x:v>書生の冠</x:v>
+      </x:c>
+      <x:c r="G6" s="7" t="str">
+        <x:v>벼슬보다 바람이 잘 통한다.</x:v>
+      </x:c>
+      <x:c r="H6" s="7" t="str">
+        <x:v>Better for catching a breeze than gaining rank.</x:v>
+      </x:c>
+      <x:c r="I6" s="7" t="str">
+        <x:v>出世よりも風通しがいい。</x:v>
       </x:c>
       <x:c r="J6" s="4" t="inlineStr">
         <x:is>
@@ -1415,20 +1391,14 @@
           <x:t xml:space="preserve">InkGhost</x:t>
         </x:is>
       </x:c>
-      <x:c r="D7" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">빈 먹 유령</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E7" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Blank Ghost</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F7" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">空っぽの墨おばけ</x:t>
-        </x:is>
+      <x:c r="D7" s="13" t="str">
+        <x:v>먹유령</x:v>
+      </x:c>
+      <x:c r="E7" s="13" t="str">
+        <x:v>Ink Ghost</x:v>
+      </x:c>
+      <x:c r="F7" s="13" t="str">
+        <x:v>墨の幽霊</x:v>
       </x:c>
       <x:c r="G7" s="7" t="str">
         <x:v>그린 길은 밟지 않아</x:v>
@@ -1694,35 +1664,23 @@
           <x:t xml:space="preserve">LotusCrown</x:t>
         </x:is>
       </x:c>
-      <x:c r="D10" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">연꽃 관</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E10" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lotus Crown</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F10" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">蓮の冠</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G10" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">연못지기가 잃어버린 작은 왕관.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H10" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">The pond keeper's missing little crown.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I10" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">池の番人がなくした小さな冠。</x:t>
-        </x:is>
+      <x:c r="D10" s="13" t="str">
+        <x:v>연꽃 관</x:v>
+      </x:c>
+      <x:c r="E10" s="13" t="str">
+        <x:v>Lotus Crown</x:v>
+      </x:c>
+      <x:c r="F10" s="13" t="str">
+        <x:v>蓮の冠</x:v>
+      </x:c>
+      <x:c r="G10" s="7" t="str">
+        <x:v>물 위에 남은 꽃 한 송이.</x:v>
+      </x:c>
+      <x:c r="H10" s="7" t="str">
+        <x:v>A single blossom left on the water.</x:v>
+      </x:c>
+      <x:c r="I10" s="7" t="str">
+        <x:v>水面に残った一輪の花。</x:v>
       </x:c>
       <x:c r="J10" s="4" t="inlineStr">
         <x:is>
@@ -1884,35 +1842,23 @@
           <x:t xml:space="preserve">BellRibbon</x:t>
         </x:is>
       </x:c>
-      <x:c r="D12" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">방울 매듭</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E12" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bell Knot</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F12" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">鈴結び</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G12" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">소리가 안 나서 도둑이 탐냈다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H12" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A thief coveted this silent bell.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I12" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">音がしないので、泥棒が欲しがった。</x:t>
-        </x:is>
+      <x:c r="D12" s="13" t="str">
+        <x:v>방울 매듭</x:v>
+      </x:c>
+      <x:c r="E12" s="13" t="str">
+        <x:v>Bell Knot</x:v>
+      </x:c>
+      <x:c r="F12" s="13" t="str">
+        <x:v>鈴結び</x:v>
+      </x:c>
+      <x:c r="G12" s="7" t="str">
+        <x:v>소리 없이 흔들리는 방울.</x:v>
+      </x:c>
+      <x:c r="H12" s="7" t="str">
+        <x:v>A bell that sways without a sound.</x:v>
+      </x:c>
+      <x:c r="I12" s="7" t="str">
+        <x:v>音もなく揺れる鈴。</x:v>
       </x:c>
       <x:c r="J12" s="4" t="inlineStr">
         <x:is>
@@ -1979,35 +1925,23 @@
           <x:t xml:space="preserve">CloudCap</x:t>
         </x:is>
       </x:c>
-      <x:c r="D13" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">구름 두건</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E13" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cloud Hood</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F13" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">雲の頭巾</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G13" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">구름 한 조각을 말렸더니 줄어들었다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H13" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">One cloud, shrunk in the wash.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I13" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">雲をひとかけ洗ったら、縮んだ。</x:t>
-        </x:is>
+      <x:c r="D13" s="13" t="str">
+        <x:v>구름 두건</x:v>
+      </x:c>
+      <x:c r="E13" s="13" t="str">
+        <x:v>Cloud Hood</x:v>
+      </x:c>
+      <x:c r="F13" s="13" t="str">
+        <x:v>雲の頭巾</x:v>
+      </x:c>
+      <x:c r="G13" s="7" t="str">
+        <x:v>잠시 머물다 갈 구름 한 조각.</x:v>
+      </x:c>
+      <x:c r="H13" s="7" t="str">
+        <x:v>A passing cloud, resting for a while.</x:v>
+      </x:c>
+      <x:c r="I13" s="7" t="str">
+        <x:v>しばらく留まる、一片の雲。</x:v>
       </x:c>
       <x:c r="J13" s="4" t="inlineStr">
         <x:is>
@@ -2074,35 +2008,23 @@
           <x:t xml:space="preserve">PaperBoat</x:t>
         </x:is>
       </x:c>
-      <x:c r="D14" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">종이배 모자</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E14" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Paper Boat</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F14" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">紙舟の帽子</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G14" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">강 대신 머리 위를 항해하기로 했다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H14" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">It chose a head over the open river.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I14" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">川ではなく、頭の上を旅することにした。</x:t>
-        </x:is>
+      <x:c r="D14" s="13" t="str">
+        <x:v>종이배</x:v>
+      </x:c>
+      <x:c r="E14" s="13" t="str">
+        <x:v>Paper Boat</x:v>
+      </x:c>
+      <x:c r="F14" s="13" t="str">
+        <x:v>紙の舟</x:v>
+      </x:c>
+      <x:c r="G14" s="7" t="str">
+        <x:v>아직 물에 띄운 적은 없다.</x:v>
+      </x:c>
+      <x:c r="H14" s="7" t="str">
+        <x:v>It has never touched the water.</x:v>
+      </x:c>
+      <x:c r="I14" s="7" t="str">
+        <x:v>まだ水に浮かべたことはない。</x:v>
       </x:c>
       <x:c r="J14" s="4" t="inlineStr">
         <x:is>
@@ -2169,35 +2091,23 @@
           <x:t xml:space="preserve">TeaCupHat</x:t>
         </x:is>
       </x:c>
-      <x:c r="D15" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">찻잔 모자</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E15" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tea Cup Hat</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F15" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">湯のみ帽</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G15" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">차는 식었지만 고집은 따뜻하다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H15" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">The tea is cold. The stubbornness is warm.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I15" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">お茶は冷めても、意地はまだ温かい。</x:t>
-        </x:is>
+      <x:c r="D15" s="13" t="str">
+        <x:v>찻잔</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="str">
+        <x:v>Teacup</x:v>
+      </x:c>
+      <x:c r="F15" s="13" t="str">
+        <x:v>茶碗</x:v>
+      </x:c>
+      <x:c r="G15" s="7" t="str">
+        <x:v>차는 식었고 향은 남았다.</x:v>
+      </x:c>
+      <x:c r="H15" s="7" t="str">
+        <x:v>The tea has cooled. Its scent remains.</x:v>
+      </x:c>
+      <x:c r="I15" s="7" t="str">
+        <x:v>茶は冷め、香りが残った。</x:v>
       </x:c>
       <x:c r="J15" s="4" t="inlineStr">
         <x:is>
@@ -2264,35 +2174,23 @@
           <x:t xml:space="preserve">FeatherHairpin</x:t>
         </x:is>
       </x:c>
-      <x:c r="D16" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">깃털 비녀</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E16" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Feather Pin</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F16" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">羽のかんざし</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G16" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">학은 빠진 깃 하나를 아직 찾고 있다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H16" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A crane is still looking for this feather.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I16" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">鶴はまだ、この羽を探している。</x:t>
-        </x:is>
+      <x:c r="D16" s="13" t="str">
+        <x:v>깃털 비녀</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="str">
+        <x:v>Feather Pin</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="str">
+        <x:v>羽のかんざし</x:v>
+      </x:c>
+      <x:c r="G16" s="7" t="str">
+        <x:v>주인 모를 깃 하나를 꽂았다.</x:v>
+      </x:c>
+      <x:c r="H16" s="7" t="str">
+        <x:v>A feather left behind, worn as a pin.</x:v>
+      </x:c>
+      <x:c r="I16" s="7" t="str">
+        <x:v>持ち主の知れない羽を一本、挿した。</x:v>
       </x:c>
       <x:c r="J16" s="4" t="inlineStr">
         <x:is>
@@ -2454,35 +2352,23 @@
           <x:t xml:space="preserve">FoxMask</x:t>
         </x:is>
       </x:c>
-      <x:c r="D18" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">여우탈</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E18" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fox Mask</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F18" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">狐の面</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G18" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">속인 건 아무도 없고, 본인만 신났다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H18" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fooled nobody. Had a wonderful time.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I18" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">誰もだませず、自分だけ大喜び。</x:t>
-        </x:is>
+      <x:c r="D18" s="13" t="str">
+        <x:v>여우탈</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="str">
+        <x:v>Fox Mask</x:v>
+      </x:c>
+      <x:c r="F18" s="13" t="str">
+        <x:v>狐の面</x:v>
+      </x:c>
+      <x:c r="G18" s="7" t="str">
+        <x:v>웃는 얼굴 뒤는 알 수 없다.</x:v>
+      </x:c>
+      <x:c r="H18" s="7" t="str">
+        <x:v>No telling what lies behind the smile.</x:v>
+      </x:c>
+      <x:c r="I18" s="7" t="str">
+        <x:v>笑顔の裏はわからない。</x:v>
       </x:c>
       <x:c r="J18" s="4" t="inlineStr">
         <x:is>
@@ -2549,35 +2435,23 @@
           <x:t xml:space="preserve">CraneCrest</x:t>
         </x:is>
       </x:c>
-      <x:c r="D19" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">학의 볏</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E19" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Crane Crest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F19" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">鶴の冠</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G19" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">높이 날던 학도 빗질은 서툴렀다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H19" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A fine flier. A terrible hairdresser.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I19" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">高く飛ぶ鶴も、髪を整えるのは苦手。</x:t>
-        </x:is>
+      <x:c r="D19" s="13" t="str">
+        <x:v>학깃</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="str">
+        <x:v>Crane Plume</x:v>
+      </x:c>
+      <x:c r="F19" s="13" t="str">
+        <x:v>鶴の羽飾り</x:v>
+      </x:c>
+      <x:c r="G19" s="7" t="str">
+        <x:v>날개에서 떨어져 여기까지 왔다.</x:v>
+      </x:c>
+      <x:c r="H19" s="7" t="str">
+        <x:v>Shed from a wing, it drifted this far.</x:v>
+      </x:c>
+      <x:c r="I19" s="7" t="str">
+        <x:v>翼を離れ、ここまで流れ着いた。</x:v>
       </x:c>
       <x:c r="J19" s="4" t="inlineStr">
         <x:is>
@@ -2852,35 +2726,23 @@
           <x:t xml:space="preserve">MoonCrown</x:t>
         </x:is>
       </x:c>
-      <x:c r="D22" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">달빛 관</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E22" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Moon Crown</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F22" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">月光の冠</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G22" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">달에서 빌렸다. 반납일은 모른다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H22" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Borrowed from the moon. No due date.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I22" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">月から借りた。返す日は知らない。</x:t>
-        </x:is>
+      <x:c r="D22" s="13" t="str">
+        <x:v>달빛 관</x:v>
+      </x:c>
+      <x:c r="E22" s="13" t="str">
+        <x:v>Moon Crown</x:v>
+      </x:c>
+      <x:c r="F22" s="13" t="str">
+        <x:v>月光の冠</x:v>
+      </x:c>
+      <x:c r="G22" s="7" t="str">
+        <x:v>기울지 않는 초승달.</x:v>
+      </x:c>
+      <x:c r="H22" s="7" t="str">
+        <x:v>A crescent that never wanes.</x:v>
+      </x:c>
+      <x:c r="I22" s="7" t="str">
+        <x:v>欠けることのない三日月。</x:v>
       </x:c>
       <x:c r="J22" s="4" t="inlineStr">
         <x:is>
@@ -2947,35 +2809,23 @@
           <x:t xml:space="preserve">BrushMaster</x:t>
         </x:is>
       </x:c>
-      <x:c r="D23" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">붓 장인</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E23" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Brush Master</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F23" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">筆の匠</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G23" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">장인은 붓을 찾고, 붓은 여기 있다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H23" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">The master is looking for these brushes.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I23" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">職人は筆を探している。筆はここにある。</x:t>
-        </x:is>
+      <x:c r="D23" s="13" t="str">
+        <x:v>쌍붓</x:v>
+      </x:c>
+      <x:c r="E23" s="13" t="str">
+        <x:v>Twin Brushes</x:v>
+      </x:c>
+      <x:c r="F23" s="13" t="str">
+        <x:v>二本の筆</x:v>
+      </x:c>
+      <x:c r="G23" s="7" t="str">
+        <x:v>붓을 쥘 손이 없어 머리에 꽂았다.</x:v>
+      </x:c>
+      <x:c r="H23" s="7" t="str">
+        <x:v>No hands to hold them, so here they rest.</x:v>
+      </x:c>
+      <x:c r="I23" s="7" t="str">
+        <x:v>筆を持つ手がないので、頭に挿した。</x:v>
       </x:c>
       <x:c r="J23" s="4" t="inlineStr">
         <x:is>
@@ -3241,35 +3091,23 @@
           <x:t xml:space="preserve">JadeCrown</x:t>
         </x:is>
       </x:c>
-      <x:c r="D26" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">비취 용관</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E26" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Jade Crown</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F26" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">翡翠の竜冠</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G26" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">돌인 줄 알고 문을 괴어 두던 용관.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H26" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Once mistaken for a very good doorstop.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I26" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ただの石だと思われ、戸止めにされていた。</x:t>
-        </x:is>
+      <x:c r="D26" s="13" t="str">
+        <x:v>옥관</x:v>
+      </x:c>
+      <x:c r="E26" s="13" t="str">
+        <x:v>Jade Crown</x:v>
+      </x:c>
+      <x:c r="F26" s="13" t="str">
+        <x:v>玉冠</x:v>
+      </x:c>
+      <x:c r="G26" s="7" t="str">
+        <x:v>오래된 옥에 빛이 남아 있다.</x:v>
+      </x:c>
+      <x:c r="H26" s="7" t="str">
+        <x:v>A trace of light remains in the old jade.</x:v>
+      </x:c>
+      <x:c r="I26" s="7" t="str">
+        <x:v>古い玉に、光が残っている。</x:v>
       </x:c>
       <x:c r="J26" s="4" t="inlineStr">
         <x:is>
@@ -3440,35 +3278,23 @@
           <x:t xml:space="preserve">TigerMask</x:t>
         </x:is>
       </x:c>
-      <x:c r="D28" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">산군 탈</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E28" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tiger Mask</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F28" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">山の虎面</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G28" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">산군도 가끔은 귀여워 보이고 싶다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H28" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Even a mountain tiger wants to look cute.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I28" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">山の虎も、たまには可愛く見られたい。</x:t>
-        </x:is>
+      <x:c r="D28" s="13" t="str">
+        <x:v>산군 탈</x:v>
+      </x:c>
+      <x:c r="E28" s="13" t="str">
+        <x:v>Tiger Mask</x:v>
+      </x:c>
+      <x:c r="F28" s="13" t="str">
+        <x:v>山の虎面</x:v>
+      </x:c>
+      <x:c r="G28" s="7" t="str">
+        <x:v>눈을 마주치면 먼저 피하게 된다.</x:v>
+      </x:c>
+      <x:c r="H28" s="7" t="str">
+        <x:v>Meet its eyes, and you look away first.</x:v>
+      </x:c>
+      <x:c r="I28" s="7" t="str">
+        <x:v>目が合うと、こちらが先にそらす。</x:v>
       </x:c>
       <x:c r="J28" s="4" t="inlineStr">
         <x:is>
@@ -3535,35 +3361,23 @@
           <x:t xml:space="preserve">MountainKing</x:t>
         </x:is>
       </x:c>
-      <x:c r="D29" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">산왕 관</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E29" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mountain Crown</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F29" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">山王の冠</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G29" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">산꼭대기에 먼저 앉은 먹의 왕관.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H29" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Crown of the first Ink to sit on the summit.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I29" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">山頂に一番乗りした墨の冠。</x:t>
-        </x:is>
+      <x:c r="D29" s="13" t="str">
+        <x:v>산왕 관</x:v>
+      </x:c>
+      <x:c r="E29" s="13" t="str">
+        <x:v>Mountain Crown</x:v>
+      </x:c>
+      <x:c r="F29" s="13" t="str">
+        <x:v>山王の冠</x:v>
+      </x:c>
+      <x:c r="G29" s="7" t="str">
+        <x:v>산을 내려온 뒤에도 벗지 않았다.</x:v>
+      </x:c>
+      <x:c r="H29" s="7" t="str">
+        <x:v>Kept on, even after leaving the mountain.</x:v>
+      </x:c>
+      <x:c r="I29" s="7" t="str">
+        <x:v>山を下りてからも、脱がなかった。</x:v>
       </x:c>
       <x:c r="J29" s="4" t="inlineStr">
         <x:is>
@@ -3630,35 +3444,23 @@
           <x:t xml:space="preserve">CloudDragon</x:t>
         </x:is>
       </x:c>
-      <x:c r="D30" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">구름 용</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E30" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cloud Dragon</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F30" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">雲の竜</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G30" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">승천 연습은 아직 구름 속에서만.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H30" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Still practicing ascension inside a cloud.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I30" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">昇天の練習は、まだ雲の中だけ。</x:t>
-        </x:is>
+      <x:c r="D30" s="13" t="str">
+        <x:v>운룡</x:v>
+      </x:c>
+      <x:c r="E30" s="13" t="str">
+        <x:v>Cloud Dragon</x:v>
+      </x:c>
+      <x:c r="F30" s="13" t="str">
+        <x:v>雲竜</x:v>
+      </x:c>
+      <x:c r="G30" s="7" t="str">
+        <x:v>구름 사이로 뿔이 드러난다.</x:v>
+      </x:c>
+      <x:c r="H30" s="7" t="str">
+        <x:v>Horns emerge between the clouds.</x:v>
+      </x:c>
+      <x:c r="I30" s="7" t="str">
+        <x:v>雲の間から角がのぞく。</x:v>
       </x:c>
       <x:c r="J30" s="4" t="inlineStr">
         <x:is>
@@ -3725,35 +3527,23 @@
           <x:t xml:space="preserve">InkMecha</x:t>
         </x:is>
       </x:c>
-      <x:c r="D31" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">먹빛 기갑</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E31" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ink Mecha</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F31" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">墨の機甲</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G31" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">대장간의 실패작. 종이로는 첫 성공작.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H31" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Failed in iron. A triumph in cardboard.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I31" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">鉄では失敗作。紙では初の成功作。</x:t>
-        </x:is>
+      <x:c r="D31" s="13" t="str">
+        <x:v>철가면</x:v>
+      </x:c>
+      <x:c r="E31" s="13" t="str">
+        <x:v>Iron Mask</x:v>
+      </x:c>
+      <x:c r="F31" s="13" t="str">
+        <x:v>鉄仮面</x:v>
+      </x:c>
+      <x:c r="G31" s="7" t="str">
+        <x:v>차가운 겉모습 안에는 같은 먹이 있다.</x:v>
+      </x:c>
+      <x:c r="H31" s="7" t="str">
+        <x:v>The same Ink beneath a cold exterior.</x:v>
+      </x:c>
+      <x:c r="I31" s="7" t="str">
+        <x:v>冷たい外見の奥には、いつもの墨がいる。</x:v>
       </x:c>
       <x:c r="J31" s="4" t="inlineStr">
         <x:is>
@@ -4271,35 +4061,23 @@
           <x:t xml:space="preserve">CraneWings</x:t>
         </x:is>
       </x:c>
-      <x:c r="D37" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">학의 날개</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E37" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Crane Wings</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F37" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">鶴の翼</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G37" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">빌린 날개라 깃털은 돌려줘야 한다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H37" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Borrowed wings. Please return every feather.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I37" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">借りた翼なので、羽は全部返すこと。</x:t>
-        </x:is>
+      <x:c r="D37" s="13" t="str">
+        <x:v>학의 날개</x:v>
+      </x:c>
+      <x:c r="E37" s="13" t="str">
+        <x:v>Crane Wings</x:v>
+      </x:c>
+      <x:c r="F37" s="13" t="str">
+        <x:v>鶴の翼</x:v>
+      </x:c>
+      <x:c r="G37" s="7" t="str">
+        <x:v>접어 두었던 날개를 펼친다.</x:v>
+      </x:c>
+      <x:c r="H37" s="7" t="str">
+        <x:v>Wings, folded until now, open.</x:v>
+      </x:c>
+      <x:c r="I37" s="7" t="str">
+        <x:v>畳んでいた翼を広げる。</x:v>
       </x:c>
       <x:c r="J37" s="4" t="inlineStr">
         <x:is>
@@ -4366,35 +4144,23 @@
           <x:t xml:space="preserve">ButterflyWings</x:t>
         </x:is>
       </x:c>
-      <x:c r="D38" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">먹나비 날개</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E38" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ink Butterfly</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F38" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">墨蝶の羽</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G38" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">먹이 묻은 줄 모르고 날아온 나비.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H38" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A butterfly unaware of its ink stains.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I38" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">墨がついたとも知らず、飛んできた蝶。</x:t>
-        </x:is>
+      <x:c r="D38" s="13" t="str">
+        <x:v>먹나비</x:v>
+      </x:c>
+      <x:c r="E38" s="13" t="str">
+        <x:v>Ink Butterfly</x:v>
+      </x:c>
+      <x:c r="F38" s="13" t="str">
+        <x:v>墨の蝶</x:v>
+      </x:c>
+      <x:c r="G38" s="7" t="str">
+        <x:v>먹이 묻은 줄 모르고 날아온 나비.</x:v>
+      </x:c>
+      <x:c r="H38" s="7" t="str">
+        <x:v>A butterfly unaware of its ink stains.</x:v>
+      </x:c>
+      <x:c r="I38" s="7" t="str">
+        <x:v>墨がついたとも知らず、飛んできた蝶。</x:v>
       </x:c>
       <x:c r="J38" s="4" t="inlineStr">
         <x:is>
@@ -4660,35 +4426,23 @@
           <x:t xml:space="preserve">BlueWisps</x:t>
         </x:is>
       </x:c>
-      <x:c r="D41" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">도깨비불 나들이</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E41" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Wisp Parade</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F41" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">鬼火のおさんぽ</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G41" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">무섭게 따라오려다 산책이 되어 버렸다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H41" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">They meant to haunt you. It turned into a stroll.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I41" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">脅かすつもりが、おさんぽになった。</x:t>
-        </x:is>
+      <x:c r="D41" s="13" t="str">
+        <x:v>도깨비불</x:v>
+      </x:c>
+      <x:c r="E41" s="13" t="str">
+        <x:v>Ghostfire</x:v>
+      </x:c>
+      <x:c r="F41" s="13" t="str">
+        <x:v>鬼火</x:v>
+      </x:c>
+      <x:c r="G41" s="7" t="str">
+        <x:v>바람이 없어도 불은 흔들린다.</x:v>
+      </x:c>
+      <x:c r="H41" s="7" t="str">
+        <x:v>The flames stir without a breeze.</x:v>
+      </x:c>
+      <x:c r="I41" s="7" t="str">
+        <x:v>風がなくても、火は揺れる。</x:v>
       </x:c>
       <x:c r="J41" s="4" t="inlineStr">
         <x:is>
@@ -4755,35 +4509,23 @@
           <x:t xml:space="preserve">PaperLanterns</x:t>
         </x:is>
       </x:c>
-      <x:c r="D42" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">길 잃은 등불</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E42" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Wandering Lanterns</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F42" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">迷子の灯り</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G42" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">집으로 가는 길은 모르지만 일단 따라온다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H42" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">They forgot the way home, so they follow you.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I42" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">帰り道は忘れたけれど、とりあえずついてくる。</x:t>
-        </x:is>
+      <x:c r="D42" s="13" t="str">
+        <x:v>길 잃은 등불</x:v>
+      </x:c>
+      <x:c r="E42" s="13" t="str">
+        <x:v>Wandering Lanterns</x:v>
+      </x:c>
+      <x:c r="F42" s="13" t="str">
+        <x:v>迷子の灯り</x:v>
+      </x:c>
+      <x:c r="G42" s="7" t="str">
+        <x:v>어디로 가는지도 모르고 따라온다.</x:v>
+      </x:c>
+      <x:c r="H42" s="7" t="str">
+        <x:v>They follow without knowing the way.</x:v>
+      </x:c>
+      <x:c r="I42" s="7" t="str">
+        <x:v>行き先も知らずについてくる。</x:v>
       </x:c>
       <x:c r="J42" s="4" t="inlineStr">
         <x:is>
@@ -4850,35 +4592,23 @@
           <x:t xml:space="preserve">MoonClouds</x:t>
         </x:is>
       </x:c>
-      <x:c r="D43" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">달구름 둥지</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E43" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mooncloud Nest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F43" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">月雲の巣</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G43" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">달이 낮잠 잘 자리를 잘못 골랐다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H43" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">The moon picked the wrong place for a nap.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I43" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">月がお昼寝する場所を間違えた。</x:t>
-        </x:is>
+      <x:c r="D43" s="13" t="str">
+        <x:v>달구름</x:v>
+      </x:c>
+      <x:c r="E43" s="13" t="str">
+        <x:v>Mooncloud</x:v>
+      </x:c>
+      <x:c r="F43" s="13" t="str">
+        <x:v>月雲</x:v>
+      </x:c>
+      <x:c r="G43" s="7" t="str">
+        <x:v>구름에 가려도 달은 남아 있다.</x:v>
+      </x:c>
+      <x:c r="H43" s="7" t="str">
+        <x:v>The moon remains behind the clouds.</x:v>
+      </x:c>
+      <x:c r="I43" s="7" t="str">
+        <x:v>雲に隠れても、月はそこにある。</x:v>
       </x:c>
       <x:c r="J43" s="4" t="inlineStr">
         <x:is>
@@ -5153,35 +4883,23 @@
           <x:t xml:space="preserve">DragonTail</x:t>
         </x:is>
       </x:c>
-      <x:c r="D46" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">용꼬리</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E46" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dragon Tail</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F46" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">竜のしっぽ</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G46" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">한 번 부딪혔을 뿐인데 꼬리가 따라왔다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H46" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">One little bump. A tail followed me home.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I46" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">一度ぶつかっただけなのに、しっぽがついてきた。</x:t>
-        </x:is>
+      <x:c r="D46" s="13" t="str">
+        <x:v>용꼬리</x:v>
+      </x:c>
+      <x:c r="E46" s="13" t="str">
+        <x:v>Dragon Tail</x:v>
+      </x:c>
+      <x:c r="F46" s="13" t="str">
+        <x:v>竜のしっぽ</x:v>
+      </x:c>
+      <x:c r="G46" s="7" t="str">
+        <x:v>스쳐 간 용이 흔적을 남겼다.</x:v>
+      </x:c>
+      <x:c r="H46" s="7" t="str">
+        <x:v>A passing dragon left its mark.</x:v>
+      </x:c>
+      <x:c r="I46" s="7" t="str">
+        <x:v>通り過ぎた竜が、跡を残した。</x:v>
       </x:c>
       <x:c r="J46" s="4" t="inlineStr">
         <x:is>
@@ -5248,20 +4966,14 @@
           <x:t xml:space="preserve">ZodiacRat</x:t>
         </x:is>
       </x:c>
-      <x:c r="D47" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">밤쥐의 동그란 귀</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E47" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Night Mouse's Round Ears</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F47" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">夜ねずみの丸い耳</x:t>
-        </x:is>
+      <x:c r="D47" s="13" t="str">
+        <x:v>밤쥐</x:v>
+      </x:c>
+      <x:c r="E47" s="13" t="str">
+        <x:v>Night Mouse</x:v>
+      </x:c>
+      <x:c r="F47" s="13" t="str">
+        <x:v>夜ねずみ</x:v>
       </x:c>
       <x:c r="G47" s="7" t="str">
         <x:v>밤참 세 개, 50만큼</x:v>
@@ -5337,29 +5049,23 @@
           <x:t xml:space="preserve">ZodiacOx</x:t>
         </x:is>
       </x:c>
-      <x:c r="D48" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">들소의 뿔</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E48" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bison Horns</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F48" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">野牛の角</x:t>
-        </x:is>
+      <x:c r="D48" s="13" t="str">
+        <x:v>황소</x:v>
+      </x:c>
+      <x:c r="E48" s="13" t="str">
+        <x:v>Bull</x:v>
+      </x:c>
+      <x:c r="F48" s="13" t="str">
+        <x:v>雄牛</x:v>
       </x:c>
       <x:c r="G48" s="7" t="str">
-        <x:v>스무 번 꾹꾹, 일 분 버티기</x:v>
+        <x:v>스무 번 딛고, 일 분 버티기</x:v>
       </x:c>
       <x:c r="H48" s="7" t="str">
-        <x:v>Twenty firm steps, one minute</x:v>
+        <x:v>Twenty landings, one minute</x:v>
       </x:c>
       <x:c r="I48" s="7" t="str">
-        <x:v>二十回ふみふみ、一分がまん</x:v>
+        <x:v>二十回着地して、一分耐える</x:v>
       </x:c>
       <x:c r="J48" s="4" t="inlineStr">
         <x:is>
@@ -5426,20 +5132,14 @@
           <x:t xml:space="preserve">ZodiacTiger</x:t>
         </x:is>
       </x:c>
-      <x:c r="D49" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">산군의 줄무늬 두건</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E49" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tiger's Striped Wrap</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F49" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">山守虎の縞ずきん</x:t>
-        </x:is>
+      <x:c r="D49" s="13" t="str">
+        <x:v>호피 두건</x:v>
+      </x:c>
+      <x:c r="E49" s="13" t="str">
+        <x:v>Tiger Bandana</x:v>
+      </x:c>
+      <x:c r="F49" s="13" t="str">
+        <x:v>虎柄の頭巾</x:v>
       </x:c>
       <x:c r="G49" s="7" t="str">
         <x:v>밤사냥은 빈손으로</x:v>
@@ -5515,20 +5215,14 @@
           <x:t xml:space="preserve">ZodiacRabbit</x:t>
         </x:is>
       </x:c>
-      <x:c r="D50" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">달토끼의 접힌 귀</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E50" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Folded Moonrabbit Ears</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F50" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">月うさぎの折れ耳</x:t>
-        </x:is>
+      <x:c r="D50" s="13" t="str">
+        <x:v>달토끼</x:v>
+      </x:c>
+      <x:c r="E50" s="13" t="str">
+        <x:v>Moon Rabbit</x:v>
+      </x:c>
+      <x:c r="F50" s="13" t="str">
+        <x:v>月兎</x:v>
       </x:c>
       <x:c r="G50" s="7" t="str">
         <x:v>달을 쓰고 밤길 200</x:v>
@@ -5604,20 +5298,14 @@
           <x:t xml:space="preserve">ZodiacDragon</x:t>
         </x:is>
       </x:c>
-      <x:c r="D51" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">꼬마 용의 새싹 뿔</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E51" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Sprouting Dragon Horns</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F51" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ちび竜の芽ぶく角</x:t>
-        </x:is>
+      <x:c r="D51" s="13" t="str">
+        <x:v>용각</x:v>
+      </x:c>
+      <x:c r="E51" s="13" t="str">
+        <x:v>Dragon Horns</x:v>
+      </x:c>
+      <x:c r="F51" s="13" t="str">
+        <x:v>竜角</x:v>
       </x:c>
       <x:c r="G51" s="7" t="str">
         <x:v>꼬리 달고 300까지</x:v>
@@ -5693,29 +5381,23 @@
           <x:t xml:space="preserve">ZodiacSnake</x:t>
         </x:is>
       </x:c>
-      <x:c r="D52" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">실뱀의 느슨한 매듭</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E52" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Little Snake's Loose Knot</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F52" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">小へびのゆる結び</x:t>
-        </x:is>
+      <x:c r="D52" s="13" t="str">
+        <x:v>뱀 매듭</x:v>
+      </x:c>
+      <x:c r="E52" s="13" t="str">
+        <x:v>Serpent Knot</x:v>
+      </x:c>
+      <x:c r="F52" s="13" t="str">
+        <x:v>蛇の結び目</x:v>
       </x:c>
       <x:c r="G52" s="7" t="str">
-        <x:v>거미는 열두 번 콩콩</x:v>
+        <x:v>거미의 열두 번째 착지</x:v>
       </x:c>
       <x:c r="H52" s="7" t="str">
-        <x:v>The spider hops twelve times</x:v>
+        <x:v>The spider's twelfth landing</x:v>
       </x:c>
       <x:c r="I52" s="7" t="str">
-        <x:v>蜘蛛は十二回ぴょんぴょん</x:v>
+        <x:v>蜘蛛の十二回目の着地</x:v>
       </x:c>
       <x:c r="J52" s="4" t="inlineStr">
         <x:is>
@@ -5782,20 +5464,14 @@
           <x:t xml:space="preserve">ZodiacHorse</x:t>
         </x:is>
       </x:c>
-      <x:c r="D53" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">바람말의 흩날린 갈기</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E53" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Wind Horse's Tousled Mane</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F53" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">風馬のなびくたてがみ</x:t>
-        </x:is>
+      <x:c r="D53" s="13" t="str">
+        <x:v>갈기</x:v>
+      </x:c>
+      <x:c r="E53" s="13" t="str">
+        <x:v>Mane</x:v>
+      </x:c>
+      <x:c r="F53" s="13" t="str">
+        <x:v>たてがみ</x:v>
       </x:c>
       <x:c r="G53" s="7" t="str">
         <x:v>300까지 일 분이면 돼</x:v>
@@ -5871,20 +5547,14 @@
           <x:t xml:space="preserve">ZodiacGoat</x:t>
         </x:is>
       </x:c>
-      <x:c r="D54" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">산양의 굽은 뿔</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E54" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Curled Ram Horns</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F54" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">山羊の巻き角</x:t>
-        </x:is>
+      <x:c r="D54" s="13" t="str">
+        <x:v>산양</x:v>
+      </x:c>
+      <x:c r="E54" s="13" t="str">
+        <x:v>Mountain Goat</x:v>
+      </x:c>
+      <x:c r="F54" s="13" t="str">
+        <x:v>山羊</x:v>
       </x:c>
       <x:c r="G54" s="7" t="str">
         <x:v>서른 번 딛고 200까지</x:v>
@@ -6049,20 +5719,14 @@
           <x:t xml:space="preserve">ZodiacRooster</x:t>
         </x:is>
       </x:c>
-      <x:c r="D56" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">새벽닭의 붉은 볏</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E56" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dawn Rooster's Red Comb</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F56" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">朝どりの赤いとさか</x:t>
-        </x:is>
+      <x:c r="D56" s="13" t="str">
+        <x:v>닭벼슬</x:v>
+      </x:c>
+      <x:c r="E56" s="13" t="str">
+        <x:v>Rooster Comb</x:v>
+      </x:c>
+      <x:c r="F56" s="13" t="str">
+        <x:v>とさか</x:v>
       </x:c>
       <x:c r="G56" s="7" t="str">
         <x:v>해 뜨면 먹방울 셋</x:v>
@@ -6138,20 +5802,14 @@
           <x:t xml:space="preserve">ZodiacDog</x:t>
         </x:is>
       </x:c>
-      <x:c r="D57" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">지킴개의 늘어진 귀</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E57" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Guardian Dog's Floppy Ears</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F57" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">見守り犬のたれ耳</x:t>
-        </x:is>
+      <x:c r="D57" s="13" t="str">
+        <x:v>사냥개</x:v>
+      </x:c>
+      <x:c r="E57" s="13" t="str">
+        <x:v>Hound</x:v>
+      </x:c>
+      <x:c r="F57" s="13" t="str">
+        <x:v>猟犬</x:v>
       </x:c>
       <x:c r="G57" s="7" t="str">
         <x:v>둘이서 일 분 반</x:v>
@@ -6227,29 +5885,23 @@
           <x:t xml:space="preserve">ZodiacPig</x:t>
         </x:is>
       </x:c>
-      <x:c r="D58" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">복돼지 코</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E58" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Lucky Pig Snout</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F58" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">福ぶたの鼻</x:t>
-        </x:is>
+      <x:c r="D58" s="13" t="str">
+        <x:v>돼지코</x:v>
+      </x:c>
+      <x:c r="E58" s="13" t="str">
+        <x:v>Pig Snout</x:v>
+      </x:c>
+      <x:c r="F58" s="13" t="str">
+        <x:v>豚の鼻</x:v>
       </x:c>
       <x:c r="G58" s="7" t="str">
-        <x:v>열둘 먹고 꿀꿀</x:v>
+        <x:v>열두 개도 모자라</x:v>
       </x:c>
       <x:c r="H58" s="7" t="str">
-        <x:v>Twelve treats, oink oink</x:v>
+        <x:v>Twelve is not enough</x:v>
       </x:c>
       <x:c r="I58" s="7" t="str">
-        <x:v>十二個食べて、ぶうぶう</x:v>
+        <x:v>十二個でも足りない</x:v>
       </x:c>
       <x:c r="J58" s="4" t="inlineStr">
         <x:is>
@@ -6399,20 +6051,14 @@
           <x:t xml:space="preserve">ThreeLeggedCrow</x:t>
         </x:is>
       </x:c>
-      <x:c r="D60" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">삼족오의 해</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E60" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Three-Legged Sun Crow</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F60" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">三足烏の太陽</x:t>
-        </x:is>
+      <x:c r="D60" s="13" t="str">
+        <x:v>삼족오</x:v>
+      </x:c>
+      <x:c r="E60" s="13" t="str">
+        <x:v>Three-Legged Crow</x:v>
+      </x:c>
+      <x:c r="F60" s="13" t="str">
+        <x:v>三足烏</x:v>
       </x:c>
       <x:c r="G60" s="7" t="str">
         <x:v>밤에는 셋셋셋</x:v>
@@ -6488,20 +6134,14 @@
           <x:t xml:space="preserve">NineTails</x:t>
         </x:is>
       </x:c>
-      <x:c r="D61" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">구미호 꼬리</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E61" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Nine Fox Tails</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F61" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九尾のしっぽ</x:t>
-        </x:is>
+      <x:c r="D61" s="13" t="str">
+        <x:v>구미호</x:v>
+      </x:c>
+      <x:c r="E61" s="13" t="str">
+        <x:v>Nine-Tailed Fox</x:v>
+      </x:c>
+      <x:c r="F61" s="13" t="str">
+        <x:v>九尾の狐</x:v>
       </x:c>
       <x:c r="G61" s="7" t="str">
         <x:v>여우 셋이서 300까지</x:v>
@@ -6922,9 +6562,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc07b293c9de94684"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re72ea5d673c540de"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2caebedf0fd34a76"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b71c314de3e4450"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/skin-chart-20260914/먹점프_스킨_뒤끝차트_v1.xlsx
+++ b/outputs/skin-chart-20260914/먹점프_스킨_뒤끝차트_v1.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skins" sheetId="1" r:id="R9718f936902d4aa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skins" sheetId="1" r:id="Rcc0d6700e6e7441c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -941,20 +941,14 @@
           <x:t xml:space="preserve">墨</x:t>
         </x:is>
       </x:c>
-      <x:c r="G2" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">벼루 밖으로 처음 굴러 나온 날.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H2" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">The day a drop rolled out of the inkstone.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I2" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">硯の外へ、はじめて転がり出た日。</x:t>
-        </x:is>
+      <x:c r="G2" s="7" t="str">
+        <x:v>벼루 밖으로 처음 굴러 나온 날</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="str">
+        <x:v>The day a drop rolled out of the inkstone</x:v>
+      </x:c>
+      <x:c r="I2" s="7" t="str">
+        <x:v>硯の外へ、はじめて転がり出た日</x:v>
       </x:c>
       <x:c r="J2" s="4" t="inlineStr">
         <x:is>
@@ -997,9 +991,9 @@
       <x:c r="R2" s="8" t="str"/>
       <x:c r="S2" s="8" t="str"/>
       <x:c r="T2" s="8" t="str"/>
-      <x:c r="U2" s="8" t="str"/>
-      <x:c r="V2" s="8" t="str"/>
-      <x:c r="W2" s="8" t="str"/>
+      <x:c r="U2" s="8"/>
+      <x:c r="V2" s="8"/>
+      <x:c r="W2" s="8"/>
       <x:c r="X2" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1082,23 +1076,17 @@
       <x:c r="T3" s="7" t="str">
         <x:v>二段跳び</x:v>
       </x:c>
-      <x:c r="U3" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">점프 정점에서 한 번 더 도약한다.
-첫 도약의 40% 힘으로 자동 발동한다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V3" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Leap again near the top of each jump.
-Automatic, at 40% of the first jump's speed.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="W3" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">跳躍の頂点付近でもう一度ジャンプ。
-最初の40%の速さで自動発動します。</x:t>
-        </x:is>
+      <x:c r="U3" s="7" t="str">
+        <x:v>점프 정점에서 한 번 더 도약한다
+첫 도약의 40% 힘으로 자동 발동한다</x:v>
+      </x:c>
+      <x:c r="V3" s="7" t="str">
+        <x:v>Leap again near the top of each jump
+Automatic, at 40% of the first jump's speed</x:v>
+      </x:c>
+      <x:c r="W3" s="7" t="str">
+        <x:v>跳躍の頂点付近でもう一度ジャンプ
+最初の40%の速さで自動発動します</x:v>
       </x:c>
       <x:c r="X3" s="18" t="n">
         <x:v>0</x:v>
@@ -1186,23 +1174,17 @@
       <x:c r="T4" s="7" t="str">
         <x:v>墨スーツ</x:v>
       </x:c>
-      <x:c r="U4" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">{cooldown}초마다 가까운 벽에 거미줄을 쏘아 본체를 18m 끌어올린다.
-상승 중에는 피해를 막으며 다른 점프 효과가 발동하면 줄을 놓는다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V4" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Every {cooldown} seconds, a web pulls the original Ink 18m toward a nearby wall.
-Blocks damage during ascent. Another launch effect releases the web.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="W4" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">{cooldown}秒ごとに近くの壁へ糸を放ち、本体を18m引き上げる。
-上昇中はダメージを防ぎ、別の跳躍効果が発動すると糸を離す。</x:t>
-        </x:is>
+      <x:c r="U4" s="7" t="str">
+        <x:v>{cooldown}초마다 가까운 벽에 거미줄을 쏘아 본체를 18m 끌어올린다
+상승 중에는 피해를 막으며 다른 점프 효과가 발동하면 줄을 놓는다</x:v>
+      </x:c>
+      <x:c r="V4" s="7" t="str">
+        <x:v>Every {cooldown} seconds, a web pulls the original Ink 18m toward a nearby wall
+Blocks damage during ascent Another launch effect releases the web</x:v>
+      </x:c>
+      <x:c r="W4" s="7" t="str">
+        <x:v>{cooldown}秒ごとに近くの壁へ糸を放ち、本体を18m引き上げる
+上昇中はダメージを防ぎ、別の跳躍効果が発動すると糸を離す</x:v>
       </x:c>
       <x:c r="X4" s="20" t="n">
         <x:v>30</x:v>
@@ -1235,13 +1217,13 @@
         <x:v>墨結び</x:v>
       </x:c>
       <x:c r="G5" s="7" t="str">
-        <x:v>처음 묶은 모양 그대로.</x:v>
+        <x:v>처음 묶은 모양 그대로</x:v>
       </x:c>
       <x:c r="H5" s="7" t="str">
-        <x:v>Still tied as it was the first day.</x:v>
+        <x:v>Still tied as it was the first day</x:v>
       </x:c>
       <x:c r="I5" s="7" t="str">
-        <x:v>初めて結んだ、そのままの形。</x:v>
+        <x:v>初めて結んだ、そのままの形</x:v>
       </x:c>
       <x:c r="J5" s="4" t="inlineStr">
         <x:is>
@@ -1284,9 +1266,9 @@
       <x:c r="R5" s="8" t="str"/>
       <x:c r="S5" s="8" t="str"/>
       <x:c r="T5" s="8" t="str"/>
-      <x:c r="U5" s="8" t="str"/>
-      <x:c r="V5" s="8" t="str"/>
-      <x:c r="W5" s="8" t="str"/>
+      <x:c r="U5" s="8"/>
+      <x:c r="V5" s="8"/>
+      <x:c r="W5" s="8"/>
       <x:c r="X5" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1318,13 +1300,13 @@
         <x:v>書生の冠</x:v>
       </x:c>
       <x:c r="G6" s="7" t="str">
-        <x:v>벼슬보다 바람이 잘 통한다.</x:v>
+        <x:v>벼슬보다 바람이 잘 통한다</x:v>
       </x:c>
       <x:c r="H6" s="7" t="str">
-        <x:v>Better for catching a breeze than gaining rank.</x:v>
+        <x:v>Better for catching a breeze than gaining rank</x:v>
       </x:c>
       <x:c r="I6" s="7" t="str">
-        <x:v>出世よりも風通しがいい。</x:v>
+        <x:v>出世よりも風通しがいい</x:v>
       </x:c>
       <x:c r="J6" s="4" t="inlineStr">
         <x:is>
@@ -1367,9 +1349,9 @@
       <x:c r="R6" s="8" t="str"/>
       <x:c r="S6" s="8" t="str"/>
       <x:c r="T6" s="8" t="str"/>
-      <x:c r="U6" s="8" t="str"/>
-      <x:c r="V6" s="8" t="str"/>
-      <x:c r="W6" s="8" t="str"/>
+      <x:c r="U6" s="8"/>
+      <x:c r="V6" s="8"/>
+      <x:c r="W6" s="8"/>
       <x:c r="X6" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1450,9 +1432,9 @@
       <x:c r="R7" s="8" t="str"/>
       <x:c r="S7" s="8" t="str"/>
       <x:c r="T7" s="8" t="str"/>
-      <x:c r="U7" s="8" t="str"/>
-      <x:c r="V7" s="8" t="str"/>
-      <x:c r="W7" s="8" t="str"/>
+      <x:c r="U7" s="8"/>
+      <x:c r="V7" s="8"/>
+      <x:c r="W7" s="8"/>
       <x:c r="X7" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1489,20 +1471,14 @@
           <x:t xml:space="preserve">竹笠</x:t>
         </x:is>
       </x:c>
-      <x:c r="G8" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">비는 막아도 먹 번짐은 못 막는다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H8" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Keeps out rain. Ink stains, not so much.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I8" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">雨は防げても、墨のにじみは防げない。</x:t>
-        </x:is>
+      <x:c r="G8" s="7" t="str">
+        <x:v>비는 막아도 먹 번짐은 못 막는다</x:v>
+      </x:c>
+      <x:c r="H8" s="7" t="str">
+        <x:v>Keeps out rain Ink stains, not so much</x:v>
+      </x:c>
+      <x:c r="I8" s="7" t="str">
+        <x:v>雨は防げても、墨のにじみは防げない</x:v>
       </x:c>
       <x:c r="J8" s="4" t="inlineStr">
         <x:is>
@@ -1545,9 +1521,9 @@
       <x:c r="R8" s="8" t="str"/>
       <x:c r="S8" s="8" t="str"/>
       <x:c r="T8" s="8" t="str"/>
-      <x:c r="U8" s="8" t="str"/>
-      <x:c r="V8" s="8" t="str"/>
-      <x:c r="W8" s="8" t="str"/>
+      <x:c r="U8" s="8"/>
+      <x:c r="V8" s="8"/>
+      <x:c r="W8" s="8"/>
       <x:c r="X8" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1584,20 +1560,14 @@
           <x:t xml:space="preserve">修行の鉢巻</x:t>
         </x:is>
       </x:c>
-      <x:c r="G9" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">백 번 넘어져도 매듭은 그대로였다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H9" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A hundred falls. The knot held firm.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I9" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">百回転んでも、結び目はそのまま。</x:t>
-        </x:is>
+      <x:c r="G9" s="7" t="str">
+        <x:v>백 번 넘어져도 매듭은 그대로였다</x:v>
+      </x:c>
+      <x:c r="H9" s="7" t="str">
+        <x:v>A hundred falls The knot held firm</x:v>
+      </x:c>
+      <x:c r="I9" s="7" t="str">
+        <x:v>百回転んでも、結び目はそのまま</x:v>
       </x:c>
       <x:c r="J9" s="4" t="inlineStr">
         <x:is>
@@ -1640,9 +1610,9 @@
       <x:c r="R9" s="8" t="str"/>
       <x:c r="S9" s="8" t="str"/>
       <x:c r="T9" s="8" t="str"/>
-      <x:c r="U9" s="8" t="str"/>
-      <x:c r="V9" s="8" t="str"/>
-      <x:c r="W9" s="8" t="str"/>
+      <x:c r="U9" s="8"/>
+      <x:c r="V9" s="8"/>
+      <x:c r="W9" s="8"/>
       <x:c r="X9" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1674,13 +1644,13 @@
         <x:v>蓮の冠</x:v>
       </x:c>
       <x:c r="G10" s="7" t="str">
-        <x:v>물 위에 남은 꽃 한 송이.</x:v>
+        <x:v>물 위에 남은 꽃 한 송이</x:v>
       </x:c>
       <x:c r="H10" s="7" t="str">
-        <x:v>A single blossom left on the water.</x:v>
+        <x:v>A single blossom left on the water</x:v>
       </x:c>
       <x:c r="I10" s="7" t="str">
-        <x:v>水面に残った一輪の花。</x:v>
+        <x:v>水面に残った一輪の花</x:v>
       </x:c>
       <x:c r="J10" s="4" t="inlineStr">
         <x:is>
@@ -1723,9 +1693,9 @@
       <x:c r="R10" s="8" t="str"/>
       <x:c r="S10" s="8" t="str"/>
       <x:c r="T10" s="8" t="str"/>
-      <x:c r="U10" s="8" t="str"/>
-      <x:c r="V10" s="8" t="str"/>
-      <x:c r="W10" s="8" t="str"/>
+      <x:c r="U10" s="8"/>
+      <x:c r="V10" s="8"/>
+      <x:c r="W10" s="8"/>
       <x:c r="X10" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1762,20 +1732,14 @@
           <x:t xml:space="preserve">猫耳</x:t>
         </x:is>
       </x:c>
-      <x:c r="G11" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">생선 냄새가 나면 살짝 기울어진다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H11" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tilts ever so slightly toward fish.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I11" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">魚の匂いがすると、少し傾く。</x:t>
-        </x:is>
+      <x:c r="G11" s="7" t="str">
+        <x:v>생선 냄새가 나면 살짝 기울어진다</x:v>
+      </x:c>
+      <x:c r="H11" s="7" t="str">
+        <x:v>Tilts ever so slightly toward fish</x:v>
+      </x:c>
+      <x:c r="I11" s="7" t="str">
+        <x:v>魚の匂いがすると、少し傾く</x:v>
       </x:c>
       <x:c r="J11" s="4" t="inlineStr">
         <x:is>
@@ -1818,9 +1782,9 @@
       <x:c r="R11" s="8" t="str"/>
       <x:c r="S11" s="8" t="str"/>
       <x:c r="T11" s="8" t="str"/>
-      <x:c r="U11" s="8" t="str"/>
-      <x:c r="V11" s="8" t="str"/>
-      <x:c r="W11" s="8" t="str"/>
+      <x:c r="U11" s="8"/>
+      <x:c r="V11" s="8"/>
+      <x:c r="W11" s="8"/>
       <x:c r="X11" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1852,13 +1816,13 @@
         <x:v>鈴結び</x:v>
       </x:c>
       <x:c r="G12" s="7" t="str">
-        <x:v>소리 없이 흔들리는 방울.</x:v>
+        <x:v>소리 없이 흔들리는 방울</x:v>
       </x:c>
       <x:c r="H12" s="7" t="str">
-        <x:v>A bell that sways without a sound.</x:v>
+        <x:v>A bell that sways without a sound</x:v>
       </x:c>
       <x:c r="I12" s="7" t="str">
-        <x:v>音もなく揺れる鈴。</x:v>
+        <x:v>音もなく揺れる鈴</x:v>
       </x:c>
       <x:c r="J12" s="4" t="inlineStr">
         <x:is>
@@ -1901,9 +1865,9 @@
       <x:c r="R12" s="8" t="str"/>
       <x:c r="S12" s="8" t="str"/>
       <x:c r="T12" s="8" t="str"/>
-      <x:c r="U12" s="8" t="str"/>
-      <x:c r="V12" s="8" t="str"/>
-      <x:c r="W12" s="8" t="str"/>
+      <x:c r="U12" s="8"/>
+      <x:c r="V12" s="8"/>
+      <x:c r="W12" s="8"/>
       <x:c r="X12" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1935,13 +1899,13 @@
         <x:v>雲の頭巾</x:v>
       </x:c>
       <x:c r="G13" s="7" t="str">
-        <x:v>잠시 머물다 갈 구름 한 조각.</x:v>
+        <x:v>잠시 머물다 갈 구름 한 조각</x:v>
       </x:c>
       <x:c r="H13" s="7" t="str">
-        <x:v>A passing cloud, resting for a while.</x:v>
+        <x:v>A passing cloud, resting for a while</x:v>
       </x:c>
       <x:c r="I13" s="7" t="str">
-        <x:v>しばらく留まる、一片の雲。</x:v>
+        <x:v>しばらく留まる、一片の雲</x:v>
       </x:c>
       <x:c r="J13" s="4" t="inlineStr">
         <x:is>
@@ -1984,9 +1948,9 @@
       <x:c r="R13" s="8" t="str"/>
       <x:c r="S13" s="8" t="str"/>
       <x:c r="T13" s="8" t="str"/>
-      <x:c r="U13" s="8" t="str"/>
-      <x:c r="V13" s="8" t="str"/>
-      <x:c r="W13" s="8" t="str"/>
+      <x:c r="U13" s="8"/>
+      <x:c r="V13" s="8"/>
+      <x:c r="W13" s="8"/>
       <x:c r="X13" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2018,13 +1982,13 @@
         <x:v>紙の舟</x:v>
       </x:c>
       <x:c r="G14" s="7" t="str">
-        <x:v>아직 물에 띄운 적은 없다.</x:v>
+        <x:v>아직 물에 띄운 적은 없다</x:v>
       </x:c>
       <x:c r="H14" s="7" t="str">
-        <x:v>It has never touched the water.</x:v>
+        <x:v>It has never touched the water</x:v>
       </x:c>
       <x:c r="I14" s="7" t="str">
-        <x:v>まだ水に浮かべたことはない。</x:v>
+        <x:v>まだ水に浮かべたことはない</x:v>
       </x:c>
       <x:c r="J14" s="4" t="inlineStr">
         <x:is>
@@ -2067,9 +2031,9 @@
       <x:c r="R14" s="8" t="str"/>
       <x:c r="S14" s="8" t="str"/>
       <x:c r="T14" s="8" t="str"/>
-      <x:c r="U14" s="8" t="str"/>
-      <x:c r="V14" s="8" t="str"/>
-      <x:c r="W14" s="8" t="str"/>
+      <x:c r="U14" s="8"/>
+      <x:c r="V14" s="8"/>
+      <x:c r="W14" s="8"/>
       <x:c r="X14" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2101,13 +2065,13 @@
         <x:v>茶碗</x:v>
       </x:c>
       <x:c r="G15" s="7" t="str">
-        <x:v>차는 식었고 향은 남았다.</x:v>
+        <x:v>차는 식었고 향은 남았다</x:v>
       </x:c>
       <x:c r="H15" s="7" t="str">
-        <x:v>The tea has cooled. Its scent remains.</x:v>
+        <x:v>The tea has cooled Its scent remains</x:v>
       </x:c>
       <x:c r="I15" s="7" t="str">
-        <x:v>茶は冷め、香りが残った。</x:v>
+        <x:v>茶は冷め、香りが残った</x:v>
       </x:c>
       <x:c r="J15" s="4" t="inlineStr">
         <x:is>
@@ -2150,9 +2114,9 @@
       <x:c r="R15" s="8" t="str"/>
       <x:c r="S15" s="8" t="str"/>
       <x:c r="T15" s="8" t="str"/>
-      <x:c r="U15" s="8" t="str"/>
-      <x:c r="V15" s="8" t="str"/>
-      <x:c r="W15" s="8" t="str"/>
+      <x:c r="U15" s="8"/>
+      <x:c r="V15" s="8"/>
+      <x:c r="W15" s="8"/>
       <x:c r="X15" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2184,13 +2148,13 @@
         <x:v>羽のかんざし</x:v>
       </x:c>
       <x:c r="G16" s="7" t="str">
-        <x:v>주인 모를 깃 하나를 꽂았다.</x:v>
+        <x:v>주인 모를 깃 하나를 꽂았다</x:v>
       </x:c>
       <x:c r="H16" s="7" t="str">
-        <x:v>A feather left behind, worn as a pin.</x:v>
+        <x:v>A feather left behind, worn as a pin</x:v>
       </x:c>
       <x:c r="I16" s="7" t="str">
-        <x:v>持ち主の知れない羽を一本、挿した。</x:v>
+        <x:v>持ち主の知れない羽を一本、挿した</x:v>
       </x:c>
       <x:c r="J16" s="4" t="inlineStr">
         <x:is>
@@ -2233,9 +2197,9 @@
       <x:c r="R16" s="8" t="str"/>
       <x:c r="S16" s="8" t="str"/>
       <x:c r="T16" s="8" t="str"/>
-      <x:c r="U16" s="8" t="str"/>
-      <x:c r="V16" s="8" t="str"/>
-      <x:c r="W16" s="8" t="str"/>
+      <x:c r="U16" s="8"/>
+      <x:c r="V16" s="8"/>
+      <x:c r="W16" s="8"/>
       <x:c r="X16" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2272,20 +2236,14 @@
           <x:t xml:space="preserve">桃の花</x:t>
         </x:is>
       </x:c>
-      <x:c r="G17" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">봄이 급히 두고 간 물건.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H17" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Spring left this behind in a hurry.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I17" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">春があわてて置いていったもの。</x:t>
-        </x:is>
+      <x:c r="G17" s="7" t="str">
+        <x:v>봄이 급히 두고 간 물건</x:v>
+      </x:c>
+      <x:c r="H17" s="7" t="str">
+        <x:v>Spring left this behind in a hurry</x:v>
+      </x:c>
+      <x:c r="I17" s="7" t="str">
+        <x:v>春があわてて置いていったもの</x:v>
       </x:c>
       <x:c r="J17" s="4" t="inlineStr">
         <x:is>
@@ -2328,9 +2286,9 @@
       <x:c r="R17" s="8" t="str"/>
       <x:c r="S17" s="8" t="str"/>
       <x:c r="T17" s="8" t="str"/>
-      <x:c r="U17" s="8" t="str"/>
-      <x:c r="V17" s="8" t="str"/>
-      <x:c r="W17" s="8" t="str"/>
+      <x:c r="U17" s="8"/>
+      <x:c r="V17" s="8"/>
+      <x:c r="W17" s="8"/>
       <x:c r="X17" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2362,13 +2320,13 @@
         <x:v>狐の面</x:v>
       </x:c>
       <x:c r="G18" s="7" t="str">
-        <x:v>웃는 얼굴 뒤는 알 수 없다.</x:v>
+        <x:v>웃는 얼굴 뒤는 알 수 없다</x:v>
       </x:c>
       <x:c r="H18" s="7" t="str">
-        <x:v>No telling what lies behind the smile.</x:v>
+        <x:v>No telling what lies behind the smile</x:v>
       </x:c>
       <x:c r="I18" s="7" t="str">
-        <x:v>笑顔の裏はわからない。</x:v>
+        <x:v>笑顔の裏はわからない</x:v>
       </x:c>
       <x:c r="J18" s="4" t="inlineStr">
         <x:is>
@@ -2411,9 +2369,9 @@
       <x:c r="R18" s="8" t="str"/>
       <x:c r="S18" s="8" t="str"/>
       <x:c r="T18" s="8" t="str"/>
-      <x:c r="U18" s="8" t="str"/>
-      <x:c r="V18" s="8" t="str"/>
-      <x:c r="W18" s="8" t="str"/>
+      <x:c r="U18" s="8"/>
+      <x:c r="V18" s="8"/>
+      <x:c r="W18" s="8"/>
       <x:c r="X18" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2445,13 +2403,13 @@
         <x:v>鶴の羽飾り</x:v>
       </x:c>
       <x:c r="G19" s="7" t="str">
-        <x:v>날개에서 떨어져 여기까지 왔다.</x:v>
+        <x:v>날개에서 떨어져 여기까지 왔다</x:v>
       </x:c>
       <x:c r="H19" s="7" t="str">
-        <x:v>Shed from a wing, it drifted this far.</x:v>
+        <x:v>Shed from a wing, it drifted this far</x:v>
       </x:c>
       <x:c r="I19" s="7" t="str">
-        <x:v>翼を離れ、ここまで流れ着いた。</x:v>
+        <x:v>翼を離れ、ここまで流れ着いた</x:v>
       </x:c>
       <x:c r="J19" s="4" t="inlineStr">
         <x:is>
@@ -2494,9 +2452,9 @@
       <x:c r="R19" s="8" t="str"/>
       <x:c r="S19" s="8" t="str"/>
       <x:c r="T19" s="8" t="str"/>
-      <x:c r="U19" s="8" t="str"/>
-      <x:c r="V19" s="8" t="str"/>
-      <x:c r="W19" s="8" t="str"/>
+      <x:c r="U19" s="8"/>
+      <x:c r="V19" s="8"/>
+      <x:c r="W19" s="8"/>
       <x:c r="X19" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2528,13 +2486,13 @@
         <x:v>花嫁の面</x:v>
       </x:c>
       <x:c r="G20" s="7" t="str">
-        <x:v>정체는 비밀인거같다.</x:v>
+        <x:v>정체는 비밀인거같다</x:v>
       </x:c>
       <x:c r="H20" s="7" t="str">
-        <x:v>Seems to keep its identity a secret.</x:v>
+        <x:v>Seems to keep its identity a secret</x:v>
       </x:c>
       <x:c r="I20" s="7" t="str">
-        <x:v>正体は秘密らしい。</x:v>
+        <x:v>正体は秘密らしい</x:v>
       </x:c>
       <x:c r="J20" s="4" t="inlineStr">
         <x:is>
@@ -2583,23 +2541,17 @@
       <x:c r="T20" s="7" t="str">
         <x:v>仮面舞</x:v>
       </x:c>
-      <x:c r="U20" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">본체가 적과 충돌하면 피해 없이 적을 제거한다.
-{cooldown}초마다 발동하며 가시·낙석에는 적용되지 않는다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V20" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Defeat an enemy on contact without taking damage.
-Cooldown: {cooldown}s. Not effective against spikes or falling rocks.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="W20" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">本体が敵に接触すると、ダメージを受けずに敵を倒す。
-{cooldown}秒ごとに発動。トゲ・落石には無効。</x:t>
-        </x:is>
+      <x:c r="U20" s="7" t="str">
+        <x:v>본체가 적과 충돌하면 피해 없이 적을 제거한다
+{cooldown}초마다 발동하며 가시·낙석에는 적용되지 않는다</x:v>
+      </x:c>
+      <x:c r="V20" s="7" t="str">
+        <x:v>Defeat an enemy on contact without taking damage
+Cooldown: {cooldown}s Not effective against spikes or falling rocks</x:v>
+      </x:c>
+      <x:c r="W20" s="7" t="str">
+        <x:v>本体が敵に接触すると、ダメージを受けずに敵を倒す
+{cooldown}秒ごとに発動 トゲ・落石には無効</x:v>
       </x:c>
       <x:c r="X20" s="20" t="n">
         <x:v>30</x:v>
@@ -2632,13 +2584,13 @@
         <x:v>玄武</x:v>
       </x:c>
       <x:c r="G21" s="7" t="str">
-        <x:v>느린 장인이 끝내 완성한 투구.</x:v>
+        <x:v>느린 장인이 끝내 완성한 투구</x:v>
       </x:c>
       <x:c r="H21" s="7" t="str">
-        <x:v>A very slow craftsman finally finished it.</x:v>
+        <x:v>A very slow craftsman finally finished it</x:v>
       </x:c>
       <x:c r="I21" s="7" t="str">
-        <x:v>のんびり屋の職人が、ついに仕上げた。</x:v>
+        <x:v>のんびり屋の職人が、ついに仕上げた</x:v>
       </x:c>
       <x:c r="J21" s="4" t="inlineStr">
         <x:is>
@@ -2687,23 +2639,17 @@
       <x:c r="T21" s="7" t="str">
         <x:v>金剛</x:v>
       </x:c>
-      <x:c r="U21" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">매 판 시작 시 본체에게 방어막 1개를 부여한다.
-충돌·추락을 한 번 막으며 분신에게는 적용되지 않는다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V21" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Start each run with a shield on Ink.
-Blocks one hit or fall; clones excluded.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="W21" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">毎回、本体に盾を1つ付けてスタート。
-衝突・落下を1回防ぎます。分身は対象外です。</x:t>
-        </x:is>
+      <x:c r="U21" s="7" t="str">
+        <x:v>매 판 시작 시 본체에게 방어막 1개를 부여한다
+충돌·추락을 한 번 막으며 분신에게는 적용되지 않는다</x:v>
+      </x:c>
+      <x:c r="V21" s="7" t="str">
+        <x:v>Start each run with a shield on Ink
+Blocks one hit or fall; clones excluded</x:v>
+      </x:c>
+      <x:c r="W21" s="7" t="str">
+        <x:v>毎回、本体に盾を1つ付けてスタート
+衝突・落下を1回防ぎます 分身は対象外です</x:v>
       </x:c>
       <x:c r="X21" s="18" t="n">
         <x:v>0</x:v>
@@ -2736,13 +2682,13 @@
         <x:v>月光の冠</x:v>
       </x:c>
       <x:c r="G22" s="7" t="str">
-        <x:v>기울지 않는 초승달.</x:v>
+        <x:v>기울지 않는 초승달</x:v>
       </x:c>
       <x:c r="H22" s="7" t="str">
-        <x:v>A crescent that never wanes.</x:v>
+        <x:v>A crescent that never wanes</x:v>
       </x:c>
       <x:c r="I22" s="7" t="str">
-        <x:v>欠けることのない三日月。</x:v>
+        <x:v>欠けることのない三日月</x:v>
       </x:c>
       <x:c r="J22" s="4" t="inlineStr">
         <x:is>
@@ -2785,9 +2731,9 @@
       <x:c r="R22" s="8" t="str"/>
       <x:c r="S22" s="8" t="str"/>
       <x:c r="T22" s="8" t="str"/>
-      <x:c r="U22" s="8" t="str"/>
-      <x:c r="V22" s="8" t="str"/>
-      <x:c r="W22" s="8" t="str"/>
+      <x:c r="U22" s="8"/>
+      <x:c r="V22" s="8"/>
+      <x:c r="W22" s="8"/>
       <x:c r="X22" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2819,13 +2765,13 @@
         <x:v>二本の筆</x:v>
       </x:c>
       <x:c r="G23" s="7" t="str">
-        <x:v>붓을 쥘 손이 없어 머리에 꽂았다.</x:v>
+        <x:v>붓을 쥘 손이 없어 머리에 꽂았다</x:v>
       </x:c>
       <x:c r="H23" s="7" t="str">
-        <x:v>No hands to hold them, so here they rest.</x:v>
+        <x:v>No hands to hold them, so here they rest</x:v>
       </x:c>
       <x:c r="I23" s="7" t="str">
-        <x:v>筆を持つ手がないので、頭に挿した。</x:v>
+        <x:v>筆を持つ手がないので、頭に挿した</x:v>
       </x:c>
       <x:c r="J23" s="4" t="inlineStr">
         <x:is>
@@ -2868,9 +2814,9 @@
       <x:c r="R23" s="8" t="str"/>
       <x:c r="S23" s="8" t="str"/>
       <x:c r="T23" s="8" t="str"/>
-      <x:c r="U23" s="8" t="str"/>
-      <x:c r="V23" s="8" t="str"/>
-      <x:c r="W23" s="8" t="str"/>
+      <x:c r="U23" s="8"/>
+      <x:c r="V23" s="8"/>
+      <x:c r="W23" s="8"/>
       <x:c r="X23" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2957,23 +2903,17 @@
       <x:c r="T24" s="7" t="str">
         <x:v>輪廻</x:v>
       </x:c>
-      <x:c r="U24" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">분신이 쓰러질 때마다 본체 체력을 1칸 회복한다.
-최대 체력을 넘거나 쓰러진 본체를 되살리지는 않는다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V24" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Each fallen clone restores 1 HP to Ink.
-Cannot exceed max HP or revive Ink.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="W24" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">分身が倒れるたび、本体の体力を1回復。
-最大体力を超えず、倒れた本体は蘇りません。</x:t>
-        </x:is>
+      <x:c r="U24" s="7" t="str">
+        <x:v>분신이 쓰러질 때마다 본체 체력을 1칸 회복한다
+최대 체력을 넘거나 쓰러진 본체를 되살리지는 않는다</x:v>
+      </x:c>
+      <x:c r="V24" s="7" t="str">
+        <x:v>Each fallen clone restores 1 HP to Ink
+Cannot exceed max HP or revive Ink</x:v>
+      </x:c>
+      <x:c r="W24" s="7" t="str">
+        <x:v>分身が倒れるたび、本体の体力を1回復
+最大体力を超えず、倒れた本体は蘇りません</x:v>
       </x:c>
       <x:c r="X24" s="18" t="n">
         <x:v>0</x:v>
@@ -3011,20 +2951,14 @@
           <x:t xml:space="preserve">鯉の面</x:t>
         </x:is>
       </x:c>
-      <x:c r="G25" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">용문 앞에서 잠깐 쉬어 가는 중.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H25" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Taking a short rest before the Dragon Gate.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I25" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">竜門の手前で、ちょっとひと休み。</x:t>
-        </x:is>
+      <x:c r="G25" s="7" t="str">
+        <x:v>용문 앞에서 잠깐 쉬어 가는 중</x:v>
+      </x:c>
+      <x:c r="H25" s="7" t="str">
+        <x:v>Taking a short rest before the Dragon Gate</x:v>
+      </x:c>
+      <x:c r="I25" s="7" t="str">
+        <x:v>竜門の手前で、ちょっとひと休み</x:v>
       </x:c>
       <x:c r="J25" s="4" t="inlineStr">
         <x:is>
@@ -3067,9 +3001,9 @@
       <x:c r="R25" s="8" t="str"/>
       <x:c r="S25" s="8" t="str"/>
       <x:c r="T25" s="8" t="str"/>
-      <x:c r="U25" s="8" t="str"/>
-      <x:c r="V25" s="8" t="str"/>
-      <x:c r="W25" s="8" t="str"/>
+      <x:c r="U25" s="8"/>
+      <x:c r="V25" s="8"/>
+      <x:c r="W25" s="8"/>
       <x:c r="X25" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3101,13 +3035,13 @@
         <x:v>玉冠</x:v>
       </x:c>
       <x:c r="G26" s="7" t="str">
-        <x:v>오래된 옥에 빛이 남아 있다.</x:v>
+        <x:v>오래된 옥에 빛이 남아 있다</x:v>
       </x:c>
       <x:c r="H26" s="7" t="str">
-        <x:v>A trace of light remains in the old jade.</x:v>
+        <x:v>A trace of light remains in the old jade</x:v>
       </x:c>
       <x:c r="I26" s="7" t="str">
-        <x:v>古い玉に、光が残っている。</x:v>
+        <x:v>古い玉に、光が残っている</x:v>
       </x:c>
       <x:c r="J26" s="4" t="inlineStr">
         <x:is>
@@ -3150,9 +3084,9 @@
       <x:c r="R26" s="8" t="str"/>
       <x:c r="S26" s="8" t="str"/>
       <x:c r="T26" s="8" t="str"/>
-      <x:c r="U26" s="8" t="str"/>
-      <x:c r="V26" s="8" t="str"/>
-      <x:c r="W26" s="8" t="str"/>
+      <x:c r="U26" s="8"/>
+      <x:c r="V26" s="8"/>
+      <x:c r="W26" s="8"/>
       <x:c r="X26" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3184,13 +3118,13 @@
         <x:v>鳳凰の冠</x:v>
       </x:c>
       <x:c r="G27" s="7" t="str">
-        <x:v>타지 않은 깃은 딱 다섯 개였다.</x:v>
+        <x:v>타지 않은 깃은 딱 다섯 개였다</x:v>
       </x:c>
       <x:c r="H27" s="7" t="str">
-        <x:v>Exactly five feathers escaped the fire.</x:v>
+        <x:v>Exactly five feathers escaped the fire</x:v>
       </x:c>
       <x:c r="I27" s="7" t="str">
-        <x:v>燃え残った羽は、ちょうど五枚だった。</x:v>
+        <x:v>燃え残った羽は、ちょうど五枚だった</x:v>
       </x:c>
       <x:c r="J27" s="4" t="inlineStr">
         <x:is>
@@ -3239,23 +3173,17 @@
       <x:c r="T27" s="7" t="str">
         <x:v>鳳凰の息吹</x:v>
       </x:c>
-      <x:c r="U27" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">한 판에 한 번 본체가 체력 1칸으로 살아남아 50m 상승한다.
-성장 부활과 횟수를 공유하며 분신에게는 적용되지 않는다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V27" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Survive one fatal hit with 1 HP per run.
-Rise 50m; shared with growth revival.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="W27" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1プレイに1回、本体が体力1で耐えて50m上昇。
-成長の復活と回数を共有。分身は対象外です。</x:t>
-        </x:is>
+      <x:c r="U27" s="7" t="str">
+        <x:v>한 판에 한 번 본체가 체력 1칸으로 살아남아 50m 상승한다
+성장 부활과 횟수를 공유하며 분신에게는 적용되지 않는다</x:v>
+      </x:c>
+      <x:c r="V27" s="7" t="str">
+        <x:v>Survive one fatal hit with 1 HP per run
+Rise 50m; shared with growth revival</x:v>
+      </x:c>
+      <x:c r="W27" s="7" t="str">
+        <x:v>1プレイに1回、本体が体力1で耐えて50m上昇
+成長の復活と回数を共有 分身は対象外です</x:v>
       </x:c>
       <x:c r="X27" s="18" t="n">
         <x:v>0</x:v>
@@ -3288,13 +3216,13 @@
         <x:v>山の虎面</x:v>
       </x:c>
       <x:c r="G28" s="7" t="str">
-        <x:v>눈을 마주치면 먼저 피하게 된다.</x:v>
+        <x:v>눈을 마주치면 먼저 피하게 된다</x:v>
       </x:c>
       <x:c r="H28" s="7" t="str">
-        <x:v>Meet its eyes, and you look away first.</x:v>
+        <x:v>Meet its eyes, and you look away first</x:v>
       </x:c>
       <x:c r="I28" s="7" t="str">
-        <x:v>目が合うと、こちらが先にそらす。</x:v>
+        <x:v>目が合うと、こちらが先にそらす</x:v>
       </x:c>
       <x:c r="J28" s="4" t="inlineStr">
         <x:is>
@@ -3337,9 +3265,9 @@
       <x:c r="R28" s="8" t="str"/>
       <x:c r="S28" s="8" t="str"/>
       <x:c r="T28" s="8" t="str"/>
-      <x:c r="U28" s="8" t="str"/>
-      <x:c r="V28" s="8" t="str"/>
-      <x:c r="W28" s="8" t="str"/>
+      <x:c r="U28" s="8"/>
+      <x:c r="V28" s="8"/>
+      <x:c r="W28" s="8"/>
       <x:c r="X28" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3371,13 +3299,13 @@
         <x:v>山王の冠</x:v>
       </x:c>
       <x:c r="G29" s="7" t="str">
-        <x:v>산을 내려온 뒤에도 벗지 않았다.</x:v>
+        <x:v>산을 내려온 뒤에도 벗지 않았다</x:v>
       </x:c>
       <x:c r="H29" s="7" t="str">
-        <x:v>Kept on, even after leaving the mountain.</x:v>
+        <x:v>Kept on, even after leaving the mountain</x:v>
       </x:c>
       <x:c r="I29" s="7" t="str">
-        <x:v>山を下りてからも、脱がなかった。</x:v>
+        <x:v>山を下りてからも、脱がなかった</x:v>
       </x:c>
       <x:c r="J29" s="4" t="inlineStr">
         <x:is>
@@ -3420,9 +3348,9 @@
       <x:c r="R29" s="8" t="str"/>
       <x:c r="S29" s="8" t="str"/>
       <x:c r="T29" s="8" t="str"/>
-      <x:c r="U29" s="8" t="str"/>
-      <x:c r="V29" s="8" t="str"/>
-      <x:c r="W29" s="8" t="str"/>
+      <x:c r="U29" s="8"/>
+      <x:c r="V29" s="8"/>
+      <x:c r="W29" s="8"/>
       <x:c r="X29" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3454,13 +3382,13 @@
         <x:v>雲竜</x:v>
       </x:c>
       <x:c r="G30" s="7" t="str">
-        <x:v>구름 사이로 뿔이 드러난다.</x:v>
+        <x:v>구름 사이로 뿔이 드러난다</x:v>
       </x:c>
       <x:c r="H30" s="7" t="str">
-        <x:v>Horns emerge between the clouds.</x:v>
+        <x:v>Horns emerge between the clouds</x:v>
       </x:c>
       <x:c r="I30" s="7" t="str">
-        <x:v>雲の間から角がのぞく。</x:v>
+        <x:v>雲の間から角がのぞく</x:v>
       </x:c>
       <x:c r="J30" s="4" t="inlineStr">
         <x:is>
@@ -3503,9 +3431,9 @@
       <x:c r="R30" s="8" t="str"/>
       <x:c r="S30" s="8" t="str"/>
       <x:c r="T30" s="8" t="str"/>
-      <x:c r="U30" s="8" t="str"/>
-      <x:c r="V30" s="8" t="str"/>
-      <x:c r="W30" s="8" t="str"/>
+      <x:c r="U30" s="8"/>
+      <x:c r="V30" s="8"/>
+      <x:c r="W30" s="8"/>
       <x:c r="X30" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3537,13 +3465,13 @@
         <x:v>鉄仮面</x:v>
       </x:c>
       <x:c r="G31" s="7" t="str">
-        <x:v>차가운 겉모습 안에는 같은 먹이 있다.</x:v>
+        <x:v>차가운 겉모습 안에는 같은 먹이 있다</x:v>
       </x:c>
       <x:c r="H31" s="7" t="str">
-        <x:v>The same Ink beneath a cold exterior.</x:v>
+        <x:v>The same Ink beneath a cold exterior</x:v>
       </x:c>
       <x:c r="I31" s="7" t="str">
-        <x:v>冷たい外見の奥には、いつもの墨がいる。</x:v>
+        <x:v>冷たい外見の奥には、いつもの墨がいる</x:v>
       </x:c>
       <x:c r="J31" s="4" t="inlineStr">
         <x:is>
@@ -3586,9 +3514,9 @@
       <x:c r="R31" s="8" t="str"/>
       <x:c r="S31" s="8" t="str"/>
       <x:c r="T31" s="8" t="str"/>
-      <x:c r="U31" s="8" t="str"/>
-      <x:c r="V31" s="8" t="str"/>
-      <x:c r="W31" s="8" t="str"/>
+      <x:c r="U31" s="8"/>
+      <x:c r="V31" s="8"/>
+      <x:c r="W31" s="8"/>
       <x:c r="X31" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3675,9 +3603,9 @@
       <x:c r="R32" s="8" t="str"/>
       <x:c r="S32" s="8" t="str"/>
       <x:c r="T32" s="8" t="str"/>
-      <x:c r="U32" s="8" t="str"/>
-      <x:c r="V32" s="8" t="str"/>
-      <x:c r="W32" s="8" t="str"/>
+      <x:c r="U32" s="8"/>
+      <x:c r="V32" s="8"/>
+      <x:c r="W32" s="8"/>
       <x:c r="X32" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3764,9 +3692,9 @@
       <x:c r="R33" s="8" t="str"/>
       <x:c r="S33" s="8" t="str"/>
       <x:c r="T33" s="8" t="str"/>
-      <x:c r="U33" s="8" t="str"/>
-      <x:c r="V33" s="8" t="str"/>
-      <x:c r="W33" s="8" t="str"/>
+      <x:c r="U33" s="8"/>
+      <x:c r="V33" s="8"/>
+      <x:c r="W33" s="8"/>
       <x:c r="X33" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3853,9 +3781,9 @@
       <x:c r="R34" s="8" t="str"/>
       <x:c r="S34" s="8" t="str"/>
       <x:c r="T34" s="8" t="str"/>
-      <x:c r="U34" s="8" t="str"/>
-      <x:c r="V34" s="8" t="str"/>
-      <x:c r="W34" s="8" t="str"/>
+      <x:c r="U34" s="8"/>
+      <x:c r="V34" s="8"/>
+      <x:c r="W34" s="8"/>
       <x:c r="X34" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3942,9 +3870,9 @@
       <x:c r="R35" s="8" t="str"/>
       <x:c r="S35" s="8" t="str"/>
       <x:c r="T35" s="8" t="str"/>
-      <x:c r="U35" s="8" t="str"/>
-      <x:c r="V35" s="8" t="str"/>
-      <x:c r="W35" s="8" t="str"/>
+      <x:c r="U35" s="8"/>
+      <x:c r="V35" s="8"/>
+      <x:c r="W35" s="8"/>
       <x:c r="X35" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3981,20 +3909,14 @@
           <x:t xml:space="preserve">紙の翼</x:t>
         </x:is>
       </x:c>
-      <x:c r="G36" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">끝까지 버틴 종이는 날개가 된다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H36" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Paper that holds on becomes a pair of wings.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I36" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">最後まで持ちこたえた紙は、翼になる。</x:t>
-        </x:is>
+      <x:c r="G36" s="7" t="str">
+        <x:v>끝까지 버틴 종이는 날개가 된다</x:v>
+      </x:c>
+      <x:c r="H36" s="7" t="str">
+        <x:v>Paper that holds on becomes a pair of wings</x:v>
+      </x:c>
+      <x:c r="I36" s="7" t="str">
+        <x:v>最後まで持ちこたえた紙は、翼になる</x:v>
       </x:c>
       <x:c r="J36" s="4" t="inlineStr">
         <x:is>
@@ -4037,9 +3959,9 @@
       <x:c r="R36" s="8" t="str"/>
       <x:c r="S36" s="8" t="str"/>
       <x:c r="T36" s="8" t="str"/>
-      <x:c r="U36" s="8" t="str"/>
-      <x:c r="V36" s="8" t="str"/>
-      <x:c r="W36" s="8" t="str"/>
+      <x:c r="U36" s="8"/>
+      <x:c r="V36" s="8"/>
+      <x:c r="W36" s="8"/>
       <x:c r="X36" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4071,13 +3993,13 @@
         <x:v>鶴の翼</x:v>
       </x:c>
       <x:c r="G37" s="7" t="str">
-        <x:v>접어 두었던 날개를 펼친다.</x:v>
+        <x:v>접어 두었던 날개를 펼친다</x:v>
       </x:c>
       <x:c r="H37" s="7" t="str">
-        <x:v>Wings, folded until now, open.</x:v>
+        <x:v>Wings, folded until now, open</x:v>
       </x:c>
       <x:c r="I37" s="7" t="str">
-        <x:v>畳んでいた翼を広げる。</x:v>
+        <x:v>畳んでいた翼を広げる</x:v>
       </x:c>
       <x:c r="J37" s="4" t="inlineStr">
         <x:is>
@@ -4120,9 +4042,9 @@
       <x:c r="R37" s="8" t="str"/>
       <x:c r="S37" s="8" t="str"/>
       <x:c r="T37" s="8" t="str"/>
-      <x:c r="U37" s="8" t="str"/>
-      <x:c r="V37" s="8" t="str"/>
-      <x:c r="W37" s="8" t="str"/>
+      <x:c r="U37" s="8"/>
+      <x:c r="V37" s="8"/>
+      <x:c r="W37" s="8"/>
       <x:c r="X37" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4154,13 +4076,13 @@
         <x:v>墨の蝶</x:v>
       </x:c>
       <x:c r="G38" s="7" t="str">
-        <x:v>먹이 묻은 줄 모르고 날아온 나비.</x:v>
+        <x:v>먹이 묻은 줄 모르고 날아온 나비</x:v>
       </x:c>
       <x:c r="H38" s="7" t="str">
-        <x:v>A butterfly unaware of its ink stains.</x:v>
+        <x:v>A butterfly unaware of its ink stains</x:v>
       </x:c>
       <x:c r="I38" s="7" t="str">
-        <x:v>墨がついたとも知らず、飛んできた蝶。</x:v>
+        <x:v>墨がついたとも知らず、飛んできた蝶</x:v>
       </x:c>
       <x:c r="J38" s="4" t="inlineStr">
         <x:is>
@@ -4203,9 +4125,9 @@
       <x:c r="R38" s="8" t="str"/>
       <x:c r="S38" s="8" t="str"/>
       <x:c r="T38" s="8" t="str"/>
-      <x:c r="U38" s="8" t="str"/>
-      <x:c r="V38" s="8" t="str"/>
-      <x:c r="W38" s="8" t="str"/>
+      <x:c r="U38" s="8"/>
+      <x:c r="V38" s="8"/>
+      <x:c r="W38" s="8"/>
       <x:c r="X38" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4242,20 +4164,14 @@
           <x:t xml:space="preserve">紅の足袋</x:t>
         </x:is>
       </x:c>
-      <x:c r="G39" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">발자국부터 먼저 길을 나섰다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H39" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">The footprints set off before their owner.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I39" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">足跡のほうが、先に旅に出た。</x:t>
-        </x:is>
+      <x:c r="G39" s="7" t="str">
+        <x:v>발자국부터 먼저 길을 나섰다</x:v>
+      </x:c>
+      <x:c r="H39" s="7" t="str">
+        <x:v>The footprints set off before their owner</x:v>
+      </x:c>
+      <x:c r="I39" s="7" t="str">
+        <x:v>足跡のほうが、先に旅に出た</x:v>
       </x:c>
       <x:c r="J39" s="4" t="inlineStr">
         <x:is>
@@ -4298,9 +4214,9 @@
       <x:c r="R39" s="8" t="str"/>
       <x:c r="S39" s="8" t="str"/>
       <x:c r="T39" s="8" t="str"/>
-      <x:c r="U39" s="8" t="str"/>
-      <x:c r="V39" s="8" t="str"/>
-      <x:c r="W39" s="8" t="str"/>
+      <x:c r="U39" s="8"/>
+      <x:c r="V39" s="8"/>
+      <x:c r="W39" s="8"/>
       <x:c r="X39" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4332,13 +4248,13 @@
         <x:v>雲の靴</x:v>
       </x:c>
       <x:c r="G40" s="7" t="str">
-        <x:v>비 오는 날엔 양말까지 구름이 된다.</x:v>
+        <x:v>비 오는 날엔 양말까지 구름이 된다</x:v>
       </x:c>
       <x:c r="H40" s="7" t="str">
-        <x:v>On rainy days, even the socks turn to cloud.</x:v>
+        <x:v>On rainy days, even the socks turn to cloud</x:v>
       </x:c>
       <x:c r="I40" s="7" t="str">
-        <x:v>雨の日には、靴下まで雲になる。</x:v>
+        <x:v>雨の日には、靴下まで雲になる</x:v>
       </x:c>
       <x:c r="J40" s="4" t="inlineStr">
         <x:is>
@@ -4387,23 +4303,17 @@
       <x:c r="T40" s="7" t="str">
         <x:v>雲の跳躍</x:v>
       </x:c>
-      <x:c r="U40" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">본체가 맵 발판에 착지하면 먹방울 효과로 50m 상승한다.
-직접 그린 발판에는 발동하지 않는다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V40" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Land on a map platform to boost Ink 50m with an Ink Drop.
-Does not trigger on drawn platforms.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="W40" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">本体がマップの足場に着地すると、墨滴の効果で50m上昇。
-描いた足場では発動しません。</x:t>
-        </x:is>
+      <x:c r="U40" s="7" t="str">
+        <x:v>본체가 맵 발판에 착지하면 먹방울 효과로 50m 상승한다
+직접 그린 발판에는 발동하지 않는다</x:v>
+      </x:c>
+      <x:c r="V40" s="7" t="str">
+        <x:v>Land on a map platform to boost Ink 50m with an Ink Drop
+Does not trigger on drawn platforms</x:v>
+      </x:c>
+      <x:c r="W40" s="7" t="str">
+        <x:v>本体がマップの足場に着地すると、墨滴の効果で50m上昇
+描いた足場では発動しません</x:v>
       </x:c>
       <x:c r="X40" s="18" t="n">
         <x:v>0</x:v>
@@ -4436,13 +4346,13 @@
         <x:v>鬼火</x:v>
       </x:c>
       <x:c r="G41" s="7" t="str">
-        <x:v>바람이 없어도 불은 흔들린다.</x:v>
+        <x:v>바람이 없어도 불은 흔들린다</x:v>
       </x:c>
       <x:c r="H41" s="7" t="str">
-        <x:v>The flames stir without a breeze.</x:v>
+        <x:v>The flames stir without a breeze</x:v>
       </x:c>
       <x:c r="I41" s="7" t="str">
-        <x:v>風がなくても、火は揺れる。</x:v>
+        <x:v>風がなくても、火は揺れる</x:v>
       </x:c>
       <x:c r="J41" s="4" t="inlineStr">
         <x:is>
@@ -4485,9 +4395,9 @@
       <x:c r="R41" s="8" t="str"/>
       <x:c r="S41" s="8" t="str"/>
       <x:c r="T41" s="8" t="str"/>
-      <x:c r="U41" s="8" t="str"/>
-      <x:c r="V41" s="8" t="str"/>
-      <x:c r="W41" s="8" t="str"/>
+      <x:c r="U41" s="8"/>
+      <x:c r="V41" s="8"/>
+      <x:c r="W41" s="8"/>
       <x:c r="X41" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4519,13 +4429,13 @@
         <x:v>迷子の灯り</x:v>
       </x:c>
       <x:c r="G42" s="7" t="str">
-        <x:v>어디로 가는지도 모르고 따라온다.</x:v>
+        <x:v>어디로 가는지도 모르고 따라온다</x:v>
       </x:c>
       <x:c r="H42" s="7" t="str">
-        <x:v>They follow without knowing the way.</x:v>
+        <x:v>They follow without knowing the way</x:v>
       </x:c>
       <x:c r="I42" s="7" t="str">
-        <x:v>行き先も知らずについてくる。</x:v>
+        <x:v>行き先も知らずについてくる</x:v>
       </x:c>
       <x:c r="J42" s="4" t="inlineStr">
         <x:is>
@@ -4568,9 +4478,9 @@
       <x:c r="R42" s="8" t="str"/>
       <x:c r="S42" s="8" t="str"/>
       <x:c r="T42" s="8" t="str"/>
-      <x:c r="U42" s="8" t="str"/>
-      <x:c r="V42" s="8" t="str"/>
-      <x:c r="W42" s="8" t="str"/>
+      <x:c r="U42" s="8"/>
+      <x:c r="V42" s="8"/>
+      <x:c r="W42" s="8"/>
       <x:c r="X42" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4602,13 +4512,13 @@
         <x:v>月雲</x:v>
       </x:c>
       <x:c r="G43" s="7" t="str">
-        <x:v>구름에 가려도 달은 남아 있다.</x:v>
+        <x:v>구름에 가려도 달은 남아 있다</x:v>
       </x:c>
       <x:c r="H43" s="7" t="str">
-        <x:v>The moon remains behind the clouds.</x:v>
+        <x:v>The moon remains behind the clouds</x:v>
       </x:c>
       <x:c r="I43" s="7" t="str">
-        <x:v>雲に隠れても、月はそこにある。</x:v>
+        <x:v>雲に隠れても、月はそこにある</x:v>
       </x:c>
       <x:c r="J43" s="4" t="inlineStr">
         <x:is>
@@ -4651,9 +4561,9 @@
       <x:c r="R43" s="8" t="str"/>
       <x:c r="S43" s="8" t="str"/>
       <x:c r="T43" s="8" t="str"/>
-      <x:c r="U43" s="8" t="str"/>
-      <x:c r="V43" s="8" t="str"/>
-      <x:c r="W43" s="8" t="str"/>
+      <x:c r="U43" s="8"/>
+      <x:c r="V43" s="8"/>
+      <x:c r="W43" s="8"/>
       <x:c r="X43" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4740,23 +4650,17 @@
       <x:c r="T44" s="7" t="str">
         <x:v>縁の導き</x:v>
       </x:c>
-      <x:c r="U44" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">매 판 시작 시 먹방울 아이템으로 50m 상승한다.
-튜토리얼 종료 후 발동하며 부활 시에는 재발동하지 않는다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V44" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Start each run with a 50m Ink Drop boost.
-After the tutorial; not granted on revival.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="W44" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">毎回、墨滴で50m上昇してスタート。
-チュートリアル後に発動。復活時は再発動しません。</x:t>
-        </x:is>
+      <x:c r="U44" s="7" t="str">
+        <x:v>매 판 시작 시 먹방울 아이템으로 50m 상승한다
+튜토리얼 종료 후 발동하며 부활 시에는 재발동하지 않는다</x:v>
+      </x:c>
+      <x:c r="V44" s="7" t="str">
+        <x:v>Start each run with a 50m Ink Drop boost
+After the tutorial; not granted on revival</x:v>
+      </x:c>
+      <x:c r="W44" s="7" t="str">
+        <x:v>毎回、墨滴で50m上昇してスタート
+チュートリアル後に発動 復活時は再発動しません</x:v>
       </x:c>
       <x:c r="X44" s="18" t="n">
         <x:v>0</x:v>
@@ -4789,13 +4693,13 @@
         <x:v>風の扇</x:v>
       </x:c>
       <x:c r="G45" s="7" t="str">
-        <x:v>부채를 펼치면, 바람의 흐름이 바뀔거같다.</x:v>
+        <x:v>부채를 펼치면, 바람의 흐름이 바뀔거같다</x:v>
       </x:c>
       <x:c r="H45" s="7" t="str">
-        <x:v>Open the fan, and the wind might change its course.</x:v>
+        <x:v>Open the fan, and the wind might change its course</x:v>
       </x:c>
       <x:c r="I45" s="7" t="str">
-        <x:v>扇を開けば、風の流れが変わりそうだ。</x:v>
+        <x:v>扇を開けば、風の流れが変わりそうだ</x:v>
       </x:c>
       <x:c r="J45" s="4" t="inlineStr">
         <x:is>
@@ -4844,23 +4748,17 @@
       <x:c r="T45" s="7" t="str">
         <x:v>風の跳躍</x:v>
       </x:c>
-      <x:c r="U45" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">전용 버튼으로 본체가 25m 도약한다.
-상승 중 피해를 막고, {cooldown}초 후 다시 사용할 수 있다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V45" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tap the skill button to leap 25m with Ink.
-Protected while rising. Cooldown: {cooldown}s.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="W45" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">専用ボタンで本体が25m跳躍。
-上昇中はダメージを防ぎ、{cooldown}秒後に再使用できます。</x:t>
-        </x:is>
+      <x:c r="U45" s="7" t="str">
+        <x:v>전용 버튼으로 본체가 25m 도약한다
+상승 중 피해를 막고, {cooldown}초 후 다시 사용할 수 있다</x:v>
+      </x:c>
+      <x:c r="V45" s="7" t="str">
+        <x:v>Tap the skill button to leap 25m with Ink
+Protected while rising Cooldown: {cooldown}s</x:v>
+      </x:c>
+      <x:c r="W45" s="7" t="str">
+        <x:v>専用ボタンで本体が25m跳躍
+上昇中はダメージを防ぎ、{cooldown}秒後に再使用できます</x:v>
       </x:c>
       <x:c r="X45" s="20" t="n">
         <x:v>20</x:v>
@@ -4893,13 +4791,13 @@
         <x:v>竜のしっぽ</x:v>
       </x:c>
       <x:c r="G46" s="7" t="str">
-        <x:v>스쳐 간 용이 흔적을 남겼다.</x:v>
+        <x:v>스쳐 간 용이 흔적을 남겼다</x:v>
       </x:c>
       <x:c r="H46" s="7" t="str">
-        <x:v>A passing dragon left its mark.</x:v>
+        <x:v>A passing dragon left its mark</x:v>
       </x:c>
       <x:c r="I46" s="7" t="str">
-        <x:v>通り過ぎた竜が、跡を残した。</x:v>
+        <x:v>通り過ぎた竜が、跡を残した</x:v>
       </x:c>
       <x:c r="J46" s="4" t="inlineStr">
         <x:is>
@@ -4942,9 +4840,9 @@
       <x:c r="R46" s="8" t="str"/>
       <x:c r="S46" s="8" t="str"/>
       <x:c r="T46" s="8" t="str"/>
-      <x:c r="U46" s="8" t="str"/>
-      <x:c r="V46" s="8" t="str"/>
-      <x:c r="W46" s="8" t="str"/>
+      <x:c r="U46" s="8"/>
+      <x:c r="V46" s="8"/>
+      <x:c r="W46" s="8"/>
       <x:c r="X46" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5025,9 +4923,9 @@
       <x:c r="R47" s="8" t="str"/>
       <x:c r="S47" s="8" t="str"/>
       <x:c r="T47" s="8" t="str"/>
-      <x:c r="U47" s="8" t="str"/>
-      <x:c r="V47" s="8" t="str"/>
-      <x:c r="W47" s="8" t="str"/>
+      <x:c r="U47" s="8"/>
+      <x:c r="V47" s="8"/>
+      <x:c r="W47" s="8"/>
       <x:c r="X47" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5108,9 +5006,9 @@
       <x:c r="R48" s="8" t="str"/>
       <x:c r="S48" s="8" t="str"/>
       <x:c r="T48" s="8" t="str"/>
-      <x:c r="U48" s="8" t="str"/>
-      <x:c r="V48" s="8" t="str"/>
-      <x:c r="W48" s="8" t="str"/>
+      <x:c r="U48" s="8"/>
+      <x:c r="V48" s="8"/>
+      <x:c r="W48" s="8"/>
       <x:c r="X48" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5191,9 +5089,9 @@
       <x:c r="R49" s="8" t="str"/>
       <x:c r="S49" s="8" t="str"/>
       <x:c r="T49" s="8" t="str"/>
-      <x:c r="U49" s="8" t="str"/>
-      <x:c r="V49" s="8" t="str"/>
-      <x:c r="W49" s="8" t="str"/>
+      <x:c r="U49" s="8"/>
+      <x:c r="V49" s="8"/>
+      <x:c r="W49" s="8"/>
       <x:c r="X49" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5274,9 +5172,9 @@
       <x:c r="R50" s="8" t="str"/>
       <x:c r="S50" s="8" t="str"/>
       <x:c r="T50" s="8" t="str"/>
-      <x:c r="U50" s="8" t="str"/>
-      <x:c r="V50" s="8" t="str"/>
-      <x:c r="W50" s="8" t="str"/>
+      <x:c r="U50" s="8"/>
+      <x:c r="V50" s="8"/>
+      <x:c r="W50" s="8"/>
       <x:c r="X50" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5357,9 +5255,9 @@
       <x:c r="R51" s="8" t="str"/>
       <x:c r="S51" s="8" t="str"/>
       <x:c r="T51" s="8" t="str"/>
-      <x:c r="U51" s="8" t="str"/>
-      <x:c r="V51" s="8" t="str"/>
-      <x:c r="W51" s="8" t="str"/>
+      <x:c r="U51" s="8"/>
+      <x:c r="V51" s="8"/>
+      <x:c r="W51" s="8"/>
       <x:c r="X51" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5440,9 +5338,9 @@
       <x:c r="R52" s="8" t="str"/>
       <x:c r="S52" s="8" t="str"/>
       <x:c r="T52" s="8" t="str"/>
-      <x:c r="U52" s="8" t="str"/>
-      <x:c r="V52" s="8" t="str"/>
-      <x:c r="W52" s="8" t="str"/>
+      <x:c r="U52" s="8"/>
+      <x:c r="V52" s="8"/>
+      <x:c r="W52" s="8"/>
       <x:c r="X52" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5523,9 +5421,9 @@
       <x:c r="R53" s="8" t="str"/>
       <x:c r="S53" s="8" t="str"/>
       <x:c r="T53" s="8" t="str"/>
-      <x:c r="U53" s="8" t="str"/>
-      <x:c r="V53" s="8" t="str"/>
-      <x:c r="W53" s="8" t="str"/>
+      <x:c r="U53" s="8"/>
+      <x:c r="V53" s="8"/>
+      <x:c r="W53" s="8"/>
       <x:c r="X53" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5606,9 +5504,9 @@
       <x:c r="R54" s="8" t="str"/>
       <x:c r="S54" s="8" t="str"/>
       <x:c r="T54" s="8" t="str"/>
-      <x:c r="U54" s="8" t="str"/>
-      <x:c r="V54" s="8" t="str"/>
-      <x:c r="W54" s="8" t="str"/>
+      <x:c r="U54" s="8"/>
+      <x:c r="V54" s="8"/>
+      <x:c r="W54" s="8"/>
       <x:c r="X54" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5695,9 +5593,9 @@
       <x:c r="R55" s="8" t="str"/>
       <x:c r="S55" s="8" t="str"/>
       <x:c r="T55" s="8" t="str"/>
-      <x:c r="U55" s="8" t="str"/>
-      <x:c r="V55" s="8" t="str"/>
-      <x:c r="W55" s="8" t="str"/>
+      <x:c r="U55" s="8"/>
+      <x:c r="V55" s="8"/>
+      <x:c r="W55" s="8"/>
       <x:c r="X55" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5778,9 +5676,9 @@
       <x:c r="R56" s="8" t="str"/>
       <x:c r="S56" s="8" t="str"/>
       <x:c r="T56" s="8" t="str"/>
-      <x:c r="U56" s="8" t="str"/>
-      <x:c r="V56" s="8" t="str"/>
-      <x:c r="W56" s="8" t="str"/>
+      <x:c r="U56" s="8"/>
+      <x:c r="V56" s="8"/>
+      <x:c r="W56" s="8"/>
       <x:c r="X56" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5861,9 +5759,9 @@
       <x:c r="R57" s="8" t="str"/>
       <x:c r="S57" s="8" t="str"/>
       <x:c r="T57" s="8" t="str"/>
-      <x:c r="U57" s="8" t="str"/>
-      <x:c r="V57" s="8" t="str"/>
-      <x:c r="W57" s="8" t="str"/>
+      <x:c r="U57" s="8"/>
+      <x:c r="V57" s="8"/>
+      <x:c r="W57" s="8"/>
       <x:c r="X57" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5944,9 +5842,9 @@
       <x:c r="R58" s="8" t="str"/>
       <x:c r="S58" s="8" t="str"/>
       <x:c r="T58" s="8" t="str"/>
-      <x:c r="U58" s="8" t="str"/>
-      <x:c r="V58" s="8" t="str"/>
-      <x:c r="W58" s="8" t="str"/>
+      <x:c r="U58" s="8"/>
+      <x:c r="V58" s="8"/>
+      <x:c r="W58" s="8"/>
       <x:c r="X58" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -6027,9 +5925,9 @@
       <x:c r="R59" s="8" t="str"/>
       <x:c r="S59" s="8" t="str"/>
       <x:c r="T59" s="8" t="str"/>
-      <x:c r="U59" s="8" t="str"/>
-      <x:c r="V59" s="8" t="str"/>
-      <x:c r="W59" s="8" t="str"/>
+      <x:c r="U59" s="8"/>
+      <x:c r="V59" s="8"/>
+      <x:c r="W59" s="8"/>
       <x:c r="X59" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -6110,9 +6008,9 @@
       <x:c r="R60" s="8" t="str"/>
       <x:c r="S60" s="8" t="str"/>
       <x:c r="T60" s="8" t="str"/>
-      <x:c r="U60" s="8" t="str"/>
-      <x:c r="V60" s="8" t="str"/>
-      <x:c r="W60" s="8" t="str"/>
+      <x:c r="U60" s="8"/>
+      <x:c r="V60" s="8"/>
+      <x:c r="W60" s="8"/>
       <x:c r="X60" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -6193,9 +6091,9 @@
       <x:c r="R61" s="8" t="str"/>
       <x:c r="S61" s="8" t="str"/>
       <x:c r="T61" s="8" t="str"/>
-      <x:c r="U61" s="8" t="str"/>
-      <x:c r="V61" s="8" t="str"/>
-      <x:c r="W61" s="8" t="str"/>
+      <x:c r="U61" s="8"/>
+      <x:c r="V61" s="8"/>
+      <x:c r="W61" s="8"/>
       <x:c r="X61" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -6282,9 +6180,9 @@
       <x:c r="R62" s="8" t="str"/>
       <x:c r="S62" s="8" t="str"/>
       <x:c r="T62" s="8" t="str"/>
-      <x:c r="U62" s="8" t="str"/>
-      <x:c r="V62" s="8" t="str"/>
-      <x:c r="W62" s="8" t="str"/>
+      <x:c r="U62" s="8"/>
+      <x:c r="V62" s="8"/>
+      <x:c r="W62" s="8"/>
       <x:c r="X62" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -6371,23 +6269,17 @@
       <x:c r="T63" s="7" t="str">
         <x:v>よみがえる光</x:v>
       </x:c>
-      <x:c r="U63" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">한 판에 한 번 본체가 체력 1칸으로 살아남아 50m 상승한다.
-성장 부활과 횟수를 공유하며 분신에게는 적용되지 않는다.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V63" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Survive one fatal hit with 1 HP per run.
-Rise 50m; shared with growth revival.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="W63" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1プレイに1回、本体が体力1で耐えて50m上昇。
-成長の復活と回数を共有。分身は対象外です。</x:t>
-        </x:is>
+      <x:c r="U63" s="7" t="str">
+        <x:v>한 판에 한 번 본체가 체력 1칸으로 살아남아 50m 상승한다
+성장 부활과 횟수를 공유하며 분신에게는 적용되지 않는다</x:v>
+      </x:c>
+      <x:c r="V63" s="7" t="str">
+        <x:v>Survive one fatal hit with 1 HP per run
+Rise 50m; shared with growth revival</x:v>
+      </x:c>
+      <x:c r="W63" s="7" t="str">
+        <x:v>1プレイに1回、本体が体力1で耐えて50m上昇
+成長の復活と回数を共有 分身は対象外です</x:v>
       </x:c>
       <x:c r="X63" s="18" t="n">
         <x:v>0</x:v>
@@ -6562,9 +6454,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re72ea5d673c540de"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5bc1cebba0064cfc"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b71c314de3e4450"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4adffb982036498b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/skin-chart-20260914/먹점프_스킨_뒤끝차트_v1.xlsx
+++ b/outputs/skin-chart-20260914/먹점프_스킨_뒤끝차트_v1.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skins" sheetId="1" r:id="Rcc0d6700e6e7441c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skins" sheetId="1" r:id="R9e163daf29974680"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -35,6 +35,7 @@
     <x:author>tc={66255747-19D8-4977-A106-BADE8FAEA2BF}</x:author>
     <x:author>tc={8C3BAA4A-9F87-44EA-BA69-A5525971EEA2}</x:author>
     <x:author>tc={73FEAC77-B7D7-4A7A-817A-021217EFBA01}</x:author>
+    <x:author>tc={8174B839-FAA8-4BAD-B3E0-E51D7C0BB970}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="A1" authorId="0">
@@ -287,6 +288,16 @@
         </x:r>
       </x:text>
     </x:comment>
+    <x:comment ref="Z1" authorId="25">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    고정: 해금 곡선 버전 2. 이 차트는 새 앱 버전에서 사용합니다. 구버전 앱에 전역 배포하지 마세요.</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
   </x:commentList>
 </x:comments>
 </file>
@@ -297,6 +308,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="0"/>
+  </x:numFmts>
   <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
@@ -331,7 +345,7 @@
       <x:name val="Apple SD Gothic Neo"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -358,6 +372,16 @@
         <x:fgColor rgb="FF282623"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F2EE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF282623"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -365,7 +389,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="21">
+  <x:cellXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -422,6 +446,20 @@
     </x:xf>
     <x:xf numFmtId="1" fontId="3" fillId="4" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -500,6 +538,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
+  <xltc:person displayName="먹점프" id="{310C0965-91AC-4914-B6F6-62383100E436}"/>
   <xltc:person displayName="tc={2839C758-B5E3-4BDB-8209-7F1C98458B5F}" id="{5AD4B75C-206E-9741-128C-4A5E1A720558}"/>
   <xltc:person displayName="tc={77D2D1B6-C0FB-4D97-89E4-B70A1F038A6D}" id="{C92261E9-AAA0-0F5C-CDA2-32B878CB565D}"/>
   <xltc:person displayName="tc={6B2C7035-D283-4953-AE18-3F2D3D1728E9}" id="{733C472E-03DA-5426-4BBB-893F95137D46}"/>
@@ -529,9 +568,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MukJumpSkinConfig" displayName="MukJumpSkinConfig" ref="A1:Y63" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:Y63"/>
-  <x:tableColumns count="25">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MukJumpSkinConfig" displayName="MukJumpSkinConfig" ref="A1:Z63" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:Z63"/>
+  <x:tableColumns count="26">
     <x:tableColumn id="1" name="schemaVersion"/>
     <x:tableColumn id="2" name="skinId"/>
     <x:tableColumn id="3" name="skinKey"/>
@@ -557,6 +596,7 @@
     <x:tableColumn id="23" name="abilityDescriptionJa"/>
     <x:tableColumn id="24" name="cooldownSeconds"/>
     <x:tableColumn id="25" name="assetKey"/>
+    <x:tableColumn id="26" name="unlockBalanceVersion"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -753,6 +793,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
+<xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
+  <xltc:threadedComment ref="Z1" dT="2026-09-21T13:53:09.793" personId="{310C0965-91AC-4914-B6F6-62383100E436}" id="{8174B839-FAA8-4BAD-B3E0-E51D7C0BB970}">
+    <xltc:text>고정: 해금 곡선 버전 2. 이 차트는 새 앱 버전에서 사용합니다. 구버전 앱에 전역 배포하지 마세요.</xltc:text>
+  </xltc:threadedComment>
+</xltc:ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
@@ -785,6 +833,7 @@
     <x:col min="23" max="23" width="54" customWidth="1"/>
     <x:col min="24" max="24" width="21" customWidth="1"/>
     <x:col min="25" max="25" width="33" customWidth="1"/>
+    <x:col min="26" max="26" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="38" customHeight="1">
@@ -913,6 +962,9 @@
           <x:t xml:space="preserve">assetKey</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z1" s="26" t="str">
+        <x:v>unlockBalanceVersion</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="76" customHeight="1">
       <x:c r="A2" s="17" t="n">
@@ -968,20 +1020,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N2" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">처음부터 사용 가능</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O2" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Available from the start</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P2" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">最初から使用可能</x:t>
-        </x:is>
+      <x:c r="N2" s="4" t="str">
+        <x:v>처음부터 사용 가능</x:v>
+      </x:c>
+      <x:c r="O2" s="4" t="str">
+        <x:v>Available from the start</x:v>
+      </x:c>
+      <x:c r="P2" s="4" t="str">
+        <x:v>最初から使用可能</x:v>
       </x:c>
       <x:c r="Q2" s="4" t="inlineStr">
         <x:is>
@@ -998,6 +1044,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Y2" s="4" t="str"/>
+      <x:c r="Z2" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="76" customHeight="1">
       <x:c r="A3" s="17" t="n">
@@ -1040,27 +1089,21 @@
         </x:is>
       </x:c>
       <x:c r="L3" s="19" t="n">
-        <x:v>100</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="M3" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N3" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">최고 고도 100m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O3" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reach 100m</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P3" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">最高高度100mに到達</x:t>
-        </x:is>
+      <x:c r="N3" s="4" t="str">
+        <x:v>최고 고도 500m 달성</x:v>
+      </x:c>
+      <x:c r="O3" s="4" t="str">
+        <x:v>Reach 500m</x:v>
+      </x:c>
+      <x:c r="P3" s="4" t="str">
+        <x:v>最高高度500mに到達</x:v>
       </x:c>
       <x:c r="Q3" s="4" t="inlineStr">
         <x:is>
@@ -1096,6 +1139,9 @@
           <x:t xml:space="preserve">skin_gat_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z3" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="76" customHeight="1">
       <x:c r="A4" s="17" t="n">
@@ -1138,27 +1184,21 @@
         </x:is>
       </x:c>
       <x:c r="L4" s="19" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M4" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N4" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">정상 플레이 10판 완료</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O4" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Finish 10 valid runs</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P4" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">通常プレイを10回完了</x:t>
-        </x:is>
+      <x:c r="N4" s="4" t="str">
+        <x:v>정상 플레이 20판 완료</x:v>
+      </x:c>
+      <x:c r="O4" s="4" t="str">
+        <x:v>Finish 20 valid runs</x:v>
+      </x:c>
+      <x:c r="P4" s="4" t="str">
+        <x:v>通常プレイを20回完了</x:v>
       </x:c>
       <x:c r="Q4" s="4" t="inlineStr">
         <x:is>
@@ -1194,6 +1234,9 @@
           <x:t xml:space="preserve">skin_spider_mask_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z4" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="76" customHeight="1">
       <x:c r="A5" s="17" t="n">
@@ -1243,20 +1286,14 @@
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N5" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">정상 플레이 1판 완료</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O5" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Finish 1 valid runs</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P5" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">通常プレイを1回完了</x:t>
-        </x:is>
+      <x:c r="N5" s="4" t="str">
+        <x:v>정상 플레이 1판 완료</x:v>
+      </x:c>
+      <x:c r="O5" s="4" t="str">
+        <x:v>Finish 1 valid runs</x:v>
+      </x:c>
+      <x:c r="P5" s="4" t="str">
+        <x:v>通常プレイを1回完了</x:v>
       </x:c>
       <x:c r="Q5" s="4" t="inlineStr">
         <x:is>
@@ -1277,6 +1314,9 @@
           <x:t xml:space="preserve">skin_first_ribbon_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z5" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="76" customHeight="1">
       <x:c r="A6" s="17" t="n">
@@ -1319,27 +1359,21 @@
         </x:is>
       </x:c>
       <x:c r="L6" s="19" t="n">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="M6" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N6" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">누적 고도 500m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O6" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Climb 500m in total</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P6" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">累計高度500mに到達</x:t>
-        </x:is>
+      <x:c r="N6" s="4" t="str">
+        <x:v>누적 고도 2500m 달성</x:v>
+      </x:c>
+      <x:c r="O6" s="4" t="str">
+        <x:v>Climb 2500m in total</x:v>
+      </x:c>
+      <x:c r="P6" s="4" t="str">
+        <x:v>累計高度2500mに到達</x:v>
       </x:c>
       <x:c r="Q6" s="4" t="inlineStr">
         <x:is>
@@ -1360,6 +1394,9 @@
           <x:t xml:space="preserve">skin_scholar_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z6" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="76" customHeight="1">
       <x:c r="A7" s="17" t="n">
@@ -1383,13 +1420,13 @@
         <x:v>墨の幽霊</x:v>
       </x:c>
       <x:c r="G7" s="7" t="str">
-        <x:v>그린 길은 밟지 않아</x:v>
+        <x:v>그린 길 없이 150, 반 분</x:v>
       </x:c>
       <x:c r="H7" s="7" t="str">
-        <x:v>Drawn paths? Not stepping there</x:v>
+        <x:v>No drawn paths, 150 and half a minute</x:v>
       </x:c>
       <x:c r="I7" s="7" t="str">
-        <x:v>描いた道は踏まないよ</x:v>
+        <x:v>描いた道なしで150、三十秒</x:v>
       </x:c>
       <x:c r="J7" s="4" t="inlineStr">
         <x:is>
@@ -1409,20 +1446,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N7" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">그린 발판에 착지하지 않고 한 판 완료</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O7" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Finish a run without landing on a drawn platform</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P7" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">描いた足場に着地せずプレイを終える</x:t>
-        </x:is>
+      <x:c r="N7" s="4" t="str">
+        <x:v>그린 발판에 착지 없이 150m·30초 이상 한 판 완료</x:v>
+      </x:c>
+      <x:c r="O7" s="4" t="str">
+        <x:v>Finish at 150m or higher after 30s without landing on a drawn platform</x:v>
+      </x:c>
+      <x:c r="P7" s="4" t="str">
+        <x:v>描いた足場に着地せず150m以上・30秒以上のプレイを完了</x:v>
       </x:c>
       <x:c r="Q7" s="4" t="inlineStr">
         <x:is>
@@ -1443,6 +1474,9 @@
           <x:t xml:space="preserve">skin_ink_ghost_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z7" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="76" customHeight="1">
       <x:c r="A8" s="17" t="n">
@@ -1491,27 +1525,21 @@
         </x:is>
       </x:c>
       <x:c r="L8" s="19" t="n">
-        <x:v>25</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="M8" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N8" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">최고 고도 25m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O8" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reach 25m</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P8" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">最高高度25mに到達</x:t>
-        </x:is>
+      <x:c r="N8" s="4" t="str">
+        <x:v>최고 고도 150m 달성</x:v>
+      </x:c>
+      <x:c r="O8" s="4" t="str">
+        <x:v>Reach 150m</x:v>
+      </x:c>
+      <x:c r="P8" s="4" t="str">
+        <x:v>最高高度150mに到達</x:v>
       </x:c>
       <x:c r="Q8" s="4" t="inlineStr">
         <x:is>
@@ -1532,6 +1560,9 @@
           <x:t xml:space="preserve">skin_bamboo_hat_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z8" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="76" customHeight="1">
       <x:c r="A9" s="17" t="n">
@@ -1580,27 +1611,21 @@
         </x:is>
       </x:c>
       <x:c r="L9" s="19" t="n">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="M9" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N9" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">그린 발판에 10회 착지</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O9" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Land on drawn platforms 10 times</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P9" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">描いた足場に10回着地</x:t>
-        </x:is>
+      <x:c r="N9" s="4" t="str">
+        <x:v>그린 발판에 40회 착지</x:v>
+      </x:c>
+      <x:c r="O9" s="4" t="str">
+        <x:v>Land on drawn platforms 40 times</x:v>
+      </x:c>
+      <x:c r="P9" s="4" t="str">
+        <x:v>描いた足場に40回着地</x:v>
       </x:c>
       <x:c r="Q9" s="4" t="inlineStr">
         <x:is>
@@ -1621,6 +1646,9 @@
           <x:t xml:space="preserve">skin_red_headband_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z9" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="76" customHeight="1">
       <x:c r="A10" s="17" t="n">
@@ -1663,27 +1691,21 @@
         </x:is>
       </x:c>
       <x:c r="L10" s="19" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="M10" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N10" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">정상 플레이 3판 완료</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O10" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Finish 3 valid runs</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P10" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">通常プレイを3回完了</x:t>
-        </x:is>
+      <x:c r="N10" s="4" t="str">
+        <x:v>정상 플레이 5판 완료</x:v>
+      </x:c>
+      <x:c r="O10" s="4" t="str">
+        <x:v>Finish 5 valid runs</x:v>
+      </x:c>
+      <x:c r="P10" s="4" t="str">
+        <x:v>通常プレイを5回完了</x:v>
       </x:c>
       <x:c r="Q10" s="4" t="inlineStr">
         <x:is>
@@ -1704,6 +1726,9 @@
           <x:t xml:space="preserve">skin_lotus_crown_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z10" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="76" customHeight="1">
       <x:c r="A11" s="17" t="n">
@@ -1752,27 +1777,21 @@
         </x:is>
       </x:c>
       <x:c r="L11" s="19" t="n">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="M11" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N11" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">먹방울 아이템 1회 획득</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O11" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Collect 1 Ink Drop items</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P11" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">墨滴アイテムを1回獲得</x:t>
-        </x:is>
+      <x:c r="N11" s="4" t="str">
+        <x:v>먹방울 아이템 10회 획득</x:v>
+      </x:c>
+      <x:c r="O11" s="4" t="str">
+        <x:v>Collect 10 Ink Drop items</x:v>
+      </x:c>
+      <x:c r="P11" s="4" t="str">
+        <x:v>墨滴アイテムを10回獲得</x:v>
       </x:c>
       <x:c r="Q11" s="4" t="inlineStr">
         <x:is>
@@ -1793,6 +1812,9 @@
           <x:t xml:space="preserve">skin_cat_ears_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z11" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="76" customHeight="1">
       <x:c r="A12" s="17" t="n">
@@ -1835,27 +1857,21 @@
         </x:is>
       </x:c>
       <x:c r="L12" s="19" t="n">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="M12" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N12" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">아이템 5회 획득</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O12" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Collect 5 items</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P12" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">アイテムを5回獲得</x:t>
-        </x:is>
+      <x:c r="N12" s="4" t="str">
+        <x:v>아이템 25회 획득</x:v>
+      </x:c>
+      <x:c r="O12" s="4" t="str">
+        <x:v>Collect 25 items</x:v>
+      </x:c>
+      <x:c r="P12" s="4" t="str">
+        <x:v>アイテムを25回獲得</x:v>
       </x:c>
       <x:c r="Q12" s="4" t="inlineStr">
         <x:is>
@@ -1876,6 +1892,9 @@
           <x:t xml:space="preserve">skin_bell_ribbon_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z12" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="76" customHeight="1">
       <x:c r="A13" s="17" t="n">
@@ -1918,27 +1937,21 @@
         </x:is>
       </x:c>
       <x:c r="L13" s="19" t="n">
-        <x:v>50</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="M13" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N13" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">최고 고도 50m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O13" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reach 50m</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P13" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">最高高度50mに到達</x:t>
-        </x:is>
+      <x:c r="N13" s="4" t="str">
+        <x:v>최고 고도 400m 달성</x:v>
+      </x:c>
+      <x:c r="O13" s="4" t="str">
+        <x:v>Reach 400m</x:v>
+      </x:c>
+      <x:c r="P13" s="4" t="str">
+        <x:v>最高高度400mに到達</x:v>
       </x:c>
       <x:c r="Q13" s="4" t="inlineStr">
         <x:is>
@@ -1959,6 +1972,9 @@
           <x:t xml:space="preserve">skin_cloud_cap_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z13" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="76" customHeight="1">
       <x:c r="A14" s="17" t="n">
@@ -2001,27 +2017,21 @@
         </x:is>
       </x:c>
       <x:c r="L14" s="19" t="n">
-        <x:v>1000</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="M14" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N14" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">누적 고도 1000m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O14" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Climb 1000m in total</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P14" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">累計高度1000mに到達</x:t>
-        </x:is>
+      <x:c r="N14" s="4" t="str">
+        <x:v>누적 고도 7500m 달성</x:v>
+      </x:c>
+      <x:c r="O14" s="4" t="str">
+        <x:v>Climb 7500m in total</x:v>
+      </x:c>
+      <x:c r="P14" s="4" t="str">
+        <x:v>累計高度7500mに到達</x:v>
       </x:c>
       <x:c r="Q14" s="4" t="inlineStr">
         <x:is>
@@ -2042,6 +2052,9 @@
           <x:t xml:space="preserve">skin_paper_boat_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z14" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="76" customHeight="1">
       <x:c r="A15" s="17" t="n">
@@ -2084,27 +2097,21 @@
         </x:is>
       </x:c>
       <x:c r="L15" s="19" t="n">
-        <x:v>45</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="M15" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N15" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">한 판에서 45초 생존</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O15" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Survive 45s in one run</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P15" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1回のプレイで45秒生存</x:t>
-        </x:is>
+      <x:c r="N15" s="4" t="str">
+        <x:v>한 판에서 120초 생존</x:v>
+      </x:c>
+      <x:c r="O15" s="4" t="str">
+        <x:v>Survive 120s in one run</x:v>
+      </x:c>
+      <x:c r="P15" s="4" t="str">
+        <x:v>1回のプレイで120秒生存</x:v>
       </x:c>
       <x:c r="Q15" s="4" t="inlineStr">
         <x:is>
@@ -2125,6 +2132,9 @@
           <x:t xml:space="preserve">skin_tea_cup_hat_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z15" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="76" customHeight="1">
       <x:c r="A16" s="17" t="n">
@@ -2167,27 +2177,21 @@
         </x:is>
       </x:c>
       <x:c r="L16" s="19" t="n">
-        <x:v>25</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="M16" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N16" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">그린 발판에 25회 착지</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O16" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Land on drawn platforms 25 times</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P16" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">描いた足場に25回着地</x:t>
-        </x:is>
+      <x:c r="N16" s="4" t="str">
+        <x:v>그린 발판에 300회 착지</x:v>
+      </x:c>
+      <x:c r="O16" s="4" t="str">
+        <x:v>Land on drawn platforms 300 times</x:v>
+      </x:c>
+      <x:c r="P16" s="4" t="str">
+        <x:v>描いた足場に300回着地</x:v>
       </x:c>
       <x:c r="Q16" s="4" t="inlineStr">
         <x:is>
@@ -2208,6 +2212,9 @@
           <x:t xml:space="preserve">skin_feather_hairpin_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z16" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="76" customHeight="1">
       <x:c r="A17" s="17" t="n">
@@ -2256,27 +2263,21 @@
         </x:is>
       </x:c>
       <x:c r="L17" s="19" t="n">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="M17" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N17" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">정상 플레이 5판 완료</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O17" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Finish 5 valid runs</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P17" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">通常プレイを5回完了</x:t>
-        </x:is>
+      <x:c r="N17" s="4" t="str">
+        <x:v>정상 플레이 12판 완료</x:v>
+      </x:c>
+      <x:c r="O17" s="4" t="str">
+        <x:v>Finish 12 valid runs</x:v>
+      </x:c>
+      <x:c r="P17" s="4" t="str">
+        <x:v>通常プレイを12回完了</x:v>
       </x:c>
       <x:c r="Q17" s="4" t="inlineStr">
         <x:is>
@@ -2297,6 +2298,9 @@
           <x:t xml:space="preserve">skin_peach_flower_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z17" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="76" customHeight="1">
       <x:c r="A18" s="17" t="n">
@@ -2339,27 +2343,21 @@
         </x:is>
       </x:c>
       <x:c r="L18" s="19" t="n">
-        <x:v>250</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="M18" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N18" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">최고 고도 250m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O18" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reach 250m</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P18" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">最高高度250mに到達</x:t>
-        </x:is>
+      <x:c r="N18" s="4" t="str">
+        <x:v>최고 고도 800m 달성</x:v>
+      </x:c>
+      <x:c r="O18" s="4" t="str">
+        <x:v>Reach 800m</x:v>
+      </x:c>
+      <x:c r="P18" s="4" t="str">
+        <x:v>最高高度800mに到達</x:v>
       </x:c>
       <x:c r="Q18" s="4" t="inlineStr">
         <x:is>
@@ -2380,6 +2378,9 @@
           <x:t xml:space="preserve">skin_fox_mask_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z18" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="76" customHeight="1">
       <x:c r="A19" s="17" t="n">
@@ -2422,27 +2423,21 @@
         </x:is>
       </x:c>
       <x:c r="L19" s="19" t="n">
-        <x:v>5000</x:v>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="M19" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N19" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">누적 고도 5000m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O19" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Climb 5000m in total</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P19" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">累計高度5000mに到達</x:t>
-        </x:is>
+      <x:c r="N19" s="4" t="str">
+        <x:v>누적 고도 35000m 달성</x:v>
+      </x:c>
+      <x:c r="O19" s="4" t="str">
+        <x:v>Climb 35000m in total</x:v>
+      </x:c>
+      <x:c r="P19" s="4" t="str">
+        <x:v>累計高度35000mに到達</x:v>
       </x:c>
       <x:c r="Q19" s="4" t="inlineStr">
         <x:is>
@@ -2463,6 +2458,9 @@
           <x:t xml:space="preserve">skin_crane_crest_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z19" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="76" customHeight="1">
       <x:c r="A20" s="17" t="n">
@@ -2505,27 +2503,21 @@
         </x:is>
       </x:c>
       <x:c r="L20" s="19" t="n">
-        <x:v>500</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="M20" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N20" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">최고 고도 500m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O20" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reach 500m</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P20" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">最高高度500mに到達</x:t>
-        </x:is>
+      <x:c r="N20" s="4" t="str">
+        <x:v>최고 고도 2000m 달성</x:v>
+      </x:c>
+      <x:c r="O20" s="4" t="str">
+        <x:v>Reach 2000m</x:v>
+      </x:c>
+      <x:c r="P20" s="4" t="str">
+        <x:v>最高高度2000mに到達</x:v>
       </x:c>
       <x:c r="Q20" s="4" t="inlineStr">
         <x:is>
@@ -2561,6 +2553,9 @@
           <x:t xml:space="preserve">skin_yaksha_mask_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z20" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="76" customHeight="1">
       <x:c r="A21" s="17" t="n">
@@ -2603,27 +2598,21 @@
         </x:is>
       </x:c>
       <x:c r="L21" s="19" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="M21" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N21" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">먹 3마리 동시 생존</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O21" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Keep 3 Inks alive together</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P21" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">墨3体が同時に生存</x:t>
-        </x:is>
+      <x:c r="N21" s="4" t="str">
+        <x:v>먹 8마리 동시 생존</x:v>
+      </x:c>
+      <x:c r="O21" s="4" t="str">
+        <x:v>Keep 8 Inks alive together</x:v>
+      </x:c>
+      <x:c r="P21" s="4" t="str">
+        <x:v>墨8体が同時に生存</x:v>
       </x:c>
       <x:c r="Q21" s="4" t="inlineStr">
         <x:is>
@@ -2659,6 +2648,9 @@
           <x:t xml:space="preserve">skin_turtle_shell_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z21" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="76" customHeight="1">
       <x:c r="A22" s="17" t="n">
@@ -2701,27 +2693,21 @@
         </x:is>
       </x:c>
       <x:c r="L22" s="19" t="n">
-        <x:v>100</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="M22" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N22" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">밤에 100m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O22" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reach 100m at night</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P22" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">夜に100m到達</x:t>
-        </x:is>
+      <x:c r="N22" s="4" t="str">
+        <x:v>밤에 600m 달성</x:v>
+      </x:c>
+      <x:c r="O22" s="4" t="str">
+        <x:v>Reach 600m at night</x:v>
+      </x:c>
+      <x:c r="P22" s="4" t="str">
+        <x:v>夜に600m到達</x:v>
       </x:c>
       <x:c r="Q22" s="4" t="inlineStr">
         <x:is>
@@ -2742,6 +2728,9 @@
           <x:t xml:space="preserve">skin_moon_crown_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z22" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="76" customHeight="1">
       <x:c r="A23" s="17" t="n">
@@ -2784,27 +2773,21 @@
         </x:is>
       </x:c>
       <x:c r="L23" s="19" t="n">
-        <x:v>100</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="M23" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N23" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">그린 발판에 100회 착지</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O23" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Land on drawn platforms 100 times</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P23" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">描いた足場に100回着地</x:t>
-        </x:is>
+      <x:c r="N23" s="4" t="str">
+        <x:v>그린 발판에 1000회 착지</x:v>
+      </x:c>
+      <x:c r="O23" s="4" t="str">
+        <x:v>Land on drawn platforms 1000 times</x:v>
+      </x:c>
+      <x:c r="P23" s="4" t="str">
+        <x:v>描いた足場に1000回着地</x:v>
       </x:c>
       <x:c r="Q23" s="4" t="inlineStr">
         <x:is>
@@ -2825,6 +2808,9 @@
           <x:t xml:space="preserve">skin_brush_master_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z23" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="76" customHeight="1">
       <x:c r="A24" s="17" t="n">
@@ -2867,27 +2853,21 @@
         </x:is>
       </x:c>
       <x:c r="L24" s="19" t="n">
-        <x:v>30</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="M24" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N24" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">아이템 30회 획득</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O24" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Collect 30 items</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P24" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">アイテムを30回獲得</x:t>
-        </x:is>
+      <x:c r="N24" s="4" t="str">
+        <x:v>아이템 200회 획득</x:v>
+      </x:c>
+      <x:c r="O24" s="4" t="str">
+        <x:v>Collect 200 items</x:v>
+      </x:c>
+      <x:c r="P24" s="4" t="str">
+        <x:v>アイテムを200回獲得</x:v>
       </x:c>
       <x:c r="Q24" s="4" t="inlineStr">
         <x:is>
@@ -2923,6 +2903,9 @@
           <x:t xml:space="preserve">skin_spirit_halo_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z24" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="76" customHeight="1">
       <x:c r="A25" s="17" t="n">
@@ -2971,27 +2954,21 @@
         </x:is>
       </x:c>
       <x:c r="L25" s="19" t="n">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="M25" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N25" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">성장 노드 5개 획득</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O25" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Own 5 growth nodes</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P25" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">成長ノードを5個獲得</x:t>
-        </x:is>
+      <x:c r="N25" s="4" t="str">
+        <x:v>성장 노드 12개 획득</x:v>
+      </x:c>
+      <x:c r="O25" s="4" t="str">
+        <x:v>Own 12 growth nodes</x:v>
+      </x:c>
+      <x:c r="P25" s="4" t="str">
+        <x:v>成長ノードを12個獲得</x:v>
       </x:c>
       <x:c r="Q25" s="4" t="inlineStr">
         <x:is>
@@ -3012,6 +2989,9 @@
           <x:t xml:space="preserve">skin_koi_mask_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z25" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="76" customHeight="1">
       <x:c r="A26" s="17" t="n">
@@ -3054,27 +3034,21 @@
         </x:is>
       </x:c>
       <x:c r="L26" s="19" t="n">
-        <x:v>10000</x:v>
+        <x:v>75000</x:v>
       </x:c>
       <x:c r="M26" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N26" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">누적 고도 10000m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O26" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Climb 10000m in total</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P26" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">累計高度10000mに到達</x:t>
-        </x:is>
+      <x:c r="N26" s="4" t="str">
+        <x:v>누적 고도 75000m 달성</x:v>
+      </x:c>
+      <x:c r="O26" s="4" t="str">
+        <x:v>Climb 75000m in total</x:v>
+      </x:c>
+      <x:c r="P26" s="4" t="str">
+        <x:v>累計高度75000mに到達</x:v>
       </x:c>
       <x:c r="Q26" s="4" t="inlineStr">
         <x:is>
@@ -3095,6 +3069,9 @@
           <x:t xml:space="preserve">skin_jade_crown_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z26" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="76" customHeight="1">
       <x:c r="A27" s="17" t="n">
@@ -3137,27 +3114,21 @@
         </x:is>
       </x:c>
       <x:c r="L27" s="19" t="n">
-        <x:v>1000</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="M27" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N27" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">최고 고도 1000m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O27" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reach 1000m</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P27" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">最高高度1000mに到達</x:t>
-        </x:is>
+      <x:c r="N27" s="4" t="str">
+        <x:v>최고 고도 4000m 달성</x:v>
+      </x:c>
+      <x:c r="O27" s="4" t="str">
+        <x:v>Reach 4000m</x:v>
+      </x:c>
+      <x:c r="P27" s="4" t="str">
+        <x:v>最高高度4000mに到達</x:v>
       </x:c>
       <x:c r="Q27" s="4" t="inlineStr">
         <x:is>
@@ -3193,6 +3164,9 @@
           <x:t xml:space="preserve">skin_phoenix_crown_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z27" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="76" customHeight="1">
       <x:c r="A28" s="17" t="n">
@@ -3235,27 +3209,21 @@
         </x:is>
       </x:c>
       <x:c r="L28" s="19" t="n">
-        <x:v>300</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="M28" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N28" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">아이템 없이 300m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O28" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reach 300m without items</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P28" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">アイテムなしで300m到達</x:t>
-        </x:is>
+      <x:c r="N28" s="4" t="str">
+        <x:v>아이템 없이 750m 달성</x:v>
+      </x:c>
+      <x:c r="O28" s="4" t="str">
+        <x:v>Reach 750m without items</x:v>
+      </x:c>
+      <x:c r="P28" s="4" t="str">
+        <x:v>アイテムなしで750m到達</x:v>
       </x:c>
       <x:c r="Q28" s="4" t="inlineStr">
         <x:is>
@@ -3276,6 +3244,9 @@
           <x:t xml:space="preserve">skin_tiger_mask_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z28" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="76" customHeight="1">
       <x:c r="A29" s="17" t="n">
@@ -3318,27 +3289,21 @@
         </x:is>
       </x:c>
       <x:c r="L29" s="19" t="n">
-        <x:v>1500</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="M29" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N29" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">최고 고도 1500m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O29" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reach 1500m</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P29" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">最高高度1500mに到達</x:t>
-        </x:is>
+      <x:c r="N29" s="4" t="str">
+        <x:v>최고 고도 6500m 달성</x:v>
+      </x:c>
+      <x:c r="O29" s="4" t="str">
+        <x:v>Reach 6500m</x:v>
+      </x:c>
+      <x:c r="P29" s="4" t="str">
+        <x:v>最高高度6500mに到達</x:v>
       </x:c>
       <x:c r="Q29" s="4" t="inlineStr">
         <x:is>
@@ -3359,6 +3324,9 @@
           <x:t xml:space="preserve">skin_mountain_king_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z29" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="76" customHeight="1">
       <x:c r="A30" s="17" t="n">
@@ -3401,27 +3369,21 @@
         </x:is>
       </x:c>
       <x:c r="L30" s="19" t="n">
-        <x:v>2000</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="M30" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N30" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">최고 고도 2000m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O30" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reach 2000m</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P30" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">最高高度2000mに到達</x:t>
-        </x:is>
+      <x:c r="N30" s="4" t="str">
+        <x:v>최고 고도 10000m 달성</x:v>
+      </x:c>
+      <x:c r="O30" s="4" t="str">
+        <x:v>Reach 10000m</x:v>
+      </x:c>
+      <x:c r="P30" s="4" t="str">
+        <x:v>最高高度10000mに到達</x:v>
       </x:c>
       <x:c r="Q30" s="4" t="inlineStr">
         <x:is>
@@ -3442,6 +3404,9 @@
           <x:t xml:space="preserve">skin_cloud_dragon_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z30" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="76" customHeight="1">
       <x:c r="A31" s="17" t="n">
@@ -3484,27 +3449,21 @@
         </x:is>
       </x:c>
       <x:c r="L31" s="19" t="n">
-        <x:v>100</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="M31" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N31" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">정상 플레이 100판 완료</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O31" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Finish 100 valid runs</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P31" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">通常プレイを100回完了</x:t>
-        </x:is>
+      <x:c r="N31" s="4" t="str">
+        <x:v>정상 플레이 150판 완료</x:v>
+      </x:c>
+      <x:c r="O31" s="4" t="str">
+        <x:v>Finish 150 valid runs</x:v>
+      </x:c>
+      <x:c r="P31" s="4" t="str">
+        <x:v>通常プレイを150回完了</x:v>
       </x:c>
       <x:c r="Q31" s="4" t="inlineStr">
         <x:is>
@@ -3525,6 +3484,9 @@
           <x:t xml:space="preserve">skin_ink_mecha_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z31" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="76" customHeight="1">
       <x:c r="A32" s="17" t="n">
@@ -3580,20 +3542,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N32" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">로비를 세 번째 밤으로 바꾸기</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O32" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bring on the third night in the lobby</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P32" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ロビーで三度目の夜を迎える</x:t>
-        </x:is>
+      <x:c r="N32" s="4" t="str">
+        <x:v>로비를 세 번째 밤으로 바꾸기</x:v>
+      </x:c>
+      <x:c r="O32" s="4" t="str">
+        <x:v>Bring on the third night in the lobby</x:v>
+      </x:c>
+      <x:c r="P32" s="4" t="str">
+        <x:v>ロビーで三度目の夜を迎える</x:v>
       </x:c>
       <x:c r="Q32" s="4" t="inlineStr">
         <x:is>
@@ -3614,6 +3570,9 @@
           <x:t xml:space="preserve">skin_night_bat_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z32" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="76" customHeight="1">
       <x:c r="A33" s="17" t="n">
@@ -3669,20 +3628,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N33" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">낮과 밤을 여섯 번 바꾸기</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O33" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Switch day and night six times</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P33" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">昼と夜を6回切り替える</x:t>
-        </x:is>
+      <x:c r="N33" s="4" t="str">
+        <x:v>낮과 밤을 여섯 번 바꾸기</x:v>
+      </x:c>
+      <x:c r="O33" s="4" t="str">
+        <x:v>Switch day and night six times</x:v>
+      </x:c>
+      <x:c r="P33" s="4" t="str">
+        <x:v>昼と夜を6回切り替える</x:v>
       </x:c>
       <x:c r="Q33" s="4" t="inlineStr">
         <x:is>
@@ -3703,6 +3656,9 @@
           <x:t xml:space="preserve">skin_astronaut_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z33" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="76" customHeight="1">
       <x:c r="A34" s="17" t="n">
@@ -3732,13 +3688,13 @@
         </x:is>
       </x:c>
       <x:c r="G34" s="7" t="str">
-        <x:v>밤고양이는 60초째 빈손</x:v>
+        <x:v>밤고양이, 빈손으로 400과 이 분</x:v>
       </x:c>
       <x:c r="H34" s="7" t="str">
-        <x:v>Night cat, empty paws for 60s</x:v>
+        <x:v>Night cat, empty paws, 400 and two minutes</x:v>
       </x:c>
       <x:c r="I34" s="7" t="str">
-        <x:v>夜の猫、60秒ずっと手ぶら</x:v>
+        <x:v>夜の猫、手ぶらで400と二分</x:v>
       </x:c>
       <x:c r="J34" s="4" t="inlineStr">
         <x:is>
@@ -3758,20 +3714,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N34" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">고양이 귀로 밤에 아이템 없이 60초 생존</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O34" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cat Ears: survive 60s at night without items</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P34" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">猫耳で夜にアイテムなしで60秒生存</x:t>
-        </x:is>
+      <x:c r="N34" s="4" t="str">
+        <x:v>고양이 귀로 밤에 아이템 없이 400m·120초 이상 한 판 완료</x:v>
+      </x:c>
+      <x:c r="O34" s="4" t="str">
+        <x:v>Cat Ears: finish a night run at 400m or higher after 120s with no items</x:v>
+      </x:c>
+      <x:c r="P34" s="4" t="str">
+        <x:v>猫耳で夜にアイテムなしで400m以上・120秒以上のプレイを完了</x:v>
       </x:c>
       <x:c r="Q34" s="4" t="inlineStr">
         <x:is>
@@ -3792,6 +3742,9 @@
           <x:t xml:space="preserve">skin_clockwork_cat_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z34" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="76" customHeight="1">
       <x:c r="A35" s="17" t="n">
@@ -3847,20 +3800,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N35" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">정확히 777m로 한 판 완료</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O35" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Finish a run at exactly 777m</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P35" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ちょうど777mでプレイを終える</x:t>
-        </x:is>
+      <x:c r="N35" s="4" t="str">
+        <x:v>정확히 777m로 한 판 완료</x:v>
+      </x:c>
+      <x:c r="O35" s="4" t="str">
+        <x:v>Finish a run at exactly 777m</x:v>
+      </x:c>
+      <x:c r="P35" s="4" t="str">
+        <x:v>ちょうど777mでプレイを終える</x:v>
       </x:c>
       <x:c r="Q35" s="4" t="inlineStr">
         <x:is>
@@ -3881,6 +3828,9 @@
           <x:t xml:space="preserve">skin_lucky_dice_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z35" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="76" customHeight="1">
       <x:c r="A36" s="17" t="n">
@@ -3929,27 +3879,21 @@
         </x:is>
       </x:c>
       <x:c r="L36" s="19" t="n">
-        <x:v>120</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="M36" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N36" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">한 판에서 120초 생존</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O36" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Survive 120s in one run</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P36" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1回のプレイで120秒生存</x:t>
-        </x:is>
+      <x:c r="N36" s="4" t="str">
+        <x:v>한 판에서 300초 생존</x:v>
+      </x:c>
+      <x:c r="O36" s="4" t="str">
+        <x:v>Survive 300s in one run</x:v>
+      </x:c>
+      <x:c r="P36" s="4" t="str">
+        <x:v>1回のプレイで300秒生存</x:v>
       </x:c>
       <x:c r="Q36" s="4" t="inlineStr">
         <x:is>
@@ -3970,6 +3914,9 @@
           <x:t xml:space="preserve">skin_origami_wings_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z36" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="76" customHeight="1">
       <x:c r="A37" s="17" t="n">
@@ -4012,27 +3959,21 @@
         </x:is>
       </x:c>
       <x:c r="L37" s="19" t="n">
-        <x:v>350</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="M37" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N37" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">최고 고도 350m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O37" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reach 350m</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P37" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">最高高度350mに到達</x:t>
-        </x:is>
+      <x:c r="N37" s="4" t="str">
+        <x:v>최고 고도 1200m 달성</x:v>
+      </x:c>
+      <x:c r="O37" s="4" t="str">
+        <x:v>Reach 1200m</x:v>
+      </x:c>
+      <x:c r="P37" s="4" t="str">
+        <x:v>最高高度1200mに到達</x:v>
       </x:c>
       <x:c r="Q37" s="4" t="inlineStr">
         <x:is>
@@ -4053,6 +3994,9 @@
           <x:t xml:space="preserve">skin_crane_wings_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z37" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="76" customHeight="1">
       <x:c r="A38" s="17" t="n">
@@ -4095,27 +4039,21 @@
         </x:is>
       </x:c>
       <x:c r="L38" s="19" t="n">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="M38" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N38" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">아이템 50회 획득</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O38" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Collect 50 items</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P38" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">アイテムを50回獲得</x:t>
-        </x:is>
+      <x:c r="N38" s="4" t="str">
+        <x:v>아이템 500회 획득</x:v>
+      </x:c>
+      <x:c r="O38" s="4" t="str">
+        <x:v>Collect 500 items</x:v>
+      </x:c>
+      <x:c r="P38" s="4" t="str">
+        <x:v>アイテムを500回獲得</x:v>
       </x:c>
       <x:c r="Q38" s="4" t="inlineStr">
         <x:is>
@@ -4136,6 +4074,9 @@
           <x:t xml:space="preserve">skin_butterfly_wings_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z38" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="76" customHeight="1">
       <x:c r="A39" s="17" t="n">
@@ -4184,27 +4125,21 @@
         </x:is>
       </x:c>
       <x:c r="L39" s="19" t="n">
-        <x:v>15</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="M39" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N39" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">그린 발판에 15회 착지</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O39" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Land on drawn platforms 15 times</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P39" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">描いた足場に15回着地</x:t>
-        </x:is>
+      <x:c r="N39" s="4" t="str">
+        <x:v>그린 발판에 120회 착지</x:v>
+      </x:c>
+      <x:c r="O39" s="4" t="str">
+        <x:v>Land on drawn platforms 120 times</x:v>
+      </x:c>
+      <x:c r="P39" s="4" t="str">
+        <x:v>描いた足場に120回着地</x:v>
       </x:c>
       <x:c r="Q39" s="4" t="inlineStr">
         <x:is>
@@ -4225,6 +4160,9 @@
           <x:t xml:space="preserve">skin_red_shoes_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z39" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="76" customHeight="1">
       <x:c r="A40" s="17" t="n">
@@ -4267,27 +4205,21 @@
         </x:is>
       </x:c>
       <x:c r="L40" s="19" t="n">
-        <x:v>3000</x:v>
+        <x:v>18000</x:v>
       </x:c>
       <x:c r="M40" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N40" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">누적 고도 3000m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O40" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Climb 3000m in total</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P40" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">累計高度3000mに到達</x:t>
-        </x:is>
+      <x:c r="N40" s="4" t="str">
+        <x:v>누적 고도 18000m 달성</x:v>
+      </x:c>
+      <x:c r="O40" s="4" t="str">
+        <x:v>Climb 18000m in total</x:v>
+      </x:c>
+      <x:c r="P40" s="4" t="str">
+        <x:v>累計高度18000mに到達</x:v>
       </x:c>
       <x:c r="Q40" s="4" t="inlineStr">
         <x:is>
@@ -4323,6 +4255,9 @@
           <x:t xml:space="preserve">skin_cloud_boots_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z40" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="76" customHeight="1">
       <x:c r="A41" s="17" t="n">
@@ -4365,27 +4300,21 @@
         </x:is>
       </x:c>
       <x:c r="L41" s="19" t="n">
-        <x:v>20</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="M41" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N41" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">먹방울 아이템 20회 획득</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O41" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Collect 20 Ink Drop items</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P41" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">墨滴アイテムを20回獲得</x:t>
-        </x:is>
+      <x:c r="N41" s="4" t="str">
+        <x:v>먹방울 아이템 150회 획득</x:v>
+      </x:c>
+      <x:c r="O41" s="4" t="str">
+        <x:v>Collect 150 Ink Drop items</x:v>
+      </x:c>
+      <x:c r="P41" s="4" t="str">
+        <x:v>墨滴アイテムを150回獲得</x:v>
       </x:c>
       <x:c r="Q41" s="4" t="inlineStr">
         <x:is>
@@ -4406,6 +4335,9 @@
           <x:t xml:space="preserve">skin_blue_wisps_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z41" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="76" customHeight="1">
       <x:c r="A42" s="17" t="n">
@@ -4448,27 +4380,21 @@
         </x:is>
       </x:c>
       <x:c r="L42" s="19" t="n">
-        <x:v>7</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="M42" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N42" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">정상 플레이 7판 완료</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O42" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Finish 7 valid runs</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P42" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">通常プレイを7回完了</x:t>
-        </x:is>
+      <x:c r="N42" s="4" t="str">
+        <x:v>정상 플레이 35판 완료</x:v>
+      </x:c>
+      <x:c r="O42" s="4" t="str">
+        <x:v>Finish 35 valid runs</x:v>
+      </x:c>
+      <x:c r="P42" s="4" t="str">
+        <x:v>通常プレイを35回完了</x:v>
       </x:c>
       <x:c r="Q42" s="4" t="inlineStr">
         <x:is>
@@ -4489,6 +4415,9 @@
           <x:t xml:space="preserve">skin_paper_lanterns_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z42" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="76" customHeight="1">
       <x:c r="A43" s="17" t="n">
@@ -4531,27 +4460,21 @@
         </x:is>
       </x:c>
       <x:c r="L43" s="19" t="n">
-        <x:v>200</x:v>
+        <x:v>1600</x:v>
       </x:c>
       <x:c r="M43" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N43" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">밤에 200m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O43" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reach 200m at night</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P43" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">夜に200m到達</x:t>
-        </x:is>
+      <x:c r="N43" s="4" t="str">
+        <x:v>밤에 1600m 달성</x:v>
+      </x:c>
+      <x:c r="O43" s="4" t="str">
+        <x:v>Reach 1600m at night</x:v>
+      </x:c>
+      <x:c r="P43" s="4" t="str">
+        <x:v>夜に1600m到達</x:v>
       </x:c>
       <x:c r="Q43" s="4" t="inlineStr">
         <x:is>
@@ -4572,6 +4495,9 @@
           <x:t xml:space="preserve">skin_moon_clouds_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z43" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="76" customHeight="1">
       <x:c r="A44" s="17" t="n">
@@ -4621,20 +4547,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N44" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Apple 계정 연동 완료</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O44" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Link your Apple account</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P44" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Appleアカウントを連携</x:t>
-        </x:is>
+      <x:c r="N44" s="4" t="str">
+        <x:v>Apple 계정 연동 완료</x:v>
+      </x:c>
+      <x:c r="O44" s="4" t="str">
+        <x:v>Link your Apple account</x:v>
+      </x:c>
+      <x:c r="P44" s="4" t="str">
+        <x:v>Appleアカウントを連携</x:v>
       </x:c>
       <x:c r="Q44" s="4" t="inlineStr">
         <x:is>
@@ -4670,6 +4590,9 @@
           <x:t xml:space="preserve">skin_bond_knot_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z44" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="76" customHeight="1">
       <x:c r="A45" s="17" t="n">
@@ -4712,27 +4635,21 @@
         </x:is>
       </x:c>
       <x:c r="L45" s="19" t="n">
-        <x:v>5</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M45" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N45" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">먹방울 아이템 5회 획득</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O45" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Collect 5 Ink Drop items</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P45" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">墨滴アイテムを5回獲得</x:t>
-        </x:is>
+      <x:c r="N45" s="4" t="str">
+        <x:v>먹방울 아이템 50회 획득</x:v>
+      </x:c>
+      <x:c r="O45" s="4" t="str">
+        <x:v>Collect 50 Ink Drop items</x:v>
+      </x:c>
+      <x:c r="P45" s="4" t="str">
+        <x:v>墨滴アイテムを50回獲得</x:v>
       </x:c>
       <x:c r="Q45" s="4" t="inlineStr">
         <x:is>
@@ -4768,6 +4685,9 @@
           <x:t xml:space="preserve">skin_wind_fan_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z45" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="76" customHeight="1">
       <x:c r="A46" s="17" t="n">
@@ -4810,27 +4730,21 @@
         </x:is>
       </x:c>
       <x:c r="L46" s="17" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="M46" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N46" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">본체가 용과 충돌해 사망하기</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O46" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Let the original Ink die from a dragon collision</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P46" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">本体が竜との衝突で倒れる</x:t>
-        </x:is>
+      <x:c r="N46" s="4" t="str">
+        <x:v>본체가 용과 충돌해 사망한 판 3회 완료</x:v>
+      </x:c>
+      <x:c r="O46" s="4" t="str">
+        <x:v>Finish 3 runs where the original Ink dies from a dragon collision</x:v>
+      </x:c>
+      <x:c r="P46" s="4" t="str">
+        <x:v>本体が竜との衝突で倒れたプレイを3回完了</x:v>
       </x:c>
       <x:c r="Q46" s="4" t="inlineStr">
         <x:is>
@@ -4851,6 +4765,9 @@
           <x:t xml:space="preserve">skin_dragon_tail_v2</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z46" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="76" customHeight="1">
       <x:c r="A47" s="17" t="n">
@@ -4874,13 +4791,13 @@
         <x:v>夜ねずみ</x:v>
       </x:c>
       <x:c r="G47" s="7" t="str">
-        <x:v>밤참 세 개, 50만큼</x:v>
+        <x:v>밤의 파수꾼, 밤참 여덟 개</x:v>
       </x:c>
       <x:c r="H47" s="7" t="str">
-        <x:v>Three night snacks, up to 50</x:v>
+        <x:v>Night watcher, eight night snacks</x:v>
       </x:c>
       <x:c r="I47" s="7" t="str">
-        <x:v>夜食は三つ、50まで</x:v>
+        <x:v>夜の番人、夜食は八つ</x:v>
       </x:c>
       <x:c r="J47" s="4" t="inlineStr">
         <x:is>
@@ -4900,20 +4817,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N47" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">밤 한 판에서 아이템 3개와 50m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O47" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">In one night run, collect 3 items and reach 50m</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P47" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">夜の1プレイでアイテム3個と50m達成</x:t>
-        </x:is>
+      <x:c r="N47" s="4" t="str">
+        <x:v>밤의 파수꾼으로 밤 한 판에서 아이템 8개·500m 달성</x:v>
+      </x:c>
+      <x:c r="O47" s="4" t="str">
+        <x:v>Night Watcher: 8 items and 500m in one night run</x:v>
+      </x:c>
+      <x:c r="P47" s="4" t="str">
+        <x:v>夜の番人で夜の1プレイ中にアイテム8個・500m達成</x:v>
       </x:c>
       <x:c r="Q47" s="4" t="inlineStr">
         <x:is>
@@ -4934,6 +4845,9 @@
           <x:t xml:space="preserve">skin_zodiac_rat_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z47" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="76" customHeight="1">
       <x:c r="A48" s="17" t="n">
@@ -4957,13 +4871,13 @@
         <x:v>雄牛</x:v>
       </x:c>
       <x:c r="G48" s="7" t="str">
-        <x:v>스무 번 딛고, 일 분 버티기</x:v>
+        <x:v>머리띠 조이고 쉰 번 딛기</x:v>
       </x:c>
       <x:c r="H48" s="7" t="str">
-        <x:v>Twenty landings, one minute</x:v>
+        <x:v>Band tied tight, fifty landings</x:v>
       </x:c>
       <x:c r="I48" s="7" t="str">
-        <x:v>二十回着地して、一分耐える</x:v>
+        <x:v>鉢巻を締めて、五十回着地</x:v>
       </x:c>
       <x:c r="J48" s="4" t="inlineStr">
         <x:is>
@@ -4983,20 +4897,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N48" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">한 판에서 그린 발판 20회 착지와 60초 생존</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O48" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">In one run, land on 20 drawn platforms and survive 60s</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P48" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1プレイで描いた足場に20回着地し60秒生存</x:t>
-        </x:is>
+      <x:c r="N48" s="4" t="str">
+        <x:v>수련 머리띠로 한 판에서 그린 발판 50회·120초·400m 달성</x:v>
+      </x:c>
+      <x:c r="O48" s="4" t="str">
+        <x:v>Training Band: 50 drawn landings, 120s and 400m in one run</x:v>
+      </x:c>
+      <x:c r="P48" s="4" t="str">
+        <x:v>修行の鉢巻で1プレイ中に描いた足場50回・120秒・400m達成</x:v>
       </x:c>
       <x:c r="Q48" s="4" t="inlineStr">
         <x:is>
@@ -5017,6 +4925,9 @@
           <x:t xml:space="preserve">skin_zodiac_ox_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z48" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="76" customHeight="1">
       <x:c r="A49" s="17" t="n">
@@ -5040,13 +4951,13 @@
         <x:v>虎柄の頭巾</x:v>
       </x:c>
       <x:c r="G49" s="7" t="str">
-        <x:v>밤사냥은 빈손으로</x:v>
+        <x:v>산군의 밤사냥은 빈손으로</x:v>
       </x:c>
       <x:c r="H49" s="7" t="str">
-        <x:v>Night hunting, empty-handed</x:v>
+        <x:v>The tiger hunts at night, empty-handed</x:v>
       </x:c>
       <x:c r="I49" s="7" t="str">
-        <x:v>夜の狩りは手ぶらで</x:v>
+        <x:v>山の虎は夜の狩りも手ぶら</x:v>
       </x:c>
       <x:c r="J49" s="4" t="inlineStr">
         <x:is>
@@ -5066,20 +4977,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N49" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">밤에 아이템 없이 150m 이상으로 한 판 완료</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O49" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Finish a night run at 150m or higher with no items</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P49" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">夜にアイテムなしで150m以上のプレイを完了</x:t>
-        </x:is>
+      <x:c r="N49" s="4" t="str">
+        <x:v>산군 탈로 밤에 아이템 없이 1000m 이상 한 판 완료</x:v>
+      </x:c>
+      <x:c r="O49" s="4" t="str">
+        <x:v>Tiger Mask: finish a night run at 1000m or higher without items</x:v>
+      </x:c>
+      <x:c r="P49" s="4" t="str">
+        <x:v>山の虎面で夜にアイテムなしで1000m以上のプレイを完了</x:v>
       </x:c>
       <x:c r="Q49" s="4" t="inlineStr">
         <x:is>
@@ -5100,6 +5005,9 @@
           <x:t xml:space="preserve">skin_zodiac_tiger_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z49" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="76" customHeight="1">
       <x:c r="A50" s="17" t="n">
@@ -5123,13 +5031,13 @@
         <x:v>月兎</x:v>
       </x:c>
       <x:c r="G50" s="7" t="str">
-        <x:v>달을 쓰고 밤길 200</x:v>
+        <x:v>달을 쓰고 밤길 1500</x:v>
       </x:c>
       <x:c r="H50" s="7" t="str">
-        <x:v>Wear the moon, climb 200 at night</x:v>
+        <x:v>Wear the moon, climb 1500 at night</x:v>
       </x:c>
       <x:c r="I50" s="7" t="str">
-        <x:v>月をかぶって、夜道を200</x:v>
+        <x:v>月をかぶって、夜道を1500</x:v>
       </x:c>
       <x:c r="J50" s="4" t="inlineStr">
         <x:is>
@@ -5149,20 +5057,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N50" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">달빛 관을 쓰고 밤에 200m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O50" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Wear Moon Crown and reach 200m at night</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P50" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">月光の冠を着けて夜に200m達成</x:t>
-        </x:is>
+      <x:c r="N50" s="4" t="str">
+        <x:v>달빛 관을 쓰고 밤에 1500m 달성</x:v>
+      </x:c>
+      <x:c r="O50" s="4" t="str">
+        <x:v>Wear Moon Crown and reach 1500m at night</x:v>
+      </x:c>
+      <x:c r="P50" s="4" t="str">
+        <x:v>月光の冠を着けて夜に1500m達成</x:v>
       </x:c>
       <x:c r="Q50" s="4" t="inlineStr">
         <x:is>
@@ -5183,6 +5085,9 @@
           <x:t xml:space="preserve">skin_zodiac_rabbit_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z50" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="76" customHeight="1">
       <x:c r="A51" s="17" t="n">
@@ -5206,13 +5111,13 @@
         <x:v>竜角</x:v>
       </x:c>
       <x:c r="G51" s="7" t="str">
-        <x:v>꼬리 달고 300까지</x:v>
+        <x:v>꼬리 달고 1800까지</x:v>
       </x:c>
       <x:c r="H51" s="7" t="str">
-        <x:v>Tail on, up to 300</x:v>
+        <x:v>Tail on, up to 1800</x:v>
       </x:c>
       <x:c r="I51" s="7" t="str">
-        <x:v>しっぽをつけて300まで</x:v>
+        <x:v>しっぽをつけて1800まで</x:v>
       </x:c>
       <x:c r="J51" s="4" t="inlineStr">
         <x:is>
@@ -5232,20 +5137,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N51" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">용꼬리를 달고 300m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O51" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Wear Dragon Tail and reach 300m</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P51" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">竜のしっぽを着けて300m達成</x:t>
-        </x:is>
+      <x:c r="N51" s="4" t="str">
+        <x:v>용꼬리를 달고 1800m 달성</x:v>
+      </x:c>
+      <x:c r="O51" s="4" t="str">
+        <x:v>Wear Dragon Tail and reach 1800m</x:v>
+      </x:c>
+      <x:c r="P51" s="4" t="str">
+        <x:v>竜のしっぽを着けて1800m達成</x:v>
       </x:c>
       <x:c r="Q51" s="4" t="inlineStr">
         <x:is>
@@ -5266,6 +5165,9 @@
           <x:t xml:space="preserve">skin_zodiac_dragon_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z51" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="76" customHeight="1">
       <x:c r="A52" s="17" t="n">
@@ -5289,13 +5191,13 @@
         <x:v>蛇の結び目</x:v>
       </x:c>
       <x:c r="G52" s="7" t="str">
-        <x:v>거미의 열두 번째 착지</x:v>
+        <x:v>거미의 마흔 번째 착지</x:v>
       </x:c>
       <x:c r="H52" s="7" t="str">
-        <x:v>The spider's twelfth landing</x:v>
+        <x:v>The spider's fortieth landing</x:v>
       </x:c>
       <x:c r="I52" s="7" t="str">
-        <x:v>蜘蛛の十二回目の着地</x:v>
+        <x:v>蜘蛛の四十回目の着地</x:v>
       </x:c>
       <x:c r="J52" s="4" t="inlineStr">
         <x:is>
@@ -5315,20 +5217,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N52" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">거미탈로 한 판에서 발판 12회 착지와 120m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O52" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Spider Mask: 12 drawn landings + 120m in one run</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P52" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">蜘蛛の面で1プレイ中に描いた足場へ12回着地し120m達成</x:t>
-        </x:is>
+      <x:c r="N52" s="4" t="str">
+        <x:v>거미탈로 한 판에서 그린 발판 40회·1000m 달성</x:v>
+      </x:c>
+      <x:c r="O52" s="4" t="str">
+        <x:v>Spider Mask: 40 drawn landings and 1000m in one run</x:v>
+      </x:c>
+      <x:c r="P52" s="4" t="str">
+        <x:v>蜘蛛の面で1プレイ中に描いた足場40回・1000m達成</x:v>
       </x:c>
       <x:c r="Q52" s="4" t="inlineStr">
         <x:is>
@@ -5349,6 +5245,9 @@
           <x:t xml:space="preserve">skin_zodiac_snake_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z52" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="76" customHeight="1">
       <x:c r="A53" s="17" t="n">
@@ -5372,13 +5271,13 @@
         <x:v>たてがみ</x:v>
       </x:c>
       <x:c r="G53" s="7" t="str">
-        <x:v>300까지 일 분이면 돼</x:v>
+        <x:v>붉은 발로 1000, 일 분 반</x:v>
       </x:c>
       <x:c r="H53" s="7" t="str">
-        <x:v>One minute to finish at 300</x:v>
+        <x:v>Crimson feet, 1000 in ninety seconds</x:v>
       </x:c>
       <x:c r="I53" s="7" t="str">
-        <x:v>300まで、一分あればいい</x:v>
+        <x:v>紅の足で1000、一分半</x:v>
       </x:c>
       <x:c r="J53" s="4" t="inlineStr">
         <x:is>
@@ -5398,20 +5297,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N53" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">60초 안에 300m 이상으로 한 판 완료</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O53" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Finish a run at 300m or higher within 60s</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P53" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">60秒以内に300m以上のプレイを完了</x:t>
-        </x:is>
+      <x:c r="N53" s="4" t="str">
+        <x:v>붉은 버선으로 90초 안에 1000m 이상 한 판 완료</x:v>
+      </x:c>
+      <x:c r="O53" s="4" t="str">
+        <x:v>Crimson Steps: finish at 1000m or higher within 90s</x:v>
+      </x:c>
+      <x:c r="P53" s="4" t="str">
+        <x:v>紅の足袋で90秒以内に1000m以上のプレイを完了</x:v>
       </x:c>
       <x:c r="Q53" s="4" t="inlineStr">
         <x:is>
@@ -5432,6 +5325,9 @@
           <x:t xml:space="preserve">skin_zodiac_horse_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z53" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="76" customHeight="1">
       <x:c r="A54" s="17" t="n">
@@ -5455,13 +5351,13 @@
         <x:v>山羊</x:v>
       </x:c>
       <x:c r="G54" s="7" t="str">
-        <x:v>서른 번 딛고 200까지</x:v>
+        <x:v>깃털 달고 여든 번 딛기</x:v>
       </x:c>
       <x:c r="H54" s="7" t="str">
-        <x:v>Thirty steps, up to 200</x:v>
+        <x:v>Feather on, eighty landings</x:v>
       </x:c>
       <x:c r="I54" s="7" t="str">
-        <x:v>三十回ふんで200まで</x:v>
+        <x:v>羽をつけて八十回着地</x:v>
       </x:c>
       <x:c r="J54" s="4" t="inlineStr">
         <x:is>
@@ -5481,20 +5377,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N54" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">한 판에서 그린 발판 30회 착지와 200m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O54" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">In one run, land on 30 drawn platforms and reach 200m</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P54" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1プレイで描いた足場に30回着地し200m達成</x:t>
-        </x:is>
+      <x:c r="N54" s="4" t="str">
+        <x:v>깃털 비녀로 한 판에서 그린 발판 80회·1500m 달성</x:v>
+      </x:c>
+      <x:c r="O54" s="4" t="str">
+        <x:v>Feather Pin: 80 drawn landings and 1500m in one run</x:v>
+      </x:c>
+      <x:c r="P54" s="4" t="str">
+        <x:v>羽のかんざしで1プレイ中に描いた足場80回・1500m達成</x:v>
       </x:c>
       <x:c r="Q54" s="4" t="inlineStr">
         <x:is>
@@ -5515,6 +5405,9 @@
           <x:t xml:space="preserve">skin_zodiac_goat_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z54" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="76" customHeight="1">
       <x:c r="A55" s="17" t="n">
@@ -5544,13 +5437,13 @@
         </x:is>
       </x:c>
       <x:c r="G55" s="7" t="str">
-        <x:v>셋이서 간식 다섯 개</x:v>
+        <x:v>방울 울려 여덟이 모이면</x:v>
       </x:c>
       <x:c r="H55" s="7" t="str">
-        <x:v>Three friends, five snacks</x:v>
+        <x:v>Ring the bell, gather eight</x:v>
       </x:c>
       <x:c r="I55" s="7" t="str">
-        <x:v>三人でおやつ五つ</x:v>
+        <x:v>鈴を鳴らして八人集合</x:v>
       </x:c>
       <x:c r="J55" s="4" t="inlineStr">
         <x:is>
@@ -5570,20 +5463,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N55" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">한 판에서 먹 3마리 동시 생존과 아이템 5개 획득</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O55" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">In one run, have 3 Inks alive together and collect 5 items</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P55" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1プレイで墨3体の同時生存とアイテム5個を達成</x:t>
-        </x:is>
+      <x:c r="N55" s="4" t="str">
+        <x:v>방울 매듭으로 한 판에서 먹 8마리 동시 생존·아이템 20개·600m 달성</x:v>
+      </x:c>
+      <x:c r="O55" s="4" t="str">
+        <x:v>Bell Knot: 8 Inks alive together, 20 items and 600m in one run</x:v>
+      </x:c>
+      <x:c r="P55" s="4" t="str">
+        <x:v>鈴結びで1プレイ中に墨8体同時生存・アイテム20個・600m達成</x:v>
       </x:c>
       <x:c r="Q55" s="4" t="inlineStr">
         <x:is>
@@ -5604,6 +5491,9 @@
           <x:t xml:space="preserve">skin_zodiac_monkey_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z55" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="76" customHeight="1">
       <x:c r="A56" s="17" t="n">
@@ -5627,13 +5517,13 @@
         <x:v>とさか</x:v>
       </x:c>
       <x:c r="G56" s="7" t="str">
-        <x:v>해 뜨면 먹방울 셋</x:v>
+        <x:v>갓 쓰고 아침 먹방울 여섯</x:v>
       </x:c>
       <x:c r="H56" s="7" t="str">
-        <x:v>Sun's up, three Ink Drops</x:v>
+        <x:v>Gat on, six morning Ink Drops</x:v>
       </x:c>
       <x:c r="I56" s="7" t="str">
-        <x:v>日が出たら墨滴三つ</x:v>
+        <x:v>笠をかぶって朝の墨滴六つ</x:v>
       </x:c>
       <x:c r="J56" s="4" t="inlineStr">
         <x:is>
@@ -5653,20 +5543,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N56" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">낮 한 판에서 먹방울 3개와 100m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O56" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">In one day run, collect 3 Ink Drops and reach 100m</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P56" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">昼の1プレイで墨滴3個と100m達成</x:t>
-        </x:is>
+      <x:c r="N56" s="4" t="str">
+        <x:v>바람 갓으로 낮 한 판에서 먹방울 6개·900m 달성</x:v>
+      </x:c>
+      <x:c r="O56" s="4" t="str">
+        <x:v>Wind Gat: 6 Ink Drops and 900m in one day run</x:v>
+      </x:c>
+      <x:c r="P56" s="4" t="str">
+        <x:v>風の笠で昼の1プレイ中に墨滴6個・900m達成</x:v>
       </x:c>
       <x:c r="Q56" s="4" t="inlineStr">
         <x:is>
@@ -5687,6 +5571,9 @@
           <x:t xml:space="preserve">skin_zodiac_rooster_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z56" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="76" customHeight="1">
       <x:c r="A57" s="17" t="n">
@@ -5710,13 +5597,13 @@
         <x:v>猟犬</x:v>
       </x:c>
       <x:c r="G57" s="7" t="str">
-        <x:v>둘이서 일 분 반</x:v>
+        <x:v>첫 매듭, 여섯 친구, 삼 분</x:v>
       </x:c>
       <x:c r="H57" s="7" t="str">
-        <x:v>Two friends, a minute and a half</x:v>
+        <x:v>First knot, six friends, three minutes</x:v>
       </x:c>
       <x:c r="I57" s="7" t="str">
-        <x:v>二人で一分半</x:v>
+        <x:v>最初の結び目、六人、三分</x:v>
       </x:c>
       <x:c r="J57" s="4" t="inlineStr">
         <x:is>
@@ -5736,20 +5623,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N57" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">한 판에서 먹 2마리 동시 생존과 90초 생존</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O57" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">In one run, have 2 Inks alive together and survive 90s</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P57" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1プレイで墨2体の同時生存と90秒生存を達成</x:t>
-        </x:is>
+      <x:c r="N57" s="4" t="str">
+        <x:v>먹매듭으로 한 판에서 먹 6마리 동시 생존·180초·800m 달성</x:v>
+      </x:c>
+      <x:c r="O57" s="4" t="str">
+        <x:v>Ink Knot: 6 Inks alive together, 180s and 800m in one run</x:v>
+      </x:c>
+      <x:c r="P57" s="4" t="str">
+        <x:v>墨結びで1プレイ中に墨6体同時生存・180秒・800m達成</x:v>
       </x:c>
       <x:c r="Q57" s="4" t="inlineStr">
         <x:is>
@@ -5770,6 +5651,9 @@
           <x:t xml:space="preserve">skin_zodiac_dog_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z57" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="76" customHeight="1">
       <x:c r="A58" s="17" t="n">
@@ -5793,13 +5677,13 @@
         <x:v>豚の鼻</x:v>
       </x:c>
       <x:c r="G58" s="7" t="str">
-        <x:v>열두 개도 모자라</x:v>
+        <x:v>고양이도 서른 개는 배불러</x:v>
       </x:c>
       <x:c r="H58" s="7" t="str">
-        <x:v>Twelve is not enough</x:v>
+        <x:v>Even a cat is full after thirty</x:v>
       </x:c>
       <x:c r="I58" s="7" t="str">
-        <x:v>十二個でも足りない</x:v>
+        <x:v>猫も三十個でお腹いっぱい</x:v>
       </x:c>
       <x:c r="J58" s="4" t="inlineStr">
         <x:is>
@@ -5819,20 +5703,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N58" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">한 판에서 먹방울 3개 포함 아이템 12개 획득</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O58" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Collect 12 items, including 3 Ink Drops, in one run</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P58" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1プレイで墨滴3個を含むアイテム12個を獲得</x:t>
-        </x:is>
+      <x:c r="N58" s="4" t="str">
+        <x:v>고양이 귀로 한 판에서 먹방울 8개 포함 아이템 30개·1000m 달성</x:v>
+      </x:c>
+      <x:c r="O58" s="4" t="str">
+        <x:v>Cat Ears: 30 items including 8 Ink Drops, and 1000m in one run</x:v>
+      </x:c>
+      <x:c r="P58" s="4" t="str">
+        <x:v>猫耳で1プレイ中に墨滴8個を含むアイテム30個・1000m達成</x:v>
       </x:c>
       <x:c r="Q58" s="4" t="inlineStr">
         <x:is>
@@ -5853,6 +5731,9 @@
           <x:t xml:space="preserve">skin_zodiac_pig_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z58" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" ht="76" customHeight="1">
       <x:c r="A59" s="17" t="n">
@@ -5882,13 +5763,13 @@
         </x:is>
       </x:c>
       <x:c r="G59" s="7" t="str">
-        <x:v>현무는 250까지 빈손</x:v>
+        <x:v>현무는 2000까지 빈손</x:v>
       </x:c>
       <x:c r="H59" s="7" t="str">
-        <x:v>Hyunmu goes to 250 empty-handed</x:v>
+        <x:v>Hyunmu goes to 2000 empty-handed</x:v>
       </x:c>
       <x:c r="I59" s="7" t="str">
-        <x:v>玄武は250まで手ぶら</x:v>
+        <x:v>玄武は2000まで手ぶら</x:v>
       </x:c>
       <x:c r="J59" s="4" t="inlineStr">
         <x:is>
@@ -5909,13 +5790,13 @@
         </x:is>
       </x:c>
       <x:c r="N59" s="4" t="str">
-        <x:v>현무로 아이템 없이 250m 이상 한 판 완료</x:v>
+        <x:v>현무로 아이템 없이 2000m 이상 한 판 완료</x:v>
       </x:c>
       <x:c r="O59" s="4" t="str">
-        <x:v>With Hyunmu, finish at 250m or higher without items</x:v>
+        <x:v>With Hyunmu, finish at 2000m or higher without items</x:v>
       </x:c>
       <x:c r="P59" s="4" t="str">
-        <x:v>玄武でアイテムなしの250m以上プレイを完了</x:v>
+        <x:v>玄武でアイテムなしの2000m以上プレイを完了</x:v>
       </x:c>
       <x:c r="Q59" s="4" t="inlineStr">
         <x:is>
@@ -5936,6 +5817,9 @@
           <x:t xml:space="preserve">skin_haetae_crest_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z59" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="76" customHeight="1">
       <x:c r="A60" s="17" t="n">
@@ -5959,13 +5843,13 @@
         <x:v>三足烏</x:v>
       </x:c>
       <x:c r="G60" s="7" t="str">
-        <x:v>밤에는 셋셋셋</x:v>
+        <x:v>파수꾼의 밤, 아홉 방울, 3333</x:v>
       </x:c>
       <x:c r="H60" s="7" t="str">
-        <x:v>Three-three-three by night</x:v>
+        <x:v>Watcher's night, nine drops, 3333</x:v>
       </x:c>
       <x:c r="I60" s="7" t="str">
-        <x:v>夜は三・三・三</x:v>
+        <x:v>番人の夜、九滴、3333</x:v>
       </x:c>
       <x:c r="J60" s="4" t="inlineStr">
         <x:is>
@@ -5985,20 +5869,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N60" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">밤 한 판에서 먹방울 3개와 333m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O60" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">In one night run, collect 3 Ink Drops and reach 333m</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P60" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">夜の1プレイで墨滴3個と333m達成</x:t>
-        </x:is>
+      <x:c r="N60" s="4" t="str">
+        <x:v>밤의 파수꾼으로 밤 한 판에서 먹방울 9개·3333m 달성</x:v>
+      </x:c>
+      <x:c r="O60" s="4" t="str">
+        <x:v>Night Watcher: 9 Ink Drops and 3333m in one night run</x:v>
+      </x:c>
+      <x:c r="P60" s="4" t="str">
+        <x:v>夜の番人で夜の1プレイ中に墨滴9個・3333m達成</x:v>
       </x:c>
       <x:c r="Q60" s="4" t="inlineStr">
         <x:is>
@@ -6019,6 +5897,9 @@
           <x:t xml:space="preserve">skin_three_legged_crow_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z60" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="76" customHeight="1">
       <x:c r="A61" s="17" t="n">
@@ -6042,13 +5923,13 @@
         <x:v>九尾の狐</x:v>
       </x:c>
       <x:c r="G61" s="7" t="str">
-        <x:v>여우 셋이서 300까지</x:v>
+        <x:v>여우 아홉이서 2500까지</x:v>
       </x:c>
       <x:c r="H61" s="7" t="str">
-        <x:v>Three foxes, up to 300</x:v>
+        <x:v>Nine foxes, up to 2500</x:v>
       </x:c>
       <x:c r="I61" s="7" t="str">
-        <x:v>三匹の狐で300まで</x:v>
+        <x:v>九匹の狐で2500まで</x:v>
       </x:c>
       <x:c r="J61" s="4" t="inlineStr">
         <x:is>
@@ -6068,20 +5949,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N61" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">여우탈로 한 판에서 먹 3마리 동시 생존과 300m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O61" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fox Mask: 3 Inks alive together + 300m in one run</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P61" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">狐の面で1プレイ中に墨3体の同時生存と300mを達成</x:t>
-        </x:is>
+      <x:c r="N61" s="4" t="str">
+        <x:v>여우탈로 한 판에서 먹 9마리 동시 생존·2500m 달성</x:v>
+      </x:c>
+      <x:c r="O61" s="4" t="str">
+        <x:v>Fox Mask: 9 Inks alive together and 2500m in one run</x:v>
+      </x:c>
+      <x:c r="P61" s="4" t="str">
+        <x:v>狐の面で1プレイ中に墨9体同時生存・2500m達成</x:v>
       </x:c>
       <x:c r="Q61" s="4" t="inlineStr">
         <x:is>
@@ -6102,6 +5977,9 @@
           <x:t xml:space="preserve">skin_nine_tails_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z61" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="62" ht="76" customHeight="1">
       <x:c r="A62" s="17" t="n">
@@ -6157,20 +6035,14 @@
           <x:t xml:space="preserve">NO</x:t>
         </x:is>
       </x:c>
-      <x:c r="N62" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">로비에서 한 번 던진 먹을 벽에 3회 연속 튕기기</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O62" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">In the lobby, get 3 wall bounces from one toss.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P62" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ロビーで墨を1回投げ、壁で連続3回跳ね返す</x:t>
-        </x:is>
+      <x:c r="N62" s="4" t="str">
+        <x:v>로비에서 한 번 던진 먹을 벽에 3회 연속 튕기기</x:v>
+      </x:c>
+      <x:c r="O62" s="4" t="str">
+        <x:v>In the lobby, get 3 wall bounces from one toss.</x:v>
+      </x:c>
+      <x:c r="P62" s="4" t="str">
+        <x:v>ロビーで墨を1回投げ、壁で連続3回跳ね返す</x:v>
       </x:c>
       <x:c r="Q62" s="4" t="inlineStr">
         <x:is>
@@ -6191,6 +6063,9 @@
           <x:t xml:space="preserve">skin_three_cushion_v1</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z62" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="76" customHeight="1">
       <x:c r="A63" s="17" t="n">
@@ -6233,27 +6108,21 @@
         </x:is>
       </x:c>
       <x:c r="L63" s="19" t="n">
-        <x:v>10000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="M63" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">YES</x:t>
         </x:is>
       </x:c>
-      <x:c r="N63" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">누적 고도 10000m 달성</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O63" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Climb 10000m in total</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P63" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">累計高度10000mに到達</x:t>
-        </x:is>
+      <x:c r="N63" s="4" t="str">
+        <x:v>누적 고도 150000m 달성</x:v>
+      </x:c>
+      <x:c r="O63" s="4" t="str">
+        <x:v>Climb 150000m in total</x:v>
+      </x:c>
+      <x:c r="P63" s="4" t="str">
+        <x:v>累計高度150000mに到達</x:v>
       </x:c>
       <x:c r="Q63" s="4" t="inlineStr">
         <x:is>
@@ -6285,6 +6154,9 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Y63" s="4" t="str"/>
+      <x:c r="Z63" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="41">
@@ -6454,9 +6326,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5bc1cebba0064cfc"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raba85d40e4044c5b"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4adffb982036498b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2359b61d89924bbf"/>
   </x:tableParts>
 </x:worksheet>
 </file>